--- a/docs/knowledge_chest.xlsx
+++ b/docs/knowledge_chest.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Dataset Universe" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Papers'!$A$1:$L$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dataset Universe'!$A$1:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Papers'!$A$1:$L$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dataset Universe'!$A$1:$I$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+          <t>Working Paper - 2026 - Egan et al. - Who Pays for Payments</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -527,50 +527,50 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Correia, Luck, Verner</t>
+          <t>Egan, Matvos, Seru, Wang, Yao</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Bank Runs with and without Bank Failure</t>
+          <t>Who Pays for Payments?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>This paper builds a comprehensive historical database of U.S. bank runs by applying large language models to historical newspapers, yielding information on 3,984 runs on individual banks from 1863 to 1934. The data show runs are far more likely at weak banks but also occur at strong banks, especially following negative news about the real economy or the broader banking system. Crucially, runs typically cause failure only when a bank's fundamentals are poor; strong banks survive through signaling, interbank cooperation, and temporary suspension. Locally, runs on weak banks produce much larger declines in deposits, lending, and manufacturing activity than runs on strong banks. The findings put poor fundamentals at the center of both when runs occur and when they are economically damaging, tempering pure self-fulfilling-panic accounts.</t>
+          <t>This paper uses novel data on the composition and cost of payments across U.S. merchants to quantify redistribution in the payment system. Card interchange fees fund consumer rewards, and when merchants raise prices for everyone, users of low-cost methods like cash and debit cross-subsidize high-reward credit-card users at the same merchant. The authors show incidence actually depends on the joint distribution of payment choices across merchants, not the standard assumption that everyone shops at the same stores facing the same fees. Two forces shape redistribution: consumer sorting, where users of different payment methods shop at different merchants, limits cash and debit users' exposure to high interchange fees; and interchange fees vary across merchants, being lower where payment types overlap (e.g., large grocery stores) due to sector discounts and negotiations. Embedding these forces in a sufficient-statistics framework, the paper revises who ultimately bears payment-system costs.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>The paper's first contribution is measurement: it uses LLMs to read historical newspapers and assemble a large, bank-level database of runs spanning 1863-1934. With this data, it asks whether runs strike indiscriminately or track fundamentals, showing runs concentrate in weak banks yet can hit strong banks after adverse news. It then distinguishes runs from failures, documenting that strong banks survive runs via signaling, cooperation, and suspension, so that failure requires poor fundamentals. Finally it links runs to local real outcomes, showing damage is concentrated where fundamentals are weak, which it interprets as evidence against models where small shocks trigger discontinuous jumps to bad equilibria.</t>
+          <t>The paper reconsiders the common claim that low-reward payers subsidize high-reward card users, noting it assumes uniform shopping and fees. Using merchant-level payment data, it documents two overlooked forces - consumer sorting across merchants and cross-merchant variation in interchange fees. It shows sorting insulates cash and debit users from high-fee exposure, while fee variation further shapes overlap points. It then embeds these forces in a sufficient-statistics incidence framework to recompute the direction and magnitude of cross-subsidies in the payment system.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Construction of a novel bank-level historical dataset via large language models applied to newspaper archives, combined with empirical analysis relating runs to bank fundamentals, survival mechanisms, and local real-economy outcomes.</t>
+          <t>A sufficient-statistics incidence framework estimated on proprietary merchant-acquirer payment data, combined with consumer payment-diary data, to quantify cross-subsidies under consumer sorting and merchant-level fee variation.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Banking History, Financial Crises, Text-as-Data / LLMs</t>
+          <t>Payments, Household Finance, Industrial Organization</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Correia, Luck &amp; Verner (this paper) — Historical bank-run database; Library of Congress — Chronicling America; OCC — National bank call reports (Annual Report to Congress)</t>
+          <t>Fiserv; Federal Reserve Bank of Atlanta — Diary of Consumer Payment Choice (DCPC); Nilson Report</t>
         </is>
       </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure.pdf</t>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Egan et al. - Who Pays for Payments.pdf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Bornstein and Castillo-Martinez - Firm Exit and Financial Frictions</t>
+          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -579,50 +579,50 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Bornstein, Castillo-Martinez</t>
+          <t>Drechsler, Savov, Schnabl</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Firm Exit and Financial Frictions</t>
+          <t>Credit Crunches and the Great Stagflation</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>This paper examines whether financial frictions cause too many firms to fail, motivating government interventions that prevent closures during crises. The authors build a firm-dynamics model with incomplete financial markets and show that frictions generate excessive firm exit, with a key sufficient statistic being the marginal propensity to exit with debt. Using confidential U.S. Census data, they estimate the debt–exit relationship and use it to discipline the model. The calibrated model implies that eliminating financial frictions would cut firm exit from 9.3% to 5.0% and deliver welfare gains of 3.6% in consumption-equivalent terms, with costs that spike during financial crises but not during ordinary productivity recessions. Comparing government-guaranteed loans and grants, the paper quantifies the trade-off between fiscal cost and effectiveness in preventing excessive exit.</t>
+          <t>This paper argues that severe banking-system credit crunches helped cause the Great Stagflation of the 1970s, working through Regulation Q, which capped deposit rates. Under Reg Q, Fed tightening triggered large deposit outflows that forced banks to contract lending, and these credit crunches line up closely with stagflation over time. Adding Reg Q to a standard model where firms finance working capital with bank loans, the authors show binding caps make working capital costlier, leading firms to raise prices and cut output. This yields an augmented Phillips curve in which monetary tightening reduces aggregate supply as well as demand, with effects increasing in credit-crunch severity, external-finance dependence, and working-capital intensity. Cross-industry tests confirm that more exposed manufacturing industries raised prices and cut output relative to others.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>The paper starts from the policy fear that viable-but-constrained firms fail in crises, and asks when firm exit is actually inefficient. It develops a firm-dynamics model with incomplete markets in which financial frictions distort the exit margin, isolating the marginal propensity to exit with debt as the statistic governing dynamic inefficiency. It then estimates the debt–exit relationship in confidential Census data to discipline that statistic and calibrate the model. Using the calibrated model, it quantifies the welfare cost of frictions across crisis and non-crisis states and evaluates guaranteed loans versus grants as interventions.</t>
+          <t>The paper links a monetary-institutional feature - Regulation Q deposit-rate caps - to the macro puzzle of simultaneous high inflation and stagnation. It explains how Fed tightening under Reg Q caused deposit outflows and lending contractions, then documents that these credit crunches track stagflation in the time series. It embeds Reg Q in a working-capital model, deriving an augmented Phillips curve where tighter credit raises firms' costs and shifts aggregate supply inward. It then tests the model's cross-sectional predictions across manufacturing industries by exposure, external-finance dependence, and working-capital intensity.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>A quantitative firm-dynamics model with incomplete financial markets, disciplined by a reduced-form debt–exit relationship estimated on confidential U.S. Census microdata, used for welfare analysis and policy (loan-guarantee vs. grant) comparison.</t>
+          <t>A quantitative macro model (working-capital channel with Regulation Q) combined with time-series evidence and cross-industry exposure-based empirical tests of its supply-side predictions.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Firm Dynamics, Financial Frictions, Macroeconomic Policy</t>
+          <t>Monetary Economics, Banking, Macro-Finance</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>U.S. Census Bureau — Longitudinal Business Database (LBD); Bureau van Dijk — Orbis (Italy)</t>
+          <t>U.S. Call Reports (via FOIA); NBER-CES — Manufacturing Industry Database; FDIC — Historical Bank Data; Federal Reserve — Senior Loan Officer Opinion Survey (SLOOS)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Bornstein and Castillo-Martinez - Firm Exit and Financial Frictions.pdf</t>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation.pdf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Malenko et al. - Fragmentation of Shareholder Power</t>
+          <t>Working Paper - 2026 - Chen and Sacerdote - Capital in the Capitol Congressional Trades Resemble Uninformed Retail Trading</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -631,50 +631,50 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Malenko, Malenko, Tsoy</t>
+          <t>Chen, Sacerdote</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Fragmentation of Shareholder Power</t>
+          <t>Capital in the Capitol: Congressional Trades Resemble Uninformed Retail Trading</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>This paper develops a theoretical framework to evaluate how the asset-management industry's shift toward tailored portfolios, fund proliferation, and decentralized stewardship affects corporate governance. Growing heterogeneity in investor preferences better aligns products with demand but can fragment ownership and weaken managerial oversight. The authors show fund proliferation does not necessarily weaken governance: stronger manager incentives and concentrated portfolios of specialized funds can offset fragmentation, especially when investor preferences are intense. However, intense preferences can also push asset managers to compete by granting investors control—decentralizing stewardship and adopting pass-through voting—without internalizing the resulting governance costs. The paper clarifies when investor-driven customization helps or harms oversight.</t>
+          <t>This paper asks whether members of Congress exploit informational advantages in their personal stock trading, using a new hand-collected dataset of all U.S. legislators' and their families' trades from 2012 to 2023. After the STOCK Act, legislators' portfolios on average underperform or merely match market benchmarks. To explain this mediocre performance, the authors show legislators' positions track financial professionals' recommendations and that their trade timing reflects prevailing market sentiment - estimated from retail investors' social-media posts - rather than anticipating price moves. Congressional trading thus looks like public-signal-following and resembles uninformed retail behavior. The paper pushes back on the view that legislators systematically trade on private information.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>The paper begins from real industry trends—customization, more funds, and decentralized voting—and asks whether they necessarily erode the monitoring that concentrated ownership provides. It builds a model in which asset managers choose portfolio concentration, effort, and how much control to pass through to investors, given heterogeneous investor preferences. Analyzing the model, it shows proliferation can coexist with strong governance when incentives and specialization are strong, particularly under intense preferences. It then identifies a countervailing force: competition on the 'control' margin can lead managers to decentralize stewardship inefficiently, because they do not bear the full governance cost.</t>
+          <t>The paper revisits the contested question of congressional trading advantage, noting prior studies used limited samples and said little about mechanisms. It builds a comprehensive hand-collected record of legislator and family trades and evaluates performance against multiple benchmarks, finding no outperformance after the STOCK Act. It then probes why, testing whether trades follow analyst recommendations and align with market sentiment measured from retail social-media activity. Finding that timing mirrors public sentiment rather than leading prices, it concludes legislators' observable trading resembles uninformed retail trading.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Theoretical model (mechanism/contracting framework) of asset-manager portfolio choice, incentives, and stewardship decentralization under heterogeneous investor preferences; no external dataset.</t>
+          <t>Event-study and calendar-time portfolio performance analysis on a hand-collected congressional-trading dataset, plus mechanism tests linking trades to analyst recommendations and social-media sentiment.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Corporate Governance, Asset Management, Financial Theory</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Theoretical paper; no nonstandard datasets identified.</t>
-        </is>
-      </c>
+          <t>Political Economy, Informed Trading, Behavioral Finance</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Chen &amp; Sacerdote (this paper) — Congressional trading records; Context Analytics — S-Score (Twitter/X sentiment)</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Malenko et al. - Fragmentation of Shareholder Power.pdf</t>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Chen and Sacerdote - Capital in the Capitol Congressional Trades Resemble Uninformed Retail Trading.pdf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Bardóczy et al. - Monopsony Power and the Transmission of Monetary Policy</t>
+          <t>Working Paper - 2026 - Pagel et al. - Bank Fees and Household Financial Well-Being</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -683,50 +683,50 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Bardóczy, Bornstein, Salgado</t>
+          <t>Pagel, Sridhar, Williams</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Monopsony Power and the Transmission of Monetary Policy</t>
+          <t>Bank Fees and Household Financial Well-Being</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>This paper studies how employer labor-market power changes the way monetary policy transmits to wages and employment. Using administrative U.S. Census data, the authors show that high-monopsony firms—those accounting for over 10 percent of their local wage bill—adjust their wage bill and employment less in response to monetary policy. They rationalize this with a New Keynesian model featuring heterogeneous firms and oligopsonistic labor competition, where wage stickiness combined with labor-market power drives the muted response. The model isolates two channels—partial passthrough and misallocation—through which oligopsony shapes aggregate effects. Calibrated to U.S. labor markets, it implies that the decline in labor-market power since the 1980s raised the output response to monetary policy by about 10 percent and accounts for roughly 15 percent of the flattening of the Phillips curve.</t>
+          <t>This paper studies 2017-2022 policy changes at large U.S. banks that eliminated non-sufficient-funds (NSF) fees and relaxed overdraft policies, using individual transaction-level data. Eliminating NSF fees immediately reduced NSF charges across the income distribution, as expected. Relaxing overdraft policies, however, reduced overdraft fees only for wealthier (higher-income, higher-liquidity) households, and only they saw subsequent declines in late fees, interest, maintenance fees, and use of alternatives like payday loans. The authors conclude the changes were not substantial enough to meaningfully relieve financial stress for the most vulnerable households. Methodologically, the multi-treatment, varying-intensity setting motivates a new stacked event-study estimator related to de Chaisemartin et al. (2024) to handle staggered-DiD biases.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>The paper posits that firms with labor-market power set wages strategically, so their response to monetary policy may differ systematically from competitive firms. Using administrative data, it establishes that high-monopsony firms adjust wage bill and employment less after monetary shocks. To interpret this, it builds a heterogeneous-firm New Keynesian model with oligopsony in which wage stickiness and market power jointly generate the muted response. The model formalizes partial passthrough and misallocation channels, and its calibration links the secular decline in monopsony to changes in the potency of monetary policy and the slope of the Phillips curve.</t>
+          <t>The paper asks whether widely publicized reductions in bank fees actually improved household financial well-being, especially for vulnerable households. Using transaction-level data, it separates two distinct policy changes - NSF-fee elimination and overdraft relaxation - and traces their effects across the income and liquidity distribution. It finds broad relief from NSF elimination but overdraft benefits accruing only to wealthier households, who then experience knock-on reductions in other fees and costly credit. Because the setting has multiple staggered treatments of differing intensity, it develops and applies a stacked event-study estimator to obtain unbiased effects.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Empirical estimation of firm-level monetary-policy responses by monopsony intensity using administrative Census data, combined with a calibrated heterogeneous-firm New Keynesian model with oligopsonistic labor markets.</t>
+          <t>Stacked event-study / staggered difference-in-differences (a new estimator related to de Chaisemartin et al. 2024) on individual transaction-level banking data around NSF/overdraft policy changes.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Monetary Policy, Labor Market Power, Macroeconomics</t>
+          <t>Household Finance, Banking, Consumer Protection</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>U.S. Census Bureau — LEHD merged with Longitudinal Business Database (LBD)</t>
+          <t>Consumer transaction-data provider; FDIC — Summary of Deposits</t>
         </is>
       </c>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Bardóczy et al. - Monopsony Power and the Transmission of Monetary Policy.pdf</t>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Pagel et al. - Bank Fees and Household Financial Well-Being.pdf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+          <t>Working Paper - 2026 - Matvos et al. - Private Credit, Balance Sheets and Financial Stability</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -735,50 +735,50 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Thesmar, Verner</t>
+          <t>Matvos, Piskorski, Seru</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Beliefs and Stock Market Fluctuations: New Evidence from the Past Seven Decades</t>
+          <t>Private Credit, Balance Sheets and Financial Stability</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>This paper builds a new seven-decade series of subjective expected equity returns (1956-2024) from an independent equity-analysis firm and uses it to reassess how beliefs move markets. Unlike the expectations of individual investors and professional forecasters, this measure is strongly positively correlated with the earnings-price ratio, responds negatively to past returns, and positively predicts future returns. Individual and professional-forecaster expectations are only weakly or negatively correlated with the new series, and disagreement between sophisticated and individual investors is associated with higher trading volume. The evidence fits a model of heterogeneous beliefs in which naive investors extrapolate past returns while sophisticated investors are close to rational. The paper offers a rare long-run window on the belief dynamics behind valuations.</t>
+          <t>This paper uses new, comprehensive fund- and asset-level data covering most of the private-credit industry to assess its balance sheets and financial-stability implications. Private-credit funds are highly capitalized, with equity typically 65-80% of assets - more than six times the capitalization of U.S. banks - and use only moderate debt, largely bank credit lines for liquidity management. Fund lives of 10-12 years exceed the shorter maturities of underlying loans, implying little maturity mismatch, unlike banks that fund long-term assets with short-term callable deposits. Portfolios are diversified across industries, geographies, and strategies, and performance shows positive average net returns with losses borne mainly by equity. The authors conclude that, as currently structured, private-credit funds are conservatively built and unlikely to pose bank-like systemic risks.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>The paper motivates the need for a long, consistent measure of sophisticated investors' return expectations, which it constructs by hand from decades of an independent equity-analysis firm's forecasts. It characterizes the new series' properties—co-movement with the earnings-price ratio, mean-reverting response to past returns, and predictive power for future returns—and contrasts them with survey measures of individuals and forecasters. Finding that sophisticated and naive expectations diverge, and that their disagreement tracks trading volume, it argues a single-belief model cannot fit the facts. It then shows a heterogeneous-beliefs model, with extrapolative naive investors and near-rational sophisticated investors, rationalizes the joint patterns.</t>
+          <t>The paper addresses the financial-stability debate around private credit by bringing comprehensive fund- and asset-level data to bear on how these funds are actually capitalized and funded. It documents high equity ratios and limited, liquidity-oriented debt, contrasting this with banks' thin capital and deposit funding. It then shows the maturity structure implies little mismatch and that portfolios are diversified, limiting correlated-shock exposure. Finally it examines performance and loss-bearing, arguing the equity-heavy structure absorbs losses, so current private-credit configurations are unlikely to generate bank-style systemic risk.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Construction and analysis of a novel long-run (1956-2024) subjective-expected-return series hand-collected from an independent equity-analysis firm, with predictive and correlation regressions against survey expectations and a heterogeneous-beliefs asset-pricing model.</t>
+          <t>Descriptive analysis of new proprietary fund- and asset-level private-credit data (~1,300 funds), benchmarked against U.S. commercial banks using regulatory data.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Behavioral Finance, Asset Pricing, Expectations &amp; Beliefs</t>
+          <t>Private Credit, Financial Stability, Banking</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Value Line Investment Survey; Robert Shiller — Investor Confidence Survey; UBS/Gallup and Livingston Survey</t>
+          <t>Proprietary private-credit data provider; Preqin</t>
         </is>
       </c>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades.pdf</t>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Matvos et al. - Private Credit, Balance Sheets and Financial Stability.pdf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+          <t>Working Paper - 2026 - Baslandze et al. - Artificial Intelligence, Productivity, and the Workforce Evidence from Corporate Executives</t>
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
@@ -787,50 +787,50 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Ahern</t>
+          <t>Baslandze, Edwards, Graham, McClure, Meyer, Sparks, Waddell, Weitz</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+          <t>Artificial Intelligence, Productivity, and the Workforce: Evidence from Corporate Executives</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>This paper shows that the industrial composition of a city's economy shapes its cost of municipal borrowing. In a panel of 1,177 U.S. cities from 2005 to 2022, greater sectoral concentration raises default risk and municipal bond spreads, especially where dominant industries are associated with low property values. Instrumental variables built from national sector-employment trends and regional house-price variation support a causal reading. A calibrated city-default model implies the estimated spread effect understates the gross risk from concentration, because concentration also brings agglomeration benefits that lower spreads, particularly in high-property-value cities. The paper connects local economic structure to public finance and credit risk.</t>
+          <t>This paper uses a novel survey of nearly 750 corporate executives to study how artificial intelligence is affecting productivity and the workforce. Adoption is highly heterogeneous: more than half of firms have already invested, though many smaller firms are just starting. Labor-productivity gains are positive, vary by sector, are expected to strengthen in 2026, and are concentrated in high-skill services and finance; they reflect higher revenue-based total factor productivity through innovation and demand channels rather than capital deepening. The authors document a 'productivity paradox' in which perceived gains exceed measured gains, likely due to delayed revenue realization. In labor markets they find little near-term aggregate employment decline, though large firms anticipate AI-driven reductions while smaller firms expect modest gains, alongside compositional labor reallocation.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>The paper reasons that a city dependent on few industries faces more concentrated economic risk, which should raise default probability and hence bond spreads, but that the effect may depend on whether those industries support high property values that anchor the tax base. It documents the concentration–spread relationship in a large city panel and shows it is stronger where dominant sectors imply low property values. To move from correlation to causation, it instruments concentration using national sector-employment trends interacted with regional house-price variation. Finally, a calibrated default model reconciles the estimates with offsetting agglomeration benefits, implying the gross risk effect is larger than the net spread effect suggests.</t>
+          <t>Because firm-level effects of AI are hard to observe in standard data, the paper gathers direct evidence by surveying corporate executives about adoption, productivity, and workforce plans. It first documents wide heterogeneity in adoption and then characterizes the size, sectoral pattern, and channels of productivity gains, attributing them to revenue-based TFP rather than capital deepening. It reconciles optimistic perceptions with smaller measured effects through a productivity paradox driven by lagged revenue. Finally it turns to labor, showing limited aggregate employment effects so far but divergent expectations and reallocation across firm size and worker types.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Panel regressions with an instrumental-variables strategy (national sector-employment trends and regional house-price variation) linking industrial concentration to municipal bond spreads, complemented by a calibrated structural model of city default.</t>
+          <t>Survey-based descriptive and cross-sectional analysis of ~750 corporate executives, with comparisons of adoption, productivity, and workforce outcomes across firm size and sector.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Municipal Finance, Credit Risk, Urban &amp; Regional Economics</t>
+          <t>Economics of AI, Productivity, Labor Economics</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>MSRB — Municipal Securities Rulemaking Board trade data; U.S. Census Bureau — LODES (LEHD Origin-Destination Employment Statistics); FHFA — House Price Index</t>
+          <t>Federal Reserve Bank of Atlanta &amp; Duke University — Survey of corporate executives</t>
         </is>
       </c>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads.pdf</t>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Baslandze et al. - Artificial Intelligence, Productivity, and the Workforce Evidence from Corporate Executives.pdf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Clayton and Coppola - The Optimal Use of AI in Financial Regulation</t>
+          <t>Working Paper - 2026 - Eisfeldt et al. - Intangible Intensity</t>
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
@@ -839,50 +839,50 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Clayton, Coppola</t>
+          <t>Eisfeldt, Hartman-Glaser, Kim, Lee</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>The Optimal Use of AI in Financial Regulation</t>
+          <t>Intangible Intensity</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>This paper asks whether modern AI methods applied to granular portfolio-holdings data can improve macroprudential regulation, and how policymakers should use such tools. The authors build a graph-based deep learning model over security-level holdings of financial intermediaries that embeds economic priors and learns latent representations of both assets and investors from the network of positions. Applied to the near-universe of non-bank financial intermediaries (about $40 trillion), the model forecasts intermediary trading far better than existing approaches, including during crises, and has more than ten times the explanatory power for cross-sectional stress-period returns. Its learned embeddings encode economically interpretable information about fire-sale vulnerability, and the architecture is inductive enough to produce estimates even for withheld asset classes or investors. The authors then embed the empirical model in a macroprudential optimal-policy framework, addressing the Lucas critique, to show why these objects matter for welfare.</t>
+          <t>This paper builds a text-based measure of firms' intangible investment intensity from 10-K filings and introduces a general 'semantic theme scoring' (STS) methodology. The approach further decomposes disclosure text into knowledge, customer, and organization capital. High-intangible-intensity firms are smaller, younger, and invest heavily in R&amp;D and human capital, and the three subcomponents map to distinct firm types - knowledge-intensive (R&amp;D-driven, high valuation, skilled labor), customer-intensive (mature, profitable, commercial), and organization-intensive (large, asset-heavy incumbents). The authors show managerial expenditure descriptions carry informative signals about intangible capital that complement financial statements. The paper offers both a new measure and a reusable NLP methodology for capturing corporate intangibles.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>The paper frames systemic risk measurement as a prediction problem over the network of who holds what, arguing that the structure of intermediary holdings encodes fire-sale vulnerability that standard metrics miss. It develops a graph neural network with built-in economic priors that learns asset and investor representations from holdings, then validates the model out-of-sample on trading behavior and stress-period returns against existing benchmarks. Having shown the learned objects are predictive and interpretable, it asks how a regulator should optimally use them. It closes by embedding the empirical model in an equilibrium optimal-policy framework that confronts the Lucas critique, formalizing the welfare rationale for AI-based supervision.</t>
+          <t>The paper motivates that intangible capital is poorly captured by accounting statements, so it turns to the language firms use to describe their spending. It develops semantic theme scoring to convert 10-K disclosure text into an intangible-intensity measure and to separate knowledge, customer, and organization capital. It validates the measure by showing high-intangible firms have the expected profile and that the three components correspond to economically distinct firm types. It argues these text-derived signals complement financial data, opening avenues for measuring firms' position in the intangible lifecycle.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Design and out-of-sample evaluation of a graph-based (network) deep-learning model on security-level intermediary holdings, benchmarked against existing systemic-risk metrics, embedded within a macroprudential optimal-policy framework robust to the Lucas critique.</t>
+          <t>Text-as-data measurement: a semantic-theme-scoring (NLP) methodology applied to 10-K filings to construct and validate an intangible-intensity measure and its subcomponents, with cross-sectional characterization.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning in Finance, Financial Regulation, Systemic Risk</t>
+          <t>Intangible Capital, Text-as-Data / NLP, Corporate Finance</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>FactSet &amp; Morningstar — Security-level intermediary holdings</t>
+          <t>SEC (WRDS SEC Analytics Suite) — 10-K filings; S&amp;P Capital IQ</t>
         </is>
       </c>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Clayton and Coppola - The Optimal Use of AI in Financial Regulation.pdf</t>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Eisfeldt et al. - Intangible Intensity.pdf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics</t>
+          <t>Working Paper - 2026 - Amiti et al. - Why Do Firms Pay Different Interest Rates on Their Bank Loans</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
@@ -891,50 +891,50 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ebsim, Lian, Ma, Ottonello, Perez</t>
+          <t>Amiti, Kashyap, Kovner, Weinstein</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Sophisticated Borrowing Constraints and Macroeconomic Dynamics</t>
+          <t>Why Do Firms Pay Different Interest Rates on Their Bank Loans?</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>This paper argues that the way debt constraints are modeled fundamentally changes their macroeconomic implications. Traditional models impose hard borrowing limits that force firms to cut borrowing and investment whenever adverse shocks bind, producing financial acceleration. The authors instead model 'sophisticated borrowing constraints' resembling real-world financial covenants, where breaching an earnings-based debt threshold transfers control rights to creditors who then act to maximize their own value rather than mechanically shrinking credit. Calibrated to micro evidence on investment and earnings around covenant violations, the model matches firm-level dynamics while, at the macro level, generating no financial acceleration because violations do not trigger indiscriminate downscaling. The result challenges a workhorse mechanism linking credit conditions to aggregate fluctuations.</t>
+          <t>This paper documents large dispersion in interest rates on similar commercial and industrial loans using confidential supervisory data on the largest U.S. banks, and argues the spread is not explained by risk. The authors rationalize the dispersion with a search-cost model in which borrowers pay to solicit competing quotes. Estimated search costs are highest for smaller and riskier borrowers and lowest for public firms, matching predictable differences in screening and monitoring costs. The search costs are economically large: over a third of firms behave as if they never comparison-shop, half appear to obtain only two quotes, and the rest search widely. The paper interprets loan-rate dispersion as evidence of substantial search frictions in credit markets rather than pure risk pricing.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>The paper contrasts textbook hard constraints, under which binding limits mechanically force deleveraging and amplify shocks, with the institutional reality of covenants, which reallocate control rather than dictate fixed borrowing ratios. It models covenant violation as a state-contingent transfer of control to creditors who choose firm policies to maximize creditor value, so tightening need not cause uniform credit cuts. The authors first show the model reproduces the empirical behavior of investment and earnings around violations at the micro level. They then embed the mechanism in a general-equilibrium setting and demonstrate that, unlike hard constraints, sophisticated constraints do not generate financial acceleration.</t>
+          <t>The paper starts from the puzzle that observably similar borrowers pay very different loan rates even after accounting for risk, suggesting frictions beyond credit quality. It proposes a search-cost model in which firms trade off the cost of gathering additional quotes against the rate savings, generating dispersion that depends on borrower type. Using confidential loan-level supervisory data, it strips out risk and attributes residual dispersion to search costs, which it estimates structurally. The estimated pattern - higher search costs for small, risky, private borrowers - lines up with the economics of screening and monitoring, and implies many firms effectively fail to shop around.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>A quantitative macro-finance model with state-contingent, covenant-like borrowing constraints and creditor control rights, calibrated to firm-level dynamics around covenant violations, then evaluated for its aggregate (financial-acceleration) implications.</t>
+          <t>Structural estimation of a borrower search-cost model on confidential loan-level supervisory (FR Y-14) data, after controlling for risk, to recover the distribution of search costs across borrower types.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Macro-Finance, Corporate Debt &amp; Covenants, Firm Investment</t>
+          <t>Banking, Credit Markets, Search Frictions</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Refinitiv LPC — DealScan; Greg Nini (Nini, Smith &amp; Sufi) — Financial covenant violation data</t>
+          <t>Federal Reserve — FR Y-14 supervisory data</t>
         </is>
       </c>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics.pdf</t>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Amiti et al. - Why Do Firms Pay Different Interest Rates on Their Bank Loans.pdf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+          <t>Working Paper - 2026 - Dyck et al. - Venture Fraud</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -943,50 +943,50 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Dou, Wang, Wang</t>
+          <t>Dyck, Fang, Hebert, Xu</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>The Cost of Intermediary Market Power for Distressed Borrowers</t>
+          <t>Venture Fraud</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>This paper measures how much lender market power raises borrowing costs for firms in financial distress, who must raise urgent financing in thin, concentrated credit markets. The authors show that distressed borrowers pay very high loan spreads even after stripping out compensation for credit risk, liquidity risk, and ordinary loan-making costs. To decompose the residual, they build and estimate a dynamic game-theoretic model of distressed lending featuring latent demand heterogeneity, endogenous lender participation, creditor blocking power, and tacit collusion sustained by repeated syndication. Lender market power explains 533 basis points of risk-adjusted spreads in debtor-in-possession (DIP) loans and 300 basis points in highly speculative loans, with roughly 140 basis points from tacit collusion in each. Because this markup reduces survival-critical liquidity by 16–20%, market power emerges as a major, previously underappreciated source of financial-distress costs.</t>
+          <t>This paper assembles the first comprehensive sample of venture fraud - 614 U.S. venture-capital-backed startups founded since 2000 that faced fraud allegations - and studies its governance roots. Within a high-detection subsample of newly public firms, VC-backed firms are 54% more likely to face fraud charges than comparable non-VC-backed firms. Fraud is more likely where founders hold stronger control rights, more convex cash-flow rights, more investors, and more non-traditional investors, with founder-controlled boards 88% more likely to commit fraud than VC- or shared-control boards. Governance features predict fraud far better than founder characteristics, and hot funding conditions at the first round - which weaken governance - forecast later fraud. The paper reframes venture fraud as substantially a product of governance structures rather than individual bad actors.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>The argument begins by noting that distressed firms borrow in markets dominated by a few specialized lenders and by existing creditors who hold blocking power, so observed spreads may reflect market power rather than pure risk. The authors first document that DIP and highly speculative loan spreads remain large after removing risk and cost components, motivating a structural explanation. They then specify a dynamic game in which lenders choose whether to participate, exploit blocking power, and sustain tacit collusion through repeated syndication, allowing the markup to be identified and decomposed. Estimating the model on facility-level loan data, they quantify the market-power markup and trace its consequences for borrower liquidity and asset-value destruction.</t>
+          <t>The paper begins by building a large hand-collected sample of venture-fraud cases, addressing the measurement gap that has limited prior work. It first establishes that VC backing is associated with more fraud in a setting where detection is high and roughly uniform, ruling out pure detection differences. It then turns to mechanisms, arguing that founder-friendly structures and cap-table complexity weaken the monitoring that should deter fraud. Using a panel prediction model, it shows governance variables - founder control, convex payoffs, investor composition - dominate founder traits, and that hot-market financing conditions that erode governance at inception predict future fraud.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Structural estimation of a dynamic game-theoretic model of distressed lending (with endogenous participation, creditor blocking power, and tacit collusion), disciplined by facility-level DIP and highly speculative loan data, used to decompose risk-adjusted spreads into market-power components.</t>
+          <t>Hand-collected case-sample construction plus a matched comparison (VC vs. non-VC among newly public firms) and a hazard-style panel prediction model relating fraud to governance and financing-market conditions.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Financial Distress &amp; Bankruptcy, Banking &amp; Lending, Market Power / Industrial Organization</t>
+          <t>Venture Capital, Corporate Governance, Financial Fraud</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Refinitiv LPC — DealScan; LPC (Refinitiv) — LSTA/LPC Mark-to-Market Pricing Data; PACER — Public Access to Court Electronic Records; Moody's — Default and Recovery Database</t>
+          <t>PitchBook; Crunchbase; Dyck, Fang, Hebert &amp; Xu (this paper) — Venture-fraud case sample</t>
         </is>
       </c>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers.pdf</t>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Dyck et al. - Venture Fraud.pdf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - He et al. - Homemade Foreign Trading</t>
+          <t>Working Paper - 2026 - Diwan et al. - Competition and Fraud in Health Care</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -995,48 +995,568 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>He, Wang, Zhu</t>
+          <t>Diwan, Eliason, League, Leder-Luis, McDevitt, Roberts</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Homemade Foreign Trading</t>
+          <t>Competition and Fraud in Health Care</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>This paper documents how Chinese mainland insiders disguise domestic trades as foreign investment by round-tripping capital through the Stock Connect program, a practice the authors term 'homemade foreign trading.' Using cross-border holding data from all custodians in Stock Connect, they show that northbound flows predict returns and correlate with insider trading, but that this predictability decays after the 2018 Northbound Investor Identification reform introduced see-through surveillance. The decay is concentrated among less prestigious foreign custodians and cross-operating mainland custodians, precisely where insiders can most easily hide. The reform also reduces price informativeness in stocks most exposed to homemade foreign investors. The paper highlights regulatory cooperation as a key ingredient for the integrity of cross-border capital market integration.</t>
+          <t>This paper examines how competition affects fraud when governments procure goods and services from private firms, using Medicare's durable medical equipment (DME) market. The authors argue competition has an ambiguous effect on fraud: it dissipates the rents that attract fraudulent firms, but also squeezes margins so that legitimate firms may exit. Exploiting Medicare's switch from administratively regulated prices to competitive bidding for DME, they show that fraudulent suppliers' cost advantage let them gain market share while legitimate suppliers left the market. The result implies that price competition can perversely concentrate a market in fraudulent providers. The paper connects procurement design to the composition of firms and the prevalence of fraud.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>The paper starts from the observation that Stock Connect lets mainland capital exit and re-enter disguised as foreign 'northbound' flow, giving insiders a channel to trade on private information while appearing to be offshore investors. It argues that if such round-tripping is real, northbound flows should predict returns and track insider activity, and that a reform imposing investor-level identification should break this link by making insiders identifiable. Exploiting the 2018 Northbound Investor Identification reform as a shock to surveillance, the authors trace how return predictability and its correlation with insider trading decay afterward. They then sharpen identification by showing the effect is strongest where hiding is easiest (opaque custodians) and by documenting a decline in price informativeness for the most exposed stocks.</t>
+          <t>The paper frames government procurement as a setting where competition lowers prices but may change which firms survive, since fraudulent firms have an artificial cost advantage from not delivering legitimate goods or services. It uses Medicare's DME competitive-bidding reform as a shock that sharply lowered reimbursement, predicting that legitimate suppliers with real costs are squeezed out while fraudulent suppliers persist. Linking supplier-level Medicare claims to fraud-enforcement records, it traces how market shares and exit differ between fraudulent and legitimate firms after the reform. It interprets the resulting shift as evidence that competition alone does not discipline fraud and can even entrench it.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Event-study / difference-in-differences around the 2018 Northbound Investor Identification reform, using custodian-level cross-border holding data and return-predictability regressions, with cross-sectional heterogeneity by custodian type and stock exposure for identification.</t>
+          <t>Event-study/difference-in-differences around Medicare's switch to competitive bidding for durable medical equipment, using supplier-level claims linked to fraud-enforcement outcomes to compare fraudulent and legitimate firms.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>International Finance, Insider Trading, Market Microstructure</t>
+          <t>Health Economics, Industrial Organization &amp; Procurement, Fraud &amp; Enforcement</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>China Securities Depository and Clearing (CSDC) / Stock Connect; CSMAR — China Stock Market &amp; Accounting Research; WIND</t>
+          <t>Centers for Medicare &amp; Medicaid Services (CMS) — Medicare DMEPOS claims; DOJ / HHS-OIG — Fraud enforcement records; Yunan Ji — Medicare DME auction bids</t>
         </is>
       </c>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Diwan et al. - Competition and Fraud in Health Care.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Correia, Luck, Verner</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Bank Runs with and without Bank Failure</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>This paper builds a comprehensive historical database of U.S. bank runs by applying large language models to historical newspapers, yielding information on 3,984 runs on individual banks from 1863 to 1934. The data show runs are far more likely at weak banks but also occur at strong banks, especially following negative news about the real economy or the broader banking system. Crucially, runs typically cause failure only when a bank's fundamentals are poor; strong banks survive through signaling, interbank cooperation, and temporary suspension. Locally, runs on weak banks produce much larger declines in deposits, lending, and manufacturing activity than runs on strong banks. The findings put poor fundamentals at the center of both when runs occur and when they are economically damaging, tempering pure self-fulfilling-panic accounts.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>The paper's first contribution is measurement: it uses LLMs to read historical newspapers and assemble a large, bank-level database of runs spanning 1863-1934. With this data, it asks whether runs strike indiscriminately or track fundamentals, showing runs concentrate in weak banks yet can hit strong banks after adverse news. It then distinguishes runs from failures, documenting that strong banks survive runs via signaling, cooperation, and suspension, so that failure requires poor fundamentals. Finally it links runs to local real outcomes, showing damage is concentrated where fundamentals are weak, which it interprets as evidence against models where small shocks trigger discontinuous jumps to bad equilibria.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Construction of a novel bank-level historical dataset via large language models applied to newspaper archives, combined with empirical analysis relating runs to bank fundamentals, survival mechanisms, and local real-economy outcomes.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Banking History, Financial Crises, Text-as-Data / LLMs</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Correia, Luck &amp; Verner (this paper) — Historical bank-run database; Library of Congress — Chronicling America; OCC — National bank call reports (Annual Report to Congress)</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Bornstein and Castillo-Martinez - Firm Exit and Financial Frictions</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Bornstein, Castillo-Martinez</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Firm Exit and Financial Frictions</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>This paper examines whether financial frictions cause too many firms to fail, motivating government interventions that prevent closures during crises. The authors build a firm-dynamics model with incomplete financial markets and show that frictions generate excessive firm exit, with a key sufficient statistic being the marginal propensity to exit with debt. Using confidential U.S. Census data, they estimate the debt–exit relationship and use it to discipline the model. The calibrated model implies that eliminating financial frictions would cut firm exit from 9.3% to 5.0% and deliver welfare gains of 3.6% in consumption-equivalent terms, with costs that spike during financial crises but not during ordinary productivity recessions. Comparing government-guaranteed loans and grants, the paper quantifies the trade-off between fiscal cost and effectiveness in preventing excessive exit.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>The paper starts from the policy fear that viable-but-constrained firms fail in crises, and asks when firm exit is actually inefficient. It develops a firm-dynamics model with incomplete markets in which financial frictions distort the exit margin, isolating the marginal propensity to exit with debt as the statistic governing dynamic inefficiency. It then estimates the debt–exit relationship in confidential Census data to discipline that statistic and calibrate the model. Using the calibrated model, it quantifies the welfare cost of frictions across crisis and non-crisis states and evaluates guaranteed loans versus grants as interventions.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>A quantitative firm-dynamics model with incomplete financial markets, disciplined by a reduced-form debt–exit relationship estimated on confidential U.S. Census microdata, used for welfare analysis and policy (loan-guarantee vs. grant) comparison.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Firm Dynamics, Financial Frictions, Macroeconomic Policy</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Census Bureau — Longitudinal Business Database (LBD); Bureau van Dijk — Orbis (Italy)</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Bornstein and Castillo-Martinez - Firm Exit and Financial Frictions.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Malenko et al. - Fragmentation of Shareholder Power</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Malenko, Malenko, Tsoy</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Fragmentation of Shareholder Power</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>This paper develops a theoretical framework to evaluate how the asset-management industry's shift toward tailored portfolios, fund proliferation, and decentralized stewardship affects corporate governance. Growing heterogeneity in investor preferences better aligns products with demand but can fragment ownership and weaken managerial oversight. The authors show fund proliferation does not necessarily weaken governance: stronger manager incentives and concentrated portfolios of specialized funds can offset fragmentation, especially when investor preferences are intense. However, intense preferences can also push asset managers to compete by granting investors control—decentralizing stewardship and adopting pass-through voting—without internalizing the resulting governance costs. The paper clarifies when investor-driven customization helps or harms oversight.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>The paper begins from real industry trends—customization, more funds, and decentralized voting—and asks whether they necessarily erode the monitoring that concentrated ownership provides. It builds a model in which asset managers choose portfolio concentration, effort, and how much control to pass through to investors, given heterogeneous investor preferences. Analyzing the model, it shows proliferation can coexist with strong governance when incentives and specialization are strong, particularly under intense preferences. It then identifies a countervailing force: competition on the 'control' margin can lead managers to decentralize stewardship inefficiently, because they do not bear the full governance cost.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Theoretical model (mechanism/contracting framework) of asset-manager portfolio choice, incentives, and stewardship decentralization under heterogeneous investor preferences; no external dataset.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Governance, Asset Management, Financial Theory</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Theoretical paper; no nonstandard datasets identified.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Malenko et al. - Fragmentation of Shareholder Power.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Bardóczy et al. - Monopsony Power and the Transmission of Monetary Policy</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Bardóczy, Bornstein, Salgado</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Monopsony Power and the Transmission of Monetary Policy</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>This paper studies how employer labor-market power changes the way monetary policy transmits to wages and employment. Using administrative U.S. Census data, the authors show that high-monopsony firms—those accounting for over 10 percent of their local wage bill—adjust their wage bill and employment less in response to monetary policy. They rationalize this with a New Keynesian model featuring heterogeneous firms and oligopsonistic labor competition, where wage stickiness combined with labor-market power drives the muted response. The model isolates two channels—partial passthrough and misallocation—through which oligopsony shapes aggregate effects. Calibrated to U.S. labor markets, it implies that the decline in labor-market power since the 1980s raised the output response to monetary policy by about 10 percent and accounts for roughly 15 percent of the flattening of the Phillips curve.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>The paper posits that firms with labor-market power set wages strategically, so their response to monetary policy may differ systematically from competitive firms. Using administrative data, it establishes that high-monopsony firms adjust wage bill and employment less after monetary shocks. To interpret this, it builds a heterogeneous-firm New Keynesian model with oligopsony in which wage stickiness and market power jointly generate the muted response. The model formalizes partial passthrough and misallocation channels, and its calibration links the secular decline in monopsony to changes in the potency of monetary policy and the slope of the Phillips curve.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Empirical estimation of firm-level monetary-policy responses by monopsony intensity using administrative Census data, combined with a calibrated heterogeneous-firm New Keynesian model with oligopsonistic labor markets.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Monetary Policy, Labor Market Power, Macroeconomics</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Census Bureau — LEHD merged with Longitudinal Business Database (LBD)</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Bardóczy et al. - Monopsony Power and the Transmission of Monetary Policy.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Thesmar, Verner</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Beliefs and Stock Market Fluctuations: New Evidence from the Past Seven Decades</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>This paper builds a new seven-decade series of subjective expected equity returns (1956-2024) from an independent equity-analysis firm and uses it to reassess how beliefs move markets. Unlike the expectations of individual investors and professional forecasters, this measure is strongly positively correlated with the earnings-price ratio, responds negatively to past returns, and positively predicts future returns. Individual and professional-forecaster expectations are only weakly or negatively correlated with the new series, and disagreement between sophisticated and individual investors is associated with higher trading volume. The evidence fits a model of heterogeneous beliefs in which naive investors extrapolate past returns while sophisticated investors are close to rational. The paper offers a rare long-run window on the belief dynamics behind valuations.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>The paper motivates the need for a long, consistent measure of sophisticated investors' return expectations, which it constructs by hand from decades of an independent equity-analysis firm's forecasts. It characterizes the new series' properties—co-movement with the earnings-price ratio, mean-reverting response to past returns, and predictive power for future returns—and contrasts them with survey measures of individuals and forecasters. Finding that sophisticated and naive expectations diverge, and that their disagreement tracks trading volume, it argues a single-belief model cannot fit the facts. It then shows a heterogeneous-beliefs model, with extrapolative naive investors and near-rational sophisticated investors, rationalizes the joint patterns.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Construction and analysis of a novel long-run (1956-2024) subjective-expected-return series hand-collected from an independent equity-analysis firm, with predictive and correlation regressions against survey expectations and a heterogeneous-beliefs asset-pricing model.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Behavioral Finance, Asset Pricing, Expectations &amp; Beliefs</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Value Line Investment Survey; Robert Shiller — Investor Confidence Survey; UBS/Gallup and Livingston Survey</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Ahern</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>This paper shows that the industrial composition of a city's economy shapes its cost of municipal borrowing. In a panel of 1,177 U.S. cities from 2005 to 2022, greater sectoral concentration raises default risk and municipal bond spreads, especially where dominant industries are associated with low property values. Instrumental variables built from national sector-employment trends and regional house-price variation support a causal reading. A calibrated city-default model implies the estimated spread effect understates the gross risk from concentration, because concentration also brings agglomeration benefits that lower spreads, particularly in high-property-value cities. The paper connects local economic structure to public finance and credit risk.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>The paper reasons that a city dependent on few industries faces more concentrated economic risk, which should raise default probability and hence bond spreads, but that the effect may depend on whether those industries support high property values that anchor the tax base. It documents the concentration–spread relationship in a large city panel and shows it is stronger where dominant sectors imply low property values. To move from correlation to causation, it instruments concentration using national sector-employment trends interacted with regional house-price variation. Finally, a calibrated default model reconciles the estimates with offsetting agglomeration benefits, implying the gross risk effect is larger than the net spread effect suggests.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Panel regressions with an instrumental-variables strategy (national sector-employment trends and regional house-price variation) linking industrial concentration to municipal bond spreads, complemented by a calibrated structural model of city default.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Finance, Credit Risk, Urban &amp; Regional Economics</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>MSRB — Municipal Securities Rulemaking Board trade data; U.S. Census Bureau — LODES (LEHD Origin-Destination Employment Statistics); FHFA — House Price Index</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Clayton and Coppola - The Optimal Use of AI in Financial Regulation</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Clayton, Coppola</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>The Optimal Use of AI in Financial Regulation</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>This paper asks whether modern AI methods applied to granular portfolio-holdings data can improve macroprudential regulation, and how policymakers should use such tools. The authors build a graph-based deep learning model over security-level holdings of financial intermediaries that embeds economic priors and learns latent representations of both assets and investors from the network of positions. Applied to the near-universe of non-bank financial intermediaries (about $40 trillion), the model forecasts intermediary trading far better than existing approaches, including during crises, and has more than ten times the explanatory power for cross-sectional stress-period returns. Its learned embeddings encode economically interpretable information about fire-sale vulnerability, and the architecture is inductive enough to produce estimates even for withheld asset classes or investors. The authors then embed the empirical model in a macroprudential optimal-policy framework, addressing the Lucas critique, to show why these objects matter for welfare.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>The paper frames systemic risk measurement as a prediction problem over the network of who holds what, arguing that the structure of intermediary holdings encodes fire-sale vulnerability that standard metrics miss. It develops a graph neural network with built-in economic priors that learns asset and investor representations from holdings, then validates the model out-of-sample on trading behavior and stress-period returns against existing benchmarks. Having shown the learned objects are predictive and interpretable, it asks how a regulator should optimally use them. It closes by embedding the empirical model in an equilibrium optimal-policy framework that confronts the Lucas critique, formalizing the welfare rationale for AI-based supervision.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Design and out-of-sample evaluation of a graph-based (network) deep-learning model on security-level intermediary holdings, benchmarked against existing systemic-risk metrics, embedded within a macroprudential optimal-policy framework robust to the Lucas critique.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning in Finance, Financial Regulation, Systemic Risk</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>FactSet &amp; Morningstar — Security-level intermediary holdings</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Clayton and Coppola - The Optimal Use of AI in Financial Regulation.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Ebsim, Lian, Ma, Ottonello, Perez</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Sophisticated Borrowing Constraints and Macroeconomic Dynamics</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>This paper argues that the way debt constraints are modeled fundamentally changes their macroeconomic implications. Traditional models impose hard borrowing limits that force firms to cut borrowing and investment whenever adverse shocks bind, producing financial acceleration. The authors instead model 'sophisticated borrowing constraints' resembling real-world financial covenants, where breaching an earnings-based debt threshold transfers control rights to creditors who then act to maximize their own value rather than mechanically shrinking credit. Calibrated to micro evidence on investment and earnings around covenant violations, the model matches firm-level dynamics while, at the macro level, generating no financial acceleration because violations do not trigger indiscriminate downscaling. The result challenges a workhorse mechanism linking credit conditions to aggregate fluctuations.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>The paper contrasts textbook hard constraints, under which binding limits mechanically force deleveraging and amplify shocks, with the institutional reality of covenants, which reallocate control rather than dictate fixed borrowing ratios. It models covenant violation as a state-contingent transfer of control to creditors who choose firm policies to maximize creditor value, so tightening need not cause uniform credit cuts. The authors first show the model reproduces the empirical behavior of investment and earnings around violations at the micro level. They then embed the mechanism in a general-equilibrium setting and demonstrate that, unlike hard constraints, sophisticated constraints do not generate financial acceleration.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>A quantitative macro-finance model with state-contingent, covenant-like borrowing constraints and creditor control rights, calibrated to firm-level dynamics around covenant violations, then evaluated for its aggregate (financial-acceleration) implications.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Macro-Finance, Corporate Debt &amp; Covenants, Firm Investment</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Refinitiv LPC — DealScan; Greg Nini (Nini, Smith &amp; Sufi) — Financial covenant violation data</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Dou, Wang, Wang</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>The Cost of Intermediary Market Power for Distressed Borrowers</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>This paper measures how much lender market power raises borrowing costs for firms in financial distress, who must raise urgent financing in thin, concentrated credit markets. The authors show that distressed borrowers pay very high loan spreads even after stripping out compensation for credit risk, liquidity risk, and ordinary loan-making costs. To decompose the residual, they build and estimate a dynamic game-theoretic model of distressed lending featuring latent demand heterogeneity, endogenous lender participation, creditor blocking power, and tacit collusion sustained by repeated syndication. Lender market power explains 533 basis points of risk-adjusted spreads in debtor-in-possession (DIP) loans and 300 basis points in highly speculative loans, with roughly 140 basis points from tacit collusion in each. Because this markup reduces survival-critical liquidity by 16–20%, market power emerges as a major, previously underappreciated source of financial-distress costs.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>The argument begins by noting that distressed firms borrow in markets dominated by a few specialized lenders and by existing creditors who hold blocking power, so observed spreads may reflect market power rather than pure risk. The authors first document that DIP and highly speculative loan spreads remain large after removing risk and cost components, motivating a structural explanation. They then specify a dynamic game in which lenders choose whether to participate, exploit blocking power, and sustain tacit collusion through repeated syndication, allowing the markup to be identified and decomposed. Estimating the model on facility-level loan data, they quantify the market-power markup and trace its consequences for borrower liquidity and asset-value destruction.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Structural estimation of a dynamic game-theoretic model of distressed lending (with endogenous participation, creditor blocking power, and tacit collusion), disciplined by facility-level DIP and highly speculative loan data, used to decompose risk-adjusted spreads into market-power components.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Financial Distress &amp; Bankruptcy, Banking &amp; Lending, Market Power / Industrial Organization</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Refinitiv LPC — DealScan; LPC (Refinitiv) — LSTA/LPC Mark-to-Market Pricing Data; PACER — Public Access to Court Electronic Records; Moody's — Default and Recovery Database</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - He et al. - Homemade Foreign Trading</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>He, Wang, Zhu</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Homemade Foreign Trading</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>This paper documents how Chinese mainland insiders disguise domestic trades as foreign investment by round-tripping capital through the Stock Connect program, a practice the authors term 'homemade foreign trading.' Using cross-border holding data from all custodians in Stock Connect, they show that northbound flows predict returns and correlate with insider trading, but that this predictability decays after the 2018 Northbound Investor Identification reform introduced see-through surveillance. The decay is concentrated among less prestigious foreign custodians and cross-operating mainland custodians, precisely where insiders can most easily hide. The reform also reduces price informativeness in stocks most exposed to homemade foreign investors. The paper highlights regulatory cooperation as a key ingredient for the integrity of cross-border capital market integration.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>The paper starts from the observation that Stock Connect lets mainland capital exit and re-enter disguised as foreign 'northbound' flow, giving insiders a channel to trade on private information while appearing to be offshore investors. It argues that if such round-tripping is real, northbound flows should predict returns and track insider activity, and that a reform imposing investor-level identification should break this link by making insiders identifiable. Exploiting the 2018 Northbound Investor Identification reform as a shock to surveillance, the authors trace how return predictability and its correlation with insider trading decay afterward. They then sharpen identification by showing the effect is strongest where hiding is easiest (opaque custodians) and by documenting a decline in price informativeness for the most exposed stocks.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Event-study / difference-in-differences around the 2018 Northbound Investor Identification reform, using custodian-level cross-border holding data and return-predictability regressions, with cross-sectional heterogeneity by custodian type and stock exposure for identification.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>International Finance, Insider Trading, Market Microstructure</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>China Securities Depository and Clearing (CSDC) / Stock Connect; CSMAR — China Stock Market &amp; Accounting Research; WIND</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
           <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - He et al. - Homemade Foreign Trading.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:L21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1047,7 +1567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1148,14 +1668,18 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>China Securities Depository and Clearing (CSDC) / Stock Connect</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
+          <t>Centers for Medicare &amp; Medicaid Services (CMS)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Medicare DMEPOS claims</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Cross-border holding and order data from all custodians in China's Stock Connect (northbound), including the 2018 Northbound Investor Identification reform, used to trace round-tripping insider flows.</t>
+          <t>Supplier- (NPI-) level Medicare durable medical equipment claims used to measure market shares, entry, and exit around the competitive-bidding reform.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1166,7 +1690,7 @@
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>China; Stock Connect; custodians; cross-border holdings</t>
+          <t>Medicare; DME; claims; suppliers</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
@@ -1174,25 +1698,25 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - He et al. - Homemade Foreign Trading</t>
+          <t>Working Paper - 2026 - Diwan et al. - Competition and Fraud in Health Care</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Correia, Luck &amp; Verner (this paper)</t>
+          <t>Chen &amp; Sacerdote (this paper)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Historical bank-run database</t>
+          <t>Congressional trading records</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Newly constructed database of 3,984 bank runs on individual U.S. banks, 1863-1934, extracted from historical newspapers using large language models.</t>
+          <t>Hand-collected transactions of all U.S. members of Congress and their immediate families, 2012-2023, from periodic financial-disclosure (STOCK Act) filings.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1203,7 +1727,7 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>bank runs; historical; LLM-constructed</t>
+          <t>congressional trades; disclosures; hand-collected</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
@@ -1211,36 +1735,32 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+          <t>Working Paper - 2026 - Chen and Sacerdote - Capital in the Capitol Congressional Trades Resemble Uninformed Retail Trading</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CSMAR</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>China Stock Market &amp; Accounting Research</t>
-        </is>
-      </c>
+          <t>China Securities Depository and Clearing (CSDC) / Stock Connect</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Chinese firms' financial statements and corporate announcements used for firm characteristics and insider-trading events.</t>
+          <t>Cross-border holding and order data from all custodians in China's Stock Connect (northbound), including the 2018 Northbound Investor Identification reform, used to trace round-tripping insider flows.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>China; accounting; announcements</t>
+          <t>China; Stock Connect; custodians; cross-border holdings</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
@@ -1255,18 +1775,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FactSet &amp; Morningstar</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Security-level intermediary holdings</t>
-        </is>
-      </c>
+          <t>Consumer transaction-data provider</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Holdings data covering the universe of non-bank financial intermediaries (mutual funds, ETFs, separate accounts, etc.), ~$40 trillion, used to train the holdings-network model.</t>
+          <t>Individual account- and transaction-level banking data used to measure NSF, overdraft, late, and maintenance fees and use of alternative financial services across households.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1277,7 +1793,7 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>holdings network; non-bank intermediaries; fire sales</t>
+          <t>transaction-level; bank fees; households</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
@@ -1285,36 +1801,36 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Clayton and Coppola - The Optimal Use of AI in Financial Regulation</t>
+          <t>Working Paper - 2026 - Pagel et al. - Bank Fees and Household Financial Well-Being</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FHFA</t>
+          <t>Context Analytics</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>House Price Index</t>
+          <t>S-Score (Twitter/X sentiment)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Regional house-price data (pre-sample 1975-2004) used to build instruments and proxy property values.</t>
+          <t>Security-level social-media sentiment scores derived from the Twitter/X firehose via proprietary NLP, used to proxy retail market sentiment.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>house prices; property values</t>
+          <t>social media sentiment; retail; NLP</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
@@ -1322,36 +1838,36 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+          <t>Working Paper - 2026 - Chen and Sacerdote - Capital in the Capitol Congressional Trades Resemble Uninformed Retail Trading</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Greg Nini (Nini, Smith &amp; Sufi)</t>
+          <t>Correia, Luck &amp; Verner (this paper)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Financial covenant violation data</t>
+          <t>Historical bank-run database</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Hand-shared extended data on financial covenant violations disclosed in firms' filings, 1996 onward, used to construct micro moments around violations.</t>
+          <t>Newly constructed database of 3,984 bank runs on individual U.S. banks, 1863-1934, extracted from historical newspapers using large language models.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>covenant violations; control rights</t>
+          <t>bank runs; historical; LLM-constructed</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
@@ -1359,36 +1875,32 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics</t>
+          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Chronicling America</t>
-        </is>
-      </c>
+          <t>Crunchbase</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Large-scale archive of digitized historical U.S. newspapers, the main source for detecting and dating bank runs.</t>
+          <t>Startup and news-feed data used alongside PitchBook to identify fraud allegations.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>historical newspapers; text source</t>
+          <t>startups; news; allegations</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
@@ -1396,25 +1908,25 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+          <t>Working Paper - 2026 - Dyck et al. - Venture Fraud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>LPC (Refinitiv)</t>
+          <t>CSMAR</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>LSTA/LPC Mark-to-Market Pricing Data</t>
+          <t>China Stock Market &amp; Accounting Research</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Secondary-market loan trading/pricing data used to measure loan liquidity and pricing.</t>
+          <t>Chinese firms' financial statements and corporate announcements used for firm characteristics and insider-trading events.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1425,7 +1937,7 @@
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>secondary loan prices; liquidity</t>
+          <t>China; accounting; announcements</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
@@ -1433,36 +1945,36 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+          <t>Working Paper - 2026 - He et al. - Homemade Foreign Trading</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>DOJ / HHS-OIG</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Default and Recovery Database</t>
+          <t>Fraud enforcement records</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Nominal recovery rates aggregated by industry, used in the risk-adjustment of spreads.</t>
+          <t>Federal fraud enforcement actions - indictments, civil settlements, and program exclusions - used to identify fraudulent suppliers.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>defaults; recoveries</t>
+          <t>fraud enforcement; exclusions; indictments</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
@@ -1470,25 +1982,25 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+          <t>Working Paper - 2026 - Diwan et al. - Competition and Fraud in Health Care</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MSRB</t>
+          <t>Dyck, Fang, Hebert &amp; Xu (this paper)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Municipal Securities Rulemaking Board trade data</t>
+          <t>Venture-fraud case sample</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Secondary-market municipal bond trades used to construct city-level bond spreads.</t>
+          <t>Hand-collected sample of 614 U.S. VC-backed startups facing fraud charges (SEC, DOJ, and civil litigation) since 2000, with fraud commitment periods.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1499,7 +2011,7 @@
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>municipal bonds; spreads; secondary market</t>
+          <t>venture fraud; hand-collected; litigation</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
@@ -1507,36 +2019,36 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+          <t>Working Paper - 2026 - Dyck et al. - Venture Fraud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>OCC</t>
+          <t>FactSet &amp; Morningstar</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>National bank call reports (Annual Report to Congress)</t>
+          <t>Security-level intermediary holdings</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Balance-sheet data for national banks used to measure bank fundamentals and outcomes.</t>
+          <t>Holdings data covering the universe of non-bank financial intermediaries (mutual funds, ETFs, separate accounts, etc.), ~$40 trillion, used to train the holdings-network model.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>call reports; bank balance sheets; fundamentals</t>
+          <t>holdings network; non-bank intermediaries; fire sales</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
@@ -1544,25 +2056,25 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+          <t>Working Paper - 2026 - Clayton and Coppola - The Optimal Use of AI in Financial Regulation</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>PACER</t>
+          <t>FDIC</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Public Access to Court Electronic Records</t>
+          <t>Summary of Deposits</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>U.S. bankruptcy court records used to identify DIP financing and Chapter 11 cases.</t>
+          <t>Branch/deposit data used to determine which metropolitan areas were exposed to each bank's policy change.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1573,7 +2085,7 @@
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>bankruptcy; DIP; court records</t>
+          <t>deposits; branch exposure; MSA</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
@@ -1581,73 +2093,73 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+          <t>Working Paper - 2026 - Pagel et al. - Bank Fees and Household Financial Well-Being</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Refinitiv LPC</t>
+          <t>FDIC</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>DealScan</t>
+          <t>Historical Bank Data</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Loan-level covenant terms (e.g., debt-to-EBITDA covenants) used to identify firms subject to earnings-based constraints. Facility-level syndicated loan terms used to build the sample of debtor-in-possession and highly speculative loans.</t>
+          <t>Aggregate historical deposits and deposit interest expense used to characterize Reg Q-era bank funding.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>syndicated loans; DIP; facilities; loan covenants; debt-to-EBITDA</t>
+          <t>historical deposits; Reg Q</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers; Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics</t>
+          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Robert Shiller</t>
+          <t>Federal Reserve</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Investor Confidence Survey</t>
+          <t>FR Y-14 supervisory data</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Investor-confidence survey data used as a comparison measure of investor beliefs.</t>
+          <t>Confidential loan-level data on commercial and industrial loans at the largest U.S. banks, collected for Dodd-Frank stress testing, used to measure rate dispersion and borrower/loan characteristics.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>investor confidence; beliefs</t>
+          <t>supervisory; C&amp;I loans; bank stress test</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
@@ -1655,25 +2167,25 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+          <t>Working Paper - 2026 - Amiti et al. - Why Do Firms Pay Different Interest Rates on Their Bank Loans</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>U.S. Census Bureau</t>
+          <t>Federal Reserve</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LODES (LEHD Origin-Destination Employment Statistics)</t>
+          <t>Senior Loan Officer Opinion Survey (SLOOS)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Sector-level job counts used to measure a city's industrial concentration.</t>
+          <t>Bank lending-standards survey (back to 1964) used as a measure of credit tightening.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1684,7 +2196,7 @@
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>employment; industry concentration; LODES</t>
+          <t>lending standards; SLOOS</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
@@ -1692,36 +2204,36 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>U.S. Census Bureau</t>
+          <t>Federal Reserve Bank of Atlanta</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LEHD merged with Longitudinal Business Database (LBD)</t>
+          <t>Diary of Consumer Payment Choice (DCPC)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Confidential administrative data on establishment-level wage bill and employment used to measure local monopsony power and firm responses to monetary policy.</t>
+          <t>Consumer payment-diary data on payment-method use and shopping, used to measure sorting across merchant sectors.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>administrative; wage bill; employment; monopsony</t>
+          <t>consumer payments; diary; sorting</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
@@ -1729,25 +2241,25 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Bardóczy et al. - Monopsony Power and the Transmission of Monetary Policy</t>
+          <t>Working Paper - 2026 - Egan et al. - Who Pays for Payments</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>U.S. Census Bureau</t>
+          <t>Federal Reserve Bank of Atlanta &amp; Duke University</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Business Database (LBD)</t>
+          <t>Survey of corporate executives</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Confidential data tracking entry and exit for the universe of U.S. employers, used to estimate the debt–exit relationship.</t>
+          <t>Novel survey of nearly 750 corporate executives on AI adoption, productivity effects, and workforce plans, benchmarked to the U.S. Census industry/size distribution.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1758,7 +2270,7 @@
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>firm entry/exit; universe of employers</t>
+          <t>executive survey; AI adoption; productivity</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
@@ -1766,21 +2278,25 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Bornstein and Castillo-Martinez - Firm Exit and Financial Frictions</t>
+          <t>Working Paper - 2026 - Baslandze et al. - Artificial Intelligence, Productivity, and the Workforce Evidence from Corporate Executives</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>UBS/Gallup and Livingston Survey</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr"/>
+          <t>FHFA</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>House Price Index</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Survey measures of individual-investor and professional-forecaster return/earnings expectations used for comparison.</t>
+          <t>Regional house-price data (pre-sample 1975-2004) used to build instruments and proxy property values.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1791,7 +2307,7 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>investor surveys; forecaster expectations</t>
+          <t>house prices; property values</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
@@ -1799,32 +2315,32 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Value Line Investment Survey</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Analyst forecasts hand-collected from microfilm records (1956-2024) used to construct a long-run series of sophisticated investors' subjective expected returns.</t>
+          <t>Two proprietary datasets from Fiserv, a large U.S. merchant acquirer, on the composition and cost (interchange/settlement) of payments across merchants.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>subjective expectations; analyst forecasts; microfilm</t>
+          <t>merchant acquiring; interchange; settlement</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
@@ -1832,45 +2348,864 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+          <t>Working Paper - 2026 - Egan et al. - Who Pays for Payments</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>WIND</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr"/>
+          <t>Greg Nini (Nini, Smith &amp; Sufi)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Financial covenant violation data</t>
+        </is>
+      </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Adjusted opening prices and free-floating shares for Chinese listed stocks.</t>
+          <t>Hand-shared extended data on financial covenant violations disclosed in firms' filings, 1996 onward, used to construct micro moments around violations.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>covenant violations; control rights</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Library of Congress</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Chronicling America</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Large-scale archive of digitized historical U.S. newspapers, the main source for detecting and dating bank runs.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>historical newspapers; text source</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>LPC (Refinitiv)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>LSTA/LPC Mark-to-Market Pricing Data</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Secondary-market loan trading/pricing data used to measure loan liquidity and pricing.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>secondary loan prices; liquidity</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Default and Recovery Database</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Nominal recovery rates aggregated by industry, used in the risk-adjustment of spreads.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>defaults; recoveries</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>MSRB</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Securities Rulemaking Board trade data</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Secondary-market municipal bond trades used to construct city-level bond spreads.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>municipal bonds; spreads; secondary market</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>NBER-CES</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing Industry Database</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Industry-level prices and quantities (derived from the U.S. Census) used to test cross-industry supply effects.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>manufacturing; prices; quantities</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Nilson Report</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Industry statistics on interchange and network fees used to benchmark payment costs.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>interchange; network fees; benchmarks</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Egan et al. - Who Pays for Payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>OCC</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>National bank call reports (Annual Report to Congress)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Balance-sheet data for national banks used to measure bank fundamentals and outcomes.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>call reports; bank balance sheets; fundamentals</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>PACER</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Public Access to Court Electronic Records</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>U.S. bankruptcy court records used to identify DIP financing and Chapter 11 cases.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>bankruptcy; DIP; court records</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>PitchBook</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Venture-capital-backed startups, their founders, financing rounds, and cap-table/board structures, used to build the sample and governance variables.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>venture capital; startups; cap tables</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Dyck et al. - Venture Fraud</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Preqin</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Industry-level private-credit assets used to gauge coverage and situate the sample within the broader market.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>private credit; industry assets</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Matvos et al. - Private Credit, Balance Sheets and Financial Stability</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary private-credit data provider</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>New proprietary fund- and asset-level data covering roughly 1,300 private-credit funds and their loans (capitalization, funding, maturities, performance), covering most of the industry.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>private credit; funds; balance sheets</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Matvos et al. - Private Credit, Balance Sheets and Financial Stability</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Refinitiv LPC</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>DealScan</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Loan-level covenant terms (e.g., debt-to-EBITDA covenants) used to identify firms subject to earnings-based constraints. Facility-level syndicated loan terms used to build the sample of debtor-in-possession and highly speculative loans.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>syndicated loans; DIP; facilities; loan covenants; debt-to-EBITDA</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers; Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Robert Shiller</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Investor Confidence Survey</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Investor-confidence survey data used as a comparison measure of investor beliefs.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>investor confidence; beliefs</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P Capital IQ</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Supplementary financial data used to improve customer-capital expense measures.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>financials; customer capital</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Eisfeldt et al. - Intangible Intensity</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>SEC (WRDS SEC Analytics Suite)</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>10-K filings</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Full-text corporate 10-K filings, accessed via the WRDS SEC Analytics Suite, used to build the text-based intangible-intensity measure.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>10-K; disclosure text; NLP</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Eisfeldt et al. - Intangible Intensity</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Call Reports (via FOIA)</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Bank-level regulatory balance-sheet data obtained back to 1959 through a Freedom of Information Act request, used to measure deposits and lending contractions.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>call reports; bank lending; 1959-</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Census Bureau</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>LODES (LEHD Origin-Destination Employment Statistics)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Sector-level job counts used to measure a city's industrial concentration.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>employment; industry concentration; LODES</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Census Bureau</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>LEHD merged with Longitudinal Business Database (LBD)</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Confidential administrative data on establishment-level wage bill and employment used to measure local monopsony power and firm responses to monetary policy.</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>administrative; wage bill; employment; monopsony</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Bardóczy et al. - Monopsony Power and the Transmission of Monetary Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Census Bureau</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Longitudinal Business Database (LBD)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Confidential data tracking entry and exit for the universe of U.S. employers, used to estimate the debt–exit relationship.</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>firm entry/exit; universe of employers</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Bornstein and Castillo-Martinez - Firm Exit and Financial Frictions</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>UBS/Gallup and Livingston Survey</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Survey measures of individual-investor and professional-forecaster return/earnings expectations used for comparison.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>investor surveys; forecaster expectations</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Value Line Investment Survey</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Analyst forecasts hand-collected from microfilm records (1956-2024) used to construct a long-run series of sophisticated investors' subjective expected returns.</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>subjective expectations; analyst forecasts; microfilm</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>WIND</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Adjusted opening prices and free-floating shares for Chinese listed stocks.</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
           <t>China; prices; shares</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="H44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>Working Paper - 2026 - He et al. - Homemade Foreign Trading</t>
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Yunan Ji</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Medicare DME auction bids</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Bids submitted in Medicare's DME competitive-bidding auctions, shared by the author, used in the bidding analysis.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>auction bids; competitive bidding</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Diwan et al. - Competition and Fraud in Health Care</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I22"/>
+  <autoFilter ref="A1:I45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/knowledge_chest.xlsx
+++ b/docs/knowledge_chest.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dataset Universe" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exogenous Shocks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Papers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dataset Universe" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Exogenous Shocks" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Papers'!$A$1:$L$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dataset Universe'!$A$1:$I$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Exogenous Shocks'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Papers'!$A$1:$L$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dataset Universe'!$A$1:$I$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Exogenous Shocks'!$A$1:$E$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -520,391 +520,455 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Egan et al. - Who Pays for Payments</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
+          <t>American Economic Review Insights - 2026 - Meyer-ter-Vehn and Board - Breaking Bad News</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>American Economic Review: Insights</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Egan, Matvos, Seru, Wang, Yao</t>
+          <t>Meyer-ter-Vehn, Board</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Who Pays for Payments?</t>
+          <t>Breaking Bad News</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>This paper uses novel data on the composition and cost of payments across U.S. merchants to quantify redistribution in the payment system. Card interchange fees fund consumer rewards, and when merchants raise prices for everyone, users of low-cost methods like cash and debit cross-subsidize high-reward credit-card users at the same merchant. The authors show incidence actually depends on the joint distribution of payment choices across merchants, not the standard assumption that everyone shops at the same stores facing the same fees. Two forces shape redistribution: consumer sorting, where users of different payment methods shop at different merchants, limits cash and debit users' exposure to high interchange fees; and interchange fees vary across merchants, being lower where payment types overlap (e.g., large grocery stores) due to sector discounts and negotiations. Embedding these forces in a sufficient-statistics framework, the paper revises who ultimately bears payment-system costs.</t>
+          <t>This paper studies how information disclosure shapes social learning about a potentially harmful product. Increased transparency helps early agents avoid harm, but this may undermine learning by later agents who no longer observe harmful outcomes. Despite this conflict of interest, the authors show that full transparency is uniquely optimal for all agents when they learn only by observing neighbors' harm. They then investigate whether full transparency about harm continues to benefit everyone when agents also learn from additional, imperfect signals. The paper clarifies when disclosing bad news helps versus hinders collective learning.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>The paper reconsiders the common claim that users of low-cost payment methods subsidize high-reward credit-card users, showing this conclusion rests on assumptions that fail in the data. The standard argument is that card interchange fees fund rewards, merchants raise prices for everyone to cover the fees, and so cash and debit users cross-subsidize card users at the same store. The authors point out this implicitly assumes that consumers using different payment methods shop at the same merchants and that merchants face similar fees. Using novel data on payment composition and cost across merchants, they document two forces that overturn the simple incidence. First, consumer sorting, since users of different payment methods often shop at different merchants, which limits cash and debit users' exposure to high-interchange environments. Second, interchange fees vary across merchants, and where payment types overlap, such as large grocery stores, fees are lower due to sector discounts and private negotiations. They embed these forces in a sufficient-statistics framework that makes incidence depend on the joint distribution of payment choices across merchants rather than on a single representative store. The result is a substantially revised picture of who ultimately bears payment-system costs, in which sorting and fee heterogeneity blunt the cross-subsidy the standard view predicts.</t>
+          <t>The paper considers a setting where agents adopt a product that may be harmful and learn about its danger from others' experiences, so disclosure of harm affects social learning. It identifies a tension: making harm transparent protects early agents but can slow later agents' learning, because avoided harm generates less observable information. The authors ask whether, given this conflict, more transparency is good for everyone. When agents learn only by observing neighbors' harm, they prove full transparency is uniquely optimal for all agents, resolving the tension in favor of disclosure. They then extend the analysis to allow additional imperfect signals and examine whether full transparency about harm still benefits all agents. The paper thus delineates the conditions under which breaking bad news aids collective welfare.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>A sufficient-statistics incidence design estimated on proprietary merchant-acquirer data (payment composition and cost across merchants) plus consumer payment-diary data. The framework makes who bears payment costs depend on the joint distribution of payment choices across merchants, so the authors estimate the two forces that matter, how consumers using different payment methods sort across merchants and how interchange fees vary across merchants, and feed them into the incidence formulas. Identification of the revised incidence comes from measuring where different payment users actually shop together and the fees they face there; the units are the merchant and the consumer or payment method.</t>
+          <t>A theoretical model of social learning about a potentially harmful product, analyzing how information disclosure (transparency about harm) affects early versus later agents. The analysis derives conditions—learning only from neighbors' harm versus also from additional imperfect signals—under which full transparency is optimal for all agents. There is no external dataset.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Payments, Household Finance, Industrial Organization</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Fiserv; Federal Reserve Bank of Atlanta — Diary of Consumer Payment Choice (DCPC); Nilson Report</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>Information Economics, Social Learning, Financial Theory</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Theoretical model; no datasets.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/American Economic Review Insights - 2026 - Meyer-ter-Vehn and Board - Breaking Bad News.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
+          <t>American Economic Review - 2026 - Hankins et al. - Consumer Credit and the Incidence of Tariffs Evidence from the Auto Industry</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>American Economic Review</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Drechsler, Savov, Schnabl</t>
+          <t>Hankins, Momeni, Sovich</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Credit Crunches and the Great Stagflation</t>
+          <t>Consumer Credit and the Incidence of Tariffs: Evidence from the Auto Industry</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>This paper argues that severe banking-system credit crunches helped cause the Great Stagflation of the 1970s, working through Regulation Q, which capped deposit rates. Under Reg Q, Fed tightening triggered large deposit outflows that forced banks to contract lending, and these credit crunches line up closely with stagflation over time. Adding Reg Q to a standard model where firms finance working capital with bank loans, the authors show binding caps make working capital costlier, leading firms to raise prices and cut output. This yields an augmented Phillips curve in which monetary tightening reduces aggregate supply as well as demand, with effects increasing in credit-crunch severity, external-finance dependence, and working-capital intensity. Cross-industry tests confirm that more exposed manufacturing industries raised prices and cut output relative to others.</t>
+          <t>This paper examines how tariffs affecting the auto industry pass through to consumers via the credit market. Using tariffs as a shock to vehicle costs, the authors study effects on auto loans and purchases, showing how much of the tariff burden falls on consumers through financing. The setting isolates the incidence of trade policy at the point of consumer borrowing. The results reveal that consumer credit is an important channel through which tariff costs reach households. The paper connects trade policy to household finance in a concrete, high-volume market.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>The paper advances a novel explanation for the 1970s Great Stagflation: severe credit crunches in the banking system, operating through Regulation Q, which capped the interest rates banks could pay on deposits. The mechanism is that when the Fed tightened, market rates rose above the Reg Q ceilings, triggering large deposit outflows that forced banks to contract lending. The authors first show these credit crunches line up closely with stagflation in the time series, motivating a causal role. To explain how a credit crunch produces stagflation, they add Reg Q to a standard model in which firms need bank loans to finance working capital, so that when credit contracts, working capital becomes more expensive, leading firms to raise prices and cut output simultaneously. This yields an augmented Phillips curve in which monetary tightening reduces aggregate supply, not just demand, with the supply effect increasing in the severity of the credit crunch, firms' dependence on external finance, and their working-capital intensity. The paper then tests these three cross-sectional predictions across manufacturing industries and finds that more exposed industries raised prices and cut output relative to others, supporting the claim that under severe financial frictions monetary policy has a supply-side channel that can generate stagflation.</t>
+          <t>The paper asks who ultimately bears the cost of tariffs, focusing on a channel usually overlooked: consumer credit. It uses tariffs affecting the auto industry as a shock that raises the cost of vehicles, and studies how this propagates to auto loans and purchases. Because cars are typically financed, the credit market is where much of the tariff incidence is realized for households. The authors trace how loan terms, borrowing, and purchases respond to the tariff-driven cost increase. Finding meaningful pass-through to consumers through financing, they quantify the household incidence of the tariffs. The paper concludes that consumer credit is a key conduit through which trade-policy costs reach households, enriching the standard analysis of tariff incidence.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>A model paired with cross-industry tests. The authors add Regulation Q deposit-rate ceilings to a working-capital model, deriving an augmented Phillips curve in which credit contractions shift aggregate supply, and generating predictions that grow with credit-crunch severity, external-finance dependence, and working-capital intensity. Empirically, they first show that Reg Q-driven credit crunches (deposit outflows when Fed tightening pushes rates above the ceilings) track stagflation over time, then test the cross-sectional predictions across manufacturing industries by exposure. Bank-level regulatory data back to 1959 measure the deposit outflows and lending contractions; the industry-by-time comparison provides the identifying variation.</t>
+          <t>A quasi-experimental design using tariffs affecting the auto industry as a shock to vehicle costs, tracing effects on auto loans, borrowing, and purchases to measure the consumer incidence of tariffs through the credit market. The unit of analysis is the loan/consumer; identification comes from the tariff event and cross-sectional exposure.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Monetary Economics, Banking, Macro-Finance</t>
+          <t>Trade Policy, Household &amp; Consumer Credit, Industrial Organization</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>U.S. Call Reports (via FOIA); NBER-CES — Manufacturing Industry Database; FDIC — Historical Bank Data; Federal Reserve — Senior Loan Officer Opinion Survey (SLOOS)</t>
+          <t>Auto loan / consumer credit data; Vehicle tariff exposure data</t>
         </is>
       </c>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/American Economic Review - 2026 - Hankins et al. - Consumer Credit and the Incidence of Tariffs Evidence from the Auto Industry.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Chen and Sacerdote - Capital in the Capitol Congressional Trades Resemble Uninformed Retail Trading</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n"/>
+          <t>American Economic Review - 2026 - Gertler et al. - Temporary Layoffs, Loss-of-Recall, and Cyclical Unemployment Dynamics</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>American Economic Review</t>
+        </is>
+      </c>
       <c r="C4" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Chen, Sacerdote</t>
+          <t>Gertler, Huckfeldt, Trigari</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Capital in the Capitol: Congressional Trades Resemble Uninformed Retail Trading</t>
+          <t>Temporary Layoffs, Loss-of-Recall, and Cyclical Unemployment Dynamics</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>This paper asks whether members of Congress exploit informational advantages in their personal stock trading, using a new hand-collected dataset of all U.S. legislators' and their families' trades from 2012 to 2023. After the STOCK Act, legislators' portfolios on average underperform or merely match market benchmarks. To explain this mediocre performance, the authors show legislators' positions track financial professionals' recommendations and that their trade timing reflects prevailing market sentiment - estimated from retail investors' social-media posts - rather than anticipating price moves. Congressional trading thus looks like public-signal-following and resembles uninformed retail behavior. The paper pushes back on the view that legislators systematically trade on private information.</t>
+          <t>This paper revisits the role of temporary layoffs in the business cycle. While recall hiring from temporary layoff can stabilize employment, the authors quantify an important countervailing, destabilizing force—'loss-of-recall'—whereby workers on temporary layoff end up losing their jobs permanently. They develop a quantitative model with endogenous flows across employment, temporary-layoff unemployment, and jobless unemployment. The model matches both pre- and post-pandemic unemployment dynamics, including the contractionary role of loss-of-recall. The paper shows temporary layoffs are not purely stabilizing and that loss-of-recall shapes cyclical unemployment.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>The paper revisits whether members of Congress exploit informational advantages in their personal trading, noting prior studies relied on limited samples and offered little on mechanisms. It first builds a comprehensive, hand-collected dataset of all legislators' and their families' trades from 2012-2023, then evaluates portfolio performance against multiple benchmarks, finding that after the STOCK Act legislators on average underperform or merely match the market. The interesting question becomes why performance is mediocre, and the paper tests two possibilities about how legislators actually trade. It shows their positions track the recommendations of financial professionals, suggesting they follow public expert signals rather than private information. It then shows their trade timing aligns with prevailing market sentiment, estimated from retail investors' social-media posts, rather than anticipating future price changes, indicating they buy and sell with the crowd. Together these results imply that legislators' observable trading behavior resembles uninformed retail trading, following public signals and sentiment, which reconciles the lack of outperformance with the popular perception of informational advantage and pushes back on the view that congressional trading systematically exploits inside information.</t>
+          <t>The paper starts from the view that temporary layoffs can stabilize the labor market because laid-off workers are often recalled, dampening cyclical swings. It challenges this by highlighting 'loss-of-recall,' where workers expecting recall instead become permanently unemployed, which is destabilizing and countercyclical. To weigh these opposing forces, the authors build a quantitative model with endogenous worker flows among employment, temporary-layoff unemployment, and jobless unemployment. They discipline the model with data on these flows and show it reproduces unemployment dynamics both before and during the pandemic. The model reveals that loss-of-recall plays a contractionary role that offsets the stabilizing effect of recall hiring. The paper concludes that accounting for loss-of-recall is essential for understanding cyclical unemployment.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>A performance-evaluation-plus-mechanism design on a hand-collected record of congressional and family trades (2012-2023), a period defined by the STOCK Act disclosure regime. Portfolio performance is measured with event-study and calendar-time methods against several benchmarks to test for out- or under-performance. Mechanism tests then relate legislators' trades to analyst recommendations and to a social-media sentiment measure, examining whether their timing follows public signals rather than anticipating price moves. The unit of analysis is the trade and legislator.</t>
+          <t>A quantitative macro-labor model with endogenous flows across employment, temporary-layoff unemployment, and jobless unemployment, calibrated to worker-flow data (e.g., from the Current Population Survey). The model is used to quantify the stabilizing role of recall versus the destabilizing 'loss-of-recall' and to match pre- and post-pandemic unemployment dynamics. The unit of analysis is the aggregate labor market; identification comes from matching flow moments.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Political Economy, Informed Trading, Behavioral Finance</t>
+          <t>Macroeconomics, Labor Markets, Business Cycles</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Chen &amp; Sacerdote (this paper) — Congressional trading records; Context Analytics — S-Score (Twitter/X sentiment)</t>
+          <t>Current Population Survey (CPS)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/American Economic Review - 2026 - Gertler et al. - Temporary Layoffs, Loss-of-Recall, and Cyclical Unemployment Dynamics.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Pagel et al. - Bank Fees and Household Financial Well-Being</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n"/>
+          <t>Review of Financial Studies - 2026 - Filipović and Wagner - The Intangibles Song in Takeover Announcements Good Tempo, Hollow Tune</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Review of Financial Studies</t>
+        </is>
+      </c>
       <c r="C5" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Pagel, Sridhar, Williams</t>
+          <t>Filipović, Wagner</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Bank Fees and Household Financial Well-Being</t>
+          <t>The Intangibles Song in Takeover Announcements: Good Tempo, Hollow Tune</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>This paper studies 2017-2022 policy changes at large U.S. banks that eliminated non-sufficient-funds (NSF) fees and relaxed overdraft policies, using individual transaction-level data. Eliminating NSF fees immediately reduced NSF charges across the income distribution, as expected. Relaxing overdraft policies, however, reduced overdraft fees only for wealthier (higher-income, higher-liquidity) households, and only they saw subsequent declines in late fees, interest, maintenance fees, and use of alternatives like payday loans. The authors conclude the changes were not substantial enough to meaningfully relieve financial stress for the most vulnerable households. Methodologically, the multi-treatment, varying-intensity setting motivates a new stacked event-study estimator related to de Chaisemartin et al. (2024) to handle staggered-DiD biases.</t>
+          <t>This paper develops a word list of intangibles and applies it to takeover announcements. One standard deviation more intangible-related language ('intangibles talk') lowers the acquirer's announcement return by 0.53 percentage points and predicts worse operating performance. Yet bidder managers appear to believe in these deals, as shown by their insider trades, payment choices, and higher completion probabilities and speed. The authors conclude that takeover-announcement texts reveal important information about hard-to-measure aspects of deal quality. The paper shows that how firms talk about intangibles in deal announcements is informative—often negatively—about deal outcomes.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>The paper studies whether widely publicized reductions in bank fees actually improved household financial well-being, exploiting 2017-2022 policy changes at large U.S. banks that eliminated non-sufficient-funds fees and relaxed overdraft policies. Using individual transaction-level data, it first confirms the mechanical effect, since eliminating NSF fees immediately lowered NSF charges across the income distribution. The more subtle question is distributional, namely who benefited from the overdraft relaxation, and here the paper finds the gains were concentrated among wealthier households (higher income and liquidity), who alone experienced overdraft-fee reductions and, subsequently, declines in late fees, interest payments, maintenance fees, and use of alternatives like payday loans. Vulnerable households, by contrast, saw little relief, implying the policy changes were not substantial enough to reduce their financial stress. Methodologically, the setting features multiple treatments with varying intensities, which standard staggered difference-in-differences estimators handle poorly, so the paper motivates and implements a new stacked event-study estimator related to recent econometric work. The argument thus connects a seemingly consumer-friendly reform to a distributional outcome, benefits accruing to those least in need, while contributing an estimation approach suited to its complicated treatment structure.</t>
+          <t>The paper begins from the difficulty of assessing deal quality when much of the rationale for a takeover rests on hard-to-measure intangibles. It proposes measuring 'intangibles talk' by building a word list of intangibles and applying it to the text of takeover announcements. The authors find that more intangibles language is associated with lower acquirer announcement returns and predicts worse subsequent operating performance, suggesting such talk often signals weaker deals. Interestingly, bidder managers seem to genuinely believe in these deals, as revealed by their insider trading, choice of payment, and the higher probability and speed of completion. This gap between market skepticism and managerial conviction is itself informative. The paper concludes that announcement texts, and intangibles language in particular, carry real information about deal quality that markets partly read.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>A stacked event-study (staggered difference-in-differences) design exploiting a wave of policy changes at large banks between 2017 and 2022 that eliminated NSF fees and relaxed overdraft terms. Because these changes hit different banks at different times and with different intensity, which trips up conventional staggered-DiD estimators, the authors develop and apply a new stacked estimator (related to de Chaisemartin et al., 2024). They estimate effects separately across the income and liquidity distribution to recover who actually benefited, using individual transaction-level data. The unit of analysis is the household or account over time.</t>
+          <t>A text-as-data design that builds an intangibles word list and applies it to takeover-announcement texts, relating 'intangibles talk' to acquirer announcement returns and future operating performance. Managerial belief is examined through insider trades, payment choices, and completion probability/speed. The unit of analysis is the deal/acquirer; identification is cross-sectional using textual intensity.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Household Finance, Banking, Consumer Protection</t>
+          <t>Mergers &amp; Acquisitions, Text-as-Data, Intangibles</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Consumer transaction-data provider; FDIC — Summary of Deposits</t>
+          <t>Takeover announcement texts (intangibles word list); Insider trading filings (Form 4)</t>
         </is>
       </c>
       <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Review of Financial Studies - 2026 - Filipović and Wagner - The Intangibles Song in Takeover Announcements Good Tempo, Hollow Tune.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Matvos et al. - Private Credit, Balance Sheets and Financial Stability</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n"/>
+          <t>Review of Financial Studies - 2026 - Burkart et al. - The Structure of Leveraged Buyouts and the Free-Rider Problem</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Review of Financial Studies</t>
+        </is>
+      </c>
       <c r="C6" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Matvos, Piskorski, Seru</t>
+          <t>Burkart, Lee, Petri</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Private Credit, Balance Sheets and Financial Stability</t>
+          <t>The Structure of Leveraged Buyouts and the Free-Rider Problem</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>This paper uses new, comprehensive fund- and asset-level data covering most of the private-credit industry to assess its balance sheets and financial-stability implications. Private-credit funds are highly capitalized, with equity typically 65-80% of assets - more than six times the capitalization of U.S. banks - and use only moderate debt, largely bank credit lines for liquidity management. Fund lives of 10-12 years exceed the shorter maturities of underlying loans, implying little maturity mismatch, unlike banks that fund long-term assets with short-term callable deposits. Portfolios are diversified across industries, geographies, and strategies, and performance shows positive average net returns with losses borne mainly by equity. The authors conclude that, as currently structured, private-credit funds are conservatively built and unlikely to pose bank-like systemic risks.</t>
+          <t>This paper studies the structure of public-firm buyouts in a model featuring both the Berle-Means problem (weak incentives) and the Grossman-Hart problem (shareholder holdout/free-riding). The authors show that bootstrapping, debt in excess of funding needs, and upfront fees to bidders are socially optimal and increase buyout premiums. These elements make LBO financing akin to a 'management contract' arranged by an outside manager who receives cash and incentives to run the firm, funded by excess debt imposed on the target. The model also rationalizes why private-equity firms collect fees from their equity partnerships. The paper offers a unified explanation for common but puzzling LBO financing features.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Debate over whether the fast-growing private-credit industry poses bank-like systemic risk has been hampered by limited data, so the paper brings comprehensive fund- and asset-level data to bear on how these funds are actually financed. It documents that private-credit funds are highly capitalized, with equity typically 65-80% of assets, more than six times banks' roughly 10%, and that their debt use is moderate and mostly bank credit lines for liquidity management rather than leverage. It then examines maturity structure and finds fund lives of 10-12 years exceed the maturities of the underlying loans, implying little maturity mismatch, in sharp contrast to banks that fund long-term assets with short-term callable deposits. Turning to portfolio risk, it shows holdings are diversified across industries, geographies, and strategies, limiting exposure to correlated shocks. On performance, it finds positive average net returns with limited downside to creditors because equity investors absorb losses first. Assembling these facts, the paper argues that as currently structured, private-credit funds are conservatively built and unlikely to generate the runnable, mismatch-driven fragility that makes banks systemically risky, while noting that this conclusion is conditional on current balance-sheet configurations.</t>
+          <t>The paper starts from two classic frictions in taking a public firm private: shareholders lack incentives to monitor (Berle-Means) and can hold out to free-ride on a bidder's value creation (Grossman-Hart). It asks whether the peculiar financing structures seen in leveraged buyouts—bootstrapping, debt beyond funding needs, and upfront fees to bidders—can be understood as solutions to these frictions. Building a model of buyouts, it shows these features are socially optimal and raise premiums, because they help overcome holdout and align incentives. The authors reinterpret LBO financing as effectively a management contract, where an outside manager receives cash and incentives to run the firm, funded by excess debt loaded onto the target. The model further explains why PE firms extract fees from their equity partnerships. The paper concludes that seemingly extractive LBO features can be efficiency-enhancing responses to free-riding.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>A descriptive, comparative design using new proprietary data on roughly 1,300 private-credit funds and their loans, benchmarked against U.S. banks' regulatory data. The authors characterize how these funds are capitalized and funded, their maturity structure, portfolio diversification, and loss-bearing, and contrast each dimension with the analogous bank figures. The financial-stability conclusions follow from the documented balance-sheet structure rather than from a causal estimate; the units of analysis are the fund and the underlying loan.</t>
+          <t>A theoretical model of public-firm leveraged buyouts incorporating the Berle-Means (incentive) and Grossman-Hart (holdout/free-rider) problems, used to show that bootstrapping, excess debt, and upfront bidder fees are socially optimal and raise premiums. There is no external dataset; the analysis is analytical and reinterprets LBO financing as a management contract.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Private Credit, Financial Stability, Banking</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Proprietary private-credit data provider; Preqin</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>Private Equity &amp; Buyouts, Corporate Governance, Financial Theory</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Theoretical model; no datasets.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Review of Financial Studies - 2026 - Burkart et al. - The Structure of Leveraged Buyouts and the Free-Rider Problem.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Baslandze et al. - Artificial Intelligence, Productivity, and the Workforce Evidence from Corporate Executives</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n"/>
+          <t>Review of Financial Studies - 2026 - Mayordomo et al. - The Impact of Bank Consolidation on Credit Supply and Performance</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Review of Financial Studies</t>
+        </is>
+      </c>
       <c r="C7" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Baslandze, Edwards, Graham, McClure, Meyer, Sparks, Waddell, Weitz</t>
+          <t>Mayordomo, Pavanini, Tarantino</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Productivity, and the Workforce: Evidence from Corporate Executives</t>
+          <t>The Impact of Bank Consolidation on Credit Supply and Performance</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>This paper uses a novel survey of nearly 750 corporate executives to study how artificial intelligence is affecting productivity and the workforce. Adoption is highly heterogeneous: more than half of firms have already invested, though many smaller firms are just starting. Labor-productivity gains are positive, vary by sector, are expected to strengthen in 2026, and are concentrated in high-skill services and finance; they reflect higher revenue-based total factor productivity through innovation and demand channels rather than capital deepening. The authors document a 'productivity paradox' in which perceived gains exceed measured gains, likely due to delayed revenue realization. In labor markets they find little near-term aggregate employment decline, though large firms anticipate AI-driven reductions while smaller firms expect modest gains, alongside compositional labor reallocation.</t>
+          <t>This paper studies how bank mergers affect credit supply and bank performance, combining quasi-experimental evidence with a structural model. Reduced-form analysis shows merged banks restrict credit supply and set higher interest rates, but also reject fewer applicants and report fewer nonperforming loans. To interpret these offsetting effects, the authors estimate a structural model in which banks set both interest rates and lending standards. They find that despite relaxing lending standards, merged banks' credit performance improved because of a significant drop in screening costs. The paper shows that consolidation can raise prices yet improve screening efficiency.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Firm-level effects of AI are hard to observe in standard datasets, so the paper gathers direct evidence through a novel survey of nearly 750 corporate executives about adoption, productivity, and workforce plans. It first documents wide heterogeneity in adoption, since over half of firms have already invested while many smaller firms are only beginning, establishing that AI diffusion is uneven. It then characterizes productivity effects, which are positive, vary across sectors, are expected to strengthen going forward, and are largest in high-skill services and finance. Digging into the source of these gains, the paper argues they are not primarily due to capital deepening but reflect higher revenue-based total factor productivity operating through innovation- and demand-oriented channels. It surfaces a 'productivity paradox' in which perceived gains exceed measured gains, interpreting the gap as a lag between AI adoption and the realization of revenue. Turning to labor, it finds little evidence of near-term aggregate employment decline, but a divergence in expectations, since large firms anticipate AI-driven workforce reductions while smaller firms expect modest gains, alongside compositional reallocation of labor within and across firms. The narrative thus links where AI is adopted to how and when its productivity shows up, and to who gains or loses in the labor market.</t>
+          <t>The paper examines a central policy question—whether bank consolidation helps or harms borrowers—that is hard to answer because mergers change both prices and lending standards at once. It first uses a quasi-experimental design around bank mergers to document a mixed pattern: merged banks lend less and charge more, yet reject fewer applicants and have fewer nonperforming loans. Because these facts pull in different directions, a purely reduced-form reading is ambiguous. The authors therefore build a structural model in which banks jointly choose interest rates and lending standards, allowing them to separate pricing from screening. Estimating the model, they find merged banks relaxed standards but nonetheless improved credit performance thanks to lower screening costs. The paper concludes that consolidation's welfare effects hinge on efficiency gains in screening, not just on prices.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>A survey-based, descriptive design. A new survey of nearly 750 corporate executives measures AI adoption, its perceived and measured productivity effects, and workforce expectations, with responses weighted to match the U.S. Census industry and size distribution. The analysis documents how adoption and productivity effects vary across sectors and firm sizes, separates productivity gains coming from capital deepening versus revenue-based TFP, and quantifies the gap between perceived and measured gains. Results are cross-sectional patterns rather than causal estimates; the unit of analysis is the firm or executive respondent.</t>
+          <t>A two-part design pairing a quasi-experimental analysis of bank mergers with a structural model of bank credit in which banks set interest rates and lending standards. The reduced form compares merged and non-merged banks on credit supply, rates, rejections, and nonperforming loans; the structural model identifies screening costs and disentangles pricing from standards. The unit of analysis is the bank/loan, using a credit register.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Economics of AI, Productivity, Labor Economics</t>
+          <t>Banking, Credit Markets, Industrial Organization</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Atlanta &amp; Duke University — Survey of corporate executives</t>
+          <t>Banco de España — Spanish Credit Register (CIRBE)</t>
         </is>
       </c>
       <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Review of Financial Studies - 2026 - Mayordomo et al. - The Impact of Bank Consolidation on Credit Supply and Performance.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Eisfeldt et al. - Intangible Intensity</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n"/>
+          <t>Review of Financial Studies - 2026 - Dávila and Parlatore - Identifying Price Informativeness</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Review of Financial Studies</t>
+        </is>
+      </c>
       <c r="C8" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Eisfeldt, Hartman-Glaser, Kim, Lee</t>
+          <t>Dávila, Parlatore</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Intangible Intensity</t>
+          <t>Identifying Price Informativeness</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>This paper builds a text-based measure of firms' intangible investment intensity from 10-K filings and introduces a general 'semantic theme scoring' (STS) methodology. The approach further decomposes disclosure text into knowledge, customer, and organization capital. High-intangible-intensity firms are smaller, younger, and invest heavily in R&amp;D and human capital, and the three subcomponents map to distinct firm types - knowledge-intensive (R&amp;D-driven, high valuation, skilled labor), customer-intensive (mature, profitable, commercial), and organization-intensive (large, asset-heavy incumbents). The authors show managerial expenditure descriptions carry informative signals about intangible capital that complement financial statements. The paper offers both a new measure and a reusable NLP methodology for capturing corporate intangibles.</t>
+          <t>This paper shows how to identify and estimate price informativeness, a necessary step in testing theories of information aggregation. Starting from a pricing equation and a stochastic process for payoffs, the authors derive how to recover relative price informativeness from regressions of asset-price changes on payoff changes. Applying the method, they estimate stock-specific informativeness measures for U.S. stocks. In the cross-section, large stocks with high turnover, idiosyncratic volatility, institutional ownership, and analyst coverage are more informative. The paper provides a tractable, theory-grounded way to measure how much prices reveal about fundamentals.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Because accounting statements poorly capture intangible capital, the paper turns to the language firms use to describe their spending and builds a text-based measure of intangible investment intensity from 10-K filings, introducing a general 'semantic theme scoring' methodology along the way. It further decomposes the disclosure text into three components, knowledge, customer, and organization capital, arguing these correspond to economically distinct kinds of intangible investment. It then validates the measure by relating it to firm characteristics, showing high-intangible firms are smaller, younger, and invest heavily in R&amp;D and human capital, consistent with what intangible intensity should proxy. The decomposition is shown to map cleanly onto distinct firm types, where knowledge-intensive firms are R&amp;D-driven with high valuations and skilled labor, customer-intensive firms are mature, profitable, and commercially oriented, and organization-intensive firms are large, asset-heavy incumbents, demonstrating the subcomponents carry different information. The broader argument is that managerial expenditure descriptions contain informative signals about intangible capital stocks that complement, rather than duplicate, financial-statement data, opening a path to measuring where firms sit in the intangible lifecycle. The methodological contribution, semantic theme scoring, is offered as a reusable tool for extracting economic constructs from disclosure text.</t>
+          <t>The paper addresses a gap between theories of information aggregation, which hinge on how informative prices are, and the empirical difficulty of measuring price informativeness. It begins from a general pricing equation and an assumed stochastic process for payoffs, and shows analytically how informativeness maps into the relationship between price changes and payoff changes. This yields an identification result: informativeness can be recovered from regressions of asset-price changes on changes in fundamentals. The authors implement this to estimate a panel of stock-specific informativeness measures for U.S. stocks. They then characterize the cross-section, finding informativeness rises with size, turnover, idiosyncratic volatility, institutional ownership, and analyst coverage. The paper concludes by offering the method as a general tool for measuring and testing price informativeness.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>A text-as-data measurement exercise. The authors apply a new 'semantic theme scoring' method to firms' 10-K filings to build a measure of intangible-investment intensity and to split it into knowledge, customer, and organization capital. They validate the measure cross-sectionally by relating it and its three components to firm size, age, R&amp;D, valuation, profitability, and workforce skill, showing the constructs behave as expected and that the components pick out distinct firm types. The unit of analysis is the firm-year, with filings as the raw input.</t>
+          <t>A methodological/econometric contribution deriving identification of price informativeness from a pricing equation and payoff process, then estimating stock-specific informativeness for U.S. stocks via regressions of price changes on payoff changes. The estimates are characterized in the cross-section; the unit of analysis is the stock over time.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Intangible Capital, Text-as-Data / NLP, Corporate Finance</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>SEC (WRDS SEC Analytics Suite) — 10-K filings; S&amp;P Capital IQ</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>Market Efficiency &amp; Information, Asset Pricing, Econometric Methods</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Estimated from standard U.S. stock price/payoff data; no distinctive datasets.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Review of Financial Studies - 2026 - Dávila and Parlatore - Identifying Price Informativeness.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Amiti et al. - Why Do Firms Pay Different Interest Rates on Their Bank Loans</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n"/>
+          <t>Review of Financial Studies - 2026 - Zhong and Zhou - Dynamic Coordination and Bankruptcy Regulations</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Review of Financial Studies</t>
+        </is>
+      </c>
       <c r="C9" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Amiti, Kashyap, Kovner, Weinstein</t>
+          <t>Zhong, Zhou</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Why Do Firms Pay Different Interest Rates on Their Bank Loans?</t>
+          <t>Dynamic Coordination and Bankruptcy Regulations</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>This paper documents large dispersion in interest rates on similar commercial and industrial loans using confidential supervisory data on the largest U.S. banks, and argues the spread is not explained by risk. The authors rationalize the dispersion with a search-cost model in which borrowers pay to solicit competing quotes. Estimated search costs are highest for smaller and riskier borrowers and lowest for public firms, matching predictable differences in screening and monitoring costs. The search costs are economically large: over a third of firms behave as if they never comparison-shop, half appear to obtain only two quotes, and the rest search widely. The paper interprets loan-rate dispersion as evidence of substantial search frictions in credit markets rather than pure risk pricing.</t>
+          <t>This paper studies how bankruptcy regulations that restrict creditors' ability to exit a distressed firm affect coordination among creditors. Such ex post restrictions can protect coordination once distress hits, but may harm creditors' ex ante incentives to stay invested, worsening outcomes. The authors build a dynamic coordination model to show how this tension shapes creditor runs, bankruptcy filings, and the design of regulation. A striking result is that filing for bankruptcy early, preserving more assets for latecomers, can prolong firm life, and that regulators' clawbacks on pre-bankruptcy repayments can dominate firms' commitment to early filing. The paper derives implications for automatic stay and avoidance provisions.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>The paper documents a puzzle in confidential supervisory data: observably similar commercial-and-industrial borrowers pay markedly different interest rates, and this dispersion does not appear attributable to differences in credit risk. It proposes that the residual dispersion reflects search frictions, since firms must expend costly effort to solicit competing quotes and those that search less pay more. To formalize this, the authors adopt a search-cost model in which each borrower trades off the cost of obtaining another quote against the expected rate savings, so equilibrium rates depend on borrower-specific search costs. The model predicts that search costs should be systematically higher for borrowers who are more expensive to screen and monitor, namely smaller and riskier firms, and lower for transparent public firms. Estimating the model on the loan data, they recover these search costs and find them large and patterned exactly as predicted. The estimates also imply striking behavior, since a substantial share of firms act as if they never comparison-shop, about half appear to obtain only two quotes, and the remainder search widely. The paper thus reinterprets loan-rate dispersion not as mispriced risk but as the footprint of costly search, with implications for competition and borrower welfare in bank lending.</t>
+          <t>The paper starts from the classic coordination problem among creditors of a distressed firm, where each creditor may 'run' by exiting, hastening the firm's collapse. It observes that bankruptcy regulations often restrict exit ex post to preserve value, but points out this changes creditors' ex ante incentives to remain invested in the first place. Building a dynamic coordination model, it traces how the anticipation of exit restrictions feeds back into creditor runs and the timing of bankruptcy filings. The model yields the counterintuitive result that filing early, which conserves assets for later creditors, can extend firm life by improving coordination. It further shows that regulators using clawbacks on pre-bankruptcy repayments can achieve better outcomes than relying on firms to commit to early filing. The paper then draws out design implications for automatic stay and avoidance rules.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>A structural estimation of a borrower search-cost model on confidential loan-level supervisory data. After showing that risk cannot explain why similar borrowers pay different C&amp;I loan rates, the authors specify a model in which each firm decides how many competing quotes to gather, trading the cost of searching against the rate savings. Estimating the model recovers the distribution of search costs across borrower types, by size, risk, and whether the firm is public. Identification comes from how rate dispersion varies with these observable borrower characteristics under the model's structure; the unit of observation is the loan and borrower.</t>
+          <t>A dynamic coordination (theoretical) model of creditors deciding whether to remain invested in or exit a distressed firm, used to analyze creditor runs, the timing of bankruptcy filings, and the design of bankruptcy regulations. There is no external dataset; results are analytical, with implications derived for automatic stay, clawbacks, and avoidance provisions.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Banking, Credit Markets, Search Frictions</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Federal Reserve — FR Y-14 supervisory data</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>Bankruptcy &amp; Restructuring, Coordination &amp; Contract Theory, Financial Regulation</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Theoretical model; no datasets.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Review of Financial Studies - 2026 - Zhong and Zhou - Dynamic Coordination and Bankruptcy Regulations.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dyck et al. - Venture Fraud</t>
+          <t>Working Paper - 2026 - Da et al. - Presidential Cycles in PEAD</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -913,46 +977,50 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Dyck, Fang, Hebert, Xu</t>
+          <t>Da, Wang, Zeng</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Venture Fraud</t>
+          <t>Presidential Cycles in PEAD</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>This paper assembles the first comprehensive sample of venture fraud - 614 U.S. venture-capital-backed startups founded since 2000 that faced fraud allegations - and studies its governance roots. Within a high-detection subsample of newly public firms, VC-backed firms are 54% more likely to face fraud charges than comparable non-VC-backed firms. Fraud is more likely where founders hold stronger control rights, more convex cash-flow rights, more investors, and more non-traditional investors, with founder-controlled boards 88% more likely to commit fraud than VC- or shared-control boards. Governance features predict fraud far better than founder characteristics, and hot funding conditions at the first round - which weaken governance - forecast later fraud. The paper reframes venture fraud as substantially a product of governance structures rather than individual bad actors.</t>
+          <t>This paper documents that post-earnings announcement drift (PEAD) follows presidential cycles: it earns about 4.1% per year during Democratic presidencies but rises to 14.9% during Republican presidencies. Survey evidence indicates greater investor underreaction to earnings news under Republican presidents. The authors argue the tax component of earnings is more volatile during Republican periods, implying larger tax-policy uncertainty that amplifies information uncertainty and investor underreaction. Consistent with this, firms reference Republican tax laws more frequently in filings. The paper links political cycles and tax-policy uncertainty to a classic asset-pricing anomaly.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>The paper begins from a measurement gap, since there has been no comprehensive record of fraud among venture-backed startups, and closes it by hand-collecting a large sample of venture-fraud cases. It then asks whether venture capital is associated with more fraud, and finds that within a high-detection subsample of newly public firms, VC-backed firms are substantially more likely to face fraud charges than comparable non-VC-backed firms, a design meant to hold detection roughly constant. The core question is why, and the paper focuses on governance rather than the personal traits of founders. It argues that two features that have grown over time, founder-friendly control structures and complex cap tables with many and non-traditional investors, weaken the monitoring that would otherwise deter fraud. Using a panel prediction model, it shows fraud is more likely when founders have stronger control rights, more convex cash-flow rights, and when there are more and less-traditional investors, with founder-controlled boards far more fraud-prone than VC- or shared-control boards even within the same firm. It further shows that hot funding conditions at the initial round, which erode investors' governance leverage, predict later fraud, and that governance variables dominate founder characteristics in predicting fraud, implying venture fraud is largely a governance phenomenon that ex-ante contract design and market conditions help produce.</t>
+          <t>The paper starts from the well-known PEAD anomaly—prices drift in the direction of earnings surprises—and asks whether its strength varies with the political cycle. Documenting that PEAD is much larger under Republican than Democratic presidents, it seeks a mechanism rather than treating the pattern as coincidence. It proposes that tax-policy uncertainty, which affects the tax component of earnings, is greater during Republican periods, making earnings news harder to interpret and amplifying underreaction. Survey evidence of stronger underreaction under Republican presidents supports the behavioral channel. Showing that the tax component of earnings is more volatile and that firms reference Republican tax laws more often reinforces the tax-uncertainty explanation. The paper concludes that political cycles, operating through tax-policy uncertainty, systematically shape the magnitude of PEAD.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Two complementary designs on a hand-collected fraud sample. To test whether VC backing raises fraud without conflating it with better detection, the authors compare VC- and non-VC-backed firms within a set of newly public firms where detection is high and roughly uniform. To study why, they estimate a panel (hazard-style) prediction model over all VC-backed firms founded since 2000, relating the probability of fraud to governance features (founder control and cash-flow rights, number and type of investors, board control) and to funding-market conditions at the first round. The unit of analysis is the startup, and within-firm comparisons of board types help separate governance from other firm traits.</t>
+          <t>An empirical asset-pricing design documenting variation in post-earnings announcement drift across presidential (Republican vs. Democratic) periods, combined with survey evidence on underreaction and tests of the tax-policy-uncertainty mechanism (volatility of the tax component of earnings, references to tax laws in filings). The unit of analysis is the firm-earnings announcement over time; identification is associational across political regimes.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Venture Capital, Corporate Governance, Financial Fraud</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>PitchBook; Crunchbase; Dyck, Fang, Hebert &amp; Xu (this paper) — Venture-fraud case sample</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>Market Anomalies, Behavioral Finance, Political Economy &amp; Finance</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Uses standard earnings and analyst (I/B/E/S) data plus survey-based expectations; no distinctive datasets identified.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Da et al. - Presidential Cycles in PEAD.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Diwan et al. - Competition and Fraud in Health Care</t>
+          <t>Working Paper - 2026 - Ormazabal and Shi - Industry (Re)Classifications and Corporate Governance</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -961,46 +1029,50 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Diwan, Eliason, League, Leder-Luis, McDevitt, Roberts</t>
+          <t>Ormazabal, Shi</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Competition and Fraud in Health Care</t>
+          <t>Industry (Re)Classifications and Corporate Governance</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>This paper examines how competition affects fraud when governments procure goods and services from private firms, using Medicare's durable medical equipment (DME) market. The authors argue competition has an ambiguous effect on fraud: it dissipates the rents that attract fraudulent firms, but also squeezes margins so that legitimate firms may exit. Exploiting Medicare's switch from administratively regulated prices to competitive bidding for DME, they show that fraudulent suppliers' cost advantage let them gain market share while legitimate suppliers left the market. The result implies that price competition can perversely concentrate a market in fraudulent providers. The paper connects procurement design to the composition of firms and the prevalence of fraud.</t>
+          <t>This paper examines whether industry classifications affect how firms select peers for executive-compensation benchmarking, using Global Industry Classification Standard (GICS) reclassifications for identification. Firms become significantly more likely to include peers whose GICS codes converge with their own and to drop peers whose codes diverge, with stronger effects when proxy advisors and passive investors provide greater oversight. The authors find no evidence of strategic peer selection. The results show that formal industry classifications shape compensation benchmarking and are disciplined by governance. The paper links classification systems to executive-pay peer selection.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Governments buy many goods and services from private firms, and competition is generally expected to lower prices, but the paper argues its effect on fraud is theoretically ambiguous. On one hand, competition dissipates the excess profits that attract fraudulent entrants; on the other, it compresses margins so far that honest firms, which bear real costs, can no longer break even, potentially leaving the market to low-cost fraudulent providers. The setting that makes this trade-off visible is Medicare's procurement of durable medical equipment, where a switch from administratively set prices to competitive bidding sharply cut reimbursement. The authors reason that because fraudulent suppliers enjoy an artificial cost advantage, since they need not actually deliver legitimate equipment, the price squeeze from competition should hit legitimate firms harder, causing them to exit while fraudulent firms gain share. They link supplier-level claims to fraud-enforcement records to classify firms and trace market shares and exit around the reform. The finding that fraudulent firms expanded as legitimate firms left implies that price competition, absent complementary screening or enforcement, can perversely concentrate a market in fraud rather than eliminate it, an important qualification to the standard case for competitive procurement.</t>
+          <t>The paper asks whether the industry classification a firm is assigned influences which peers it chooses for executive-pay benchmarking. Because classifications and peer choices could be jointly determined, it needs exogenous variation, which it finds in GICS reclassifications that reassign firms to different industry codes for reasons outside their compensation decisions. The authors predict that after a reclassification, firms will add peers whose codes now converge with theirs and drop peers whose codes diverge. They confirm this and show the effect is stronger where proxy advisors and passive investors exert more oversight, indicating governance disciplines the process. Finding no evidence of strategic selection, they interpret the peer changes as governance-driven rather than opportunistic. The paper concludes that formal industry classifications causally shape compensation peer selection.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>An event-study / difference-in-differences design using Medicare's shift from administratively set prices to competitive bidding for durable medical equipment as the policy shock. Because the reform sharply cut reimbursement in affected product-areas and regions, the authors can compare how fraudulent and legitimate suppliers fared afterward. They classify suppliers by linking Medicare claims to fraud-enforcement records, then track market shares, entry, and exit for each group around the reform. The unit of analysis is the supplier (NPI); auction-bid data support the analysis of bidding.</t>
+          <t>A quasi-experimental design exploiting GICS industry reclassifications as exogenous changes in firms' industry membership, examining how firms adjust their executive-compensation peer groups (adding converging, dropping diverging peers). Heterogeneity by proxy-advisor and passive-investor oversight tests the governance channel. The unit of analysis is the firm (and peer pair); identification comes from reclassification events.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Health Economics, Industrial Organization &amp; Procurement, Fraud &amp; Enforcement</t>
+          <t>Executive Compensation, Corporate Governance, Industry Classification</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Centers for Medicare &amp; Medicaid Services (CMS) — Medicare DMEPOS claims; DOJ / HHS-OIG — Fraud enforcement records; Yunan Ji — Medicare DME auction bids</t>
+          <t>GICS reclassification data (MSCI/S&amp;P); Compensation peer-group disclosures</t>
         </is>
       </c>
       <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Ormazabal and Shi - Industry (Re)Classifications and Corporate Governance.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+          <t>Working Paper - 2026 - Bernstein - The Value of Ratings Evidence from Their Introduction in Securities Markets</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -1009,476 +1081,3180 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Correia, Luck, Verner</t>
+          <t>Bernstein</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Bank Runs with and without Bank Failure</t>
+          <t>The Value of Ratings: Evidence from Their Introduction in Securities Markets</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>This paper builds a comprehensive historical database of U.S. bank runs by applying large language models to historical newspapers, yielding information on 3,984 runs on individual banks from 1863 to 1934. The data show runs are far more likely at weak banks but also occur at strong banks, especially following negative news about the real economy or the broader banking system. Crucially, runs typically cause failure only when a bank's fundamentals are poor; strong banks survive through signaling, interbank cooperation, and temporary suspension. Locally, runs on weak banks produce much larger declines in deposits, lending, and manufacturing activity than runs on strong banks. The findings put poor fundamentals at the center of both when runs occur and when they are economically damaging, tempering pure self-fulfilling-panic accounts.</t>
+          <t>This paper studies the first-ever ratings for corporate securities, using John Moody's 1909 publication that assigned letter grades to most listed railroad bonds. These ratings had no regulatory implications and were largely explainable from public information, isolating their pure information role. The author finds that bonds rated lower than the market implied saw rising secondary-market yields, and that rated bonds experienced a substantial decline in bid-ask spreads, consistent with reduced information asymmetry and improved liquidity. The results show ratings can improve information transmission even without regulatory force. The paper provides clean historical evidence on the value of ratings.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>The paper's first contribution is measurement: to study bank runs systematically, the authors use large language models to read historical newspapers and assemble a large, bank-level database of runs spanning 1863-1934, far broader than hand-collected samples. Armed with this data, they ask whether runs strike indiscriminately, as pure panic models suggest, or track fundamentals. They find runs concentrate at weak banks but can also hit strong ones, especially after negative news about the real economy or the banking system, indicating an information-driven component. The central distinction they then draw is between a run and a failure, since a run threatens a bank but whether it causes failure depends on fundamentals. Strong banks survive runs through signaling their soundness, cooperation among banks, and temporary suspension of convertibility, whereas weak banks fail. The paper then links runs to the real economy, showing that runs on weak banks cause much larger local declines in deposits, lending, and manufacturing activity than runs on strong banks. Taken together, the evidence places poor fundamentals at the center of both when runs occur and when they do damage, tempering models in which small shocks trigger discontinuous jumps to bad equilibria and favoring accounts in which fundamentals discipline both the incidence and consequences of runs.</t>
+          <t>The paper addresses the difficulty of isolating the informational value of credit ratings, since modern ratings are entangled with regulation. It turns to a historical natural experiment: John Moody's 1909 introduction of the first letter ratings for railroad bonds, which carried no regulatory implications and drew on public information. Because the ratings had no mechanical regulatory effect, any market reaction reflects their information content. The author examines how bond yields and liquidity responded to being rated and to receiving ratings below market-implied levels. Finding that lower-than-expected ratings raised yields and that rated bonds saw narrower bid-ask spreads, the paper attributes these to reduced information asymmetry. It concludes that ratings can improve information transmission and liquidity on their own informational merits.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>An empirical study built on a newly constructed dataset. Using large language models to read historical newspapers, the authors assemble information on 3,984 bank runs (1863-1934). They then relate the incidence of runs to bank fundamentals and to news about the economy and banking system, separate runs that caused failure from those that did not, and identify the mechanisms (signaling, interbank cooperation, suspension) that let strong banks survive. A local analysis compares deposits, lending, and manufacturing activity around runs on weak versus strong banks. The units of analysis are the bank and its local economy.</t>
+          <t>A historical natural-experiment design using John Moody's 1909 introduction of the first-ever corporate (railroad) bond ratings, which had no regulatory implications, to isolate the information value of ratings. The author compares secondary-market yields and bid-ask spreads for rated versus unrated bonds and for bonds rated below market-implied levels. The unit of analysis is the bond; identification comes from the rating introduction.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Banking History, Financial Crises, Text-as-Data / LLMs</t>
+          <t>Credit Ratings, Liquidity &amp; Microstructure, Financial History</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Correia, Luck &amp; Verner (this paper) — Historical bank-run database; Library of Congress — Chronicling America; OCC — National bank call reports (Annual Report to Congress)</t>
+          <t>Moody's (1909) — First-ever railroad bond ratings; Historical railroad bond prices/yields</t>
         </is>
       </c>
       <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Bernstein - The Value of Ratings Evidence from Their Introduction in Securities Markets.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Bornstein and Castillo-Martinez - Firm Exit and Financial Frictions</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
+          <t>Journal of Accounting Research - 2026 - Billings et al. - Incidence, Risk, and Disclosure of Corporate Litigation Insights from Federal Court Filings</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting Research</t>
+        </is>
+      </c>
       <c r="C13" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Bornstein, Castillo-Martinez</t>
+          <t>Billings, Holthausen, Petrovits, Wang</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Firm Exit and Financial Frictions</t>
+          <t>Incidence, Risk, and Disclosure of Corporate Litigation: Insights from Federal Court Filings</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>This paper examines whether financial frictions cause too many firms to fail, motivating government interventions that prevent closures during crises. The authors build a firm-dynamics model with incomplete financial markets and show that frictions generate excessive firm exit, with a key sufficient statistic being the marginal propensity to exit with debt. Using confidential U.S. Census data, they estimate the debt–exit relationship and use it to discipline the model. The calibrated model implies that eliminating financial frictions would cut firm exit from 9.3% to 5.0% and deliver welfare gains of 3.6% in consumption-equivalent terms, with costs that spike during financial crises but not during ordinary productivity recessions. Comparing government-guaranteed loans and grants, the paper quantifies the trade-off between fiscal cost and effectiveness in preventing excessive exit.</t>
+          <t>This paper assembles and describes a comprehensive sample of 174,782 lawsuits filed against 218,437 public-company defendants in U.S. federal district court from 2006 to 2021. The suits span product liability, civil-rights discrimination, contract breaches, labor practices, antitrust, corruption, securities violations, pollution, and IP infringement. The sample shows rich variation across firms, industries, time, suit types, plaintiffs, and outcomes. The authors use it to characterize the incidence, risk, and disclosure of corporate litigation. The paper provides a broad, systematic picture of public firms' exposure to federal litigation.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Policymakers routinely intervene to prevent firm closures during crises on the presumption that financial frictions push otherwise-viable firms out of business, but whether exit is actually inefficient is theoretically ambiguous, and the paper sets out to answer it. It builds a firm-dynamics model with incomplete financial markets in which frictions can distort the exit margin, and it identifies the marginal propensity to exit with respect to debt as the sufficient statistic that governs whether exit is excessive. The intuition is that if firms carrying more debt are disproportionately likely to exit, the frictions are inducing closures that would not occur in a frictionless world. To make this operational, the authors estimate the debt-exit relationship directly in confidential firm-level data and use it to discipline the model's key parameter. They then use the calibrated model to compute how much frictions inflate the exit rate and the associated welfare loss, and to show that this loss is state-dependent, spiking during financial crises but not during ordinary productivity recessions, precisely because crises tighten the financial channel. Finally, the paper compares policy instruments, government-guaranteed loans versus grants, evaluating each on the trade-off between fiscal cost and effectiveness at curbing excessive exit.</t>
+          <t>The paper is motivated by the fact that research on corporate litigation often focuses narrowly on securities class actions, missing the full breadth of lawsuits firms face. To address this, the authors build a large sample of federal district court filings against public companies over 2006-2021, covering many allegation types. They document the sample's rich variation across firms, industries, suit types, plaintiffs, and outcomes, establishing basic facts about corporate litigation. They then examine the incidence and risk of litigation across firms and how firms disclose it. The descriptive breadth allows comparisons that narrower samples cannot support. The paper concludes by providing a systematic, comprehensive characterization of public firms' federal-litigation exposure and its disclosure.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>A quantitative firm-dynamics model with incomplete markets, disciplined by one reduced-form estimate. The theoretical contribution is to show that the marginal propensity to exit with respect to debt is a sufficient statistic for whether financial frictions make exit excessive. The authors estimate that debt-exit relationship in confidential Census microdata covering all employers, use it to pin down the model's key parameter, and then use the model to compute how much frictions inflate exit and reduce welfare, and how that cost differs between financial crises and ordinary recessions. Finally they compare guaranteed loans against grants as interventions.</t>
+          <t>A descriptive, data-construction study assembling 174,782 federal district court lawsuits against 218,437 public-company defendants (2006-2021) and characterizing the incidence, risk, and disclosure of corporate litigation across firms, industries, suit types, and outcomes. The unit of analysis is the lawsuit/firm; the contribution is comprehensive measurement rather than a single identification strategy.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Firm Dynamics, Financial Frictions, Macroeconomic Policy</t>
+          <t>Corporate Litigation, Disclosure, Law and Finance</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>U.S. Census Bureau — Longitudinal Business Database (LBD); Bureau van Dijk — Orbis (Italy)</t>
+          <t>U.S. federal district court filings (PACER)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting Research - 2026 - Billings et al. - Incidence, Risk, and Disclosure of Corporate Litigation Insights from Federal Court Filings.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Malenko et al. - Fragmentation of Shareholder Power</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n"/>
+          <t>Journal of Accounting Research - 2026 - Armstrong et al. - The Assignment of Intellectual Property Rights and Innovation</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting Research</t>
+        </is>
+      </c>
       <c r="C14" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Malenko, Malenko, Tsoy</t>
+          <t>Armstrong, Glaeser, Park</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Fragmentation of Shareholder Power</t>
+          <t>The Assignment of Intellectual Property Rights and Innovation</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>This paper develops a theoretical framework to evaluate how the asset-management industry's shift toward tailored portfolios, fund proliferation, and decentralized stewardship affects corporate governance. Growing heterogeneity in investor preferences better aligns products with demand but can fragment ownership and weaken managerial oversight. The authors show fund proliferation does not necessarily weaken governance: stronger manager incentives and concentrated portfolios of specialized funds can offset fragmentation, especially when investor preferences are intense. However, intense preferences can also push asset managers to compete by granting investors control—decentralizing stewardship and adopting pass-through voting—without internalizing the resulting governance costs. The paper clarifies when investor-driven customization helps or harms oversight.</t>
+          <t>This paper studies how the assignment of intellectual-property rights between inventors and their employers affects innovation. Incomplete-contracting theory predicts that stronger employer property rights reduce the threat that employee inventors hold up their employers, affecting inventor and invention outcomes. The authors test this using a U.S. appellate court ruling that shifted the assignment of patent rights from inventors to employers. Within-employer-year analyses show affected inventors are less likely to retain patent rights or assign patents to new employers. The paper provides causal evidence on how IP-rights allocation shapes innovation.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>The asset-management industry has moved toward tailored portfolios, a proliferation of funds, and decentralized stewardship, and the paper asks whether these trends necessarily weaken the corporate oversight that concentrated ownership traditionally provides. It sets up the tension: greater heterogeneity in investor preferences improves the match between products and demand, but it can also fragment ownership and dilute any single manager's incentive to monitor. The authors build a model in which asset managers choose how concentrated their portfolios are, how much monitoring effort to exert, and how much control to pass through to their investors, all given the intensity of investor preferences. Analyzing it, they show that fund proliferation does not mechanically degrade governance, because stronger managerial incentives and the concentrated portfolios of specialized funds can offset fragmentation, and this offset is strongest when investor preferences are intense. However, the same intensity creates a countervailing force, since competition among managers on the 'control' dimension can lead them to hand voting power to investors even when doing so is socially costly, because each manager does not internalize the governance externality. The framework thus delineates conditions under which investor-driven customization helps versus harms oversight, rather than predicting a uniform decline.</t>
+          <t>The paper draws on incomplete-contracting theory, which holds that who owns the rights to an invention affects bargaining and hold-up between inventors and employers, and thus innovation. It predicts that strengthening employer property rights reduces inventors' ability to hold up employers, changing inventor mobility and invention outcomes. To test this causally, the authors exploit a U.S. appellate court ruling that shifted the default assignment of patent rights from inventors toward employers, providing an exogenous change in property rights. Using within-employer-year comparisons, they examine how affected inventors' retention and reassignment of patents change. Finding affected inventors less able to retain or move patents, they confirm the theory's predictions. The paper concludes that the legal allocation of IP rights materially shapes inventor behavior and innovation.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>A theoretical (mechanism-design) model, with no external data. Asset managers choose how concentrated their portfolios are, how much effort to put into monitoring firms, and how much voting control to hand to their investors, all as functions of how intense investor preferences are. The analysis derives comparative statics showing when fund proliferation is offset by stronger incentives and specialization (so governance holds up) and when competition on the 'control' margin leads managers to decentralize stewardship inefficiently. The key results characterize which force dominates as preference intensity varies.</t>
+          <t>A natural-experiment design exploiting a U.S. appellate court ruling that shifted the default assignment of patent rights from employee inventors to employers, with within-employer-year comparisons of affected versus unaffected inventors. Outcomes include inventors' retention of patent rights and reassignment to new employers. The unit of analysis is the inventor (within employer-year); identification comes from the court ruling.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Corporate Governance, Asset Management, Financial Theory</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Theoretical paper; no nonstandard datasets identified.</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>Intellectual Property, Innovation, Law and Finance</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>USPTO patent and inventor data</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting Research - 2026 - Armstrong et al. - The Assignment of Intellectual Property Rights and Innovation.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Bardóczy et al. - Monopsony Power and the Transmission of Monetary Policy</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n"/>
+          <t>Journal of Accounting Research - 2026 - Liu et al. - Strategic (Inconsistent) Disclosures and Sophisticated Investors Evidence from Hedge Funds</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting Research</t>
+        </is>
+      </c>
       <c r="C15" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Bardóczy, Bornstein, Salgado</t>
+          <t>Liu, Madsen, Zhou</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Monopsony Power and the Transmission of Monetary Policy</t>
+          <t>Strategic (Inconsistent) Disclosures and Sophisticated Investors: Evidence from Hedge Funds</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>This paper studies how employer labor-market power changes the way monetary policy transmits to wages and employment. Using administrative U.S. Census data, the authors show that high-monopsony firms—those accounting for over 10 percent of their local wage bill—adjust their wage bill and employment less in response to monetary policy. They rationalize this with a New Keynesian model featuring heterogeneous firms and oligopsonistic labor competition, where wage stickiness combined with labor-market power drives the muted response. The model isolates two channels—partial passthrough and misallocation—through which oligopsony shapes aggregate effects. Calibrated to U.S. labor markets, it implies that the decline in labor-market power since the 1980s raised the output response to monetary policy by about 10 percent and accounts for roughly 15 percent of the flattening of the Phillips curve.</t>
+          <t>This paper studies strategic, inconsistent disclosures by hedge-fund advisers. The authors find that 40% of these disclosures omit or de-emphasize information about advisers' operational and investment risks relative to other public sources. Funds with such inconsistencies subsequently deliver predictably lower performance, yet do not differ in fund flows, the flow-performance relation, ownership structure, or management. The results suggest even sophisticated investors do not fully penalize inconsistent disclosure. The paper documents strategic disclosure in a setting with ostensibly sophisticated investors.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>The paper starts from the observation that firms with labor-market (monopsony) power set wages strategically rather than taking them as given, so their response to monetary policy need not resemble that of competitive firms. It hypothesizes that when wages are sticky and a firm holds monopsony power, the firm absorbs monetary shocks differently, adjusting its wage bill and employment less, because its wage-setting margin interacts with nominal rigidity. Using administrative data, the authors first document exactly this, showing that high-monopsony firms, those accounting for a large share of their local labor market, react less to monetary-policy shocks. To interpret the fact and quantify aggregate implications, they build a heterogeneous-firm New Keynesian model with oligopsonistic labor markets in which the muted response emerges from the interaction of wage stickiness and market power. The model isolates two channels through which oligopsony shapes aggregate outcomes, incomplete passthrough of shocks to wages and misallocation of labor across firms. Calibrating it to U.S. labor markets lets the authors run counterfactuals, and they find that the secular decline in labor-market power since the 1980s made monetary policy more potent and accounts for a meaningful share of the flattening of the Phillips curve, linking a structural labor-market trend to the changing behavior of monetary policy.</t>
+          <t>The paper examines whether hedge-fund advisers strategically shade their disclosures, comparing what they tell investors against other public information about their risks. It finds a large share of disclosures omit or downplay operational and investment risks, indicating strategic inconsistency. The authors then ask whether these inconsistencies are informative about outcomes, and find funds with inconsistent disclosures earn predictably lower returns. Strikingly, investors do not appear to react—flows, the flow-performance relation, ownership, and management look similar—suggesting the inconsistency is not fully priced. This is notable because hedge-fund investors are typically considered sophisticated. The paper concludes that strategic disclosure persists and is under-penalized even among sophisticated investors.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>A two-part design combining reduced-form estimates with a calibrated model. Empirically, the authors measure how individual firms' wage bills and employment respond to surprise (high-frequency identified) monetary-policy shocks, and compare firms with more versus less local labor-market power using confidential Census data. They then build and calibrate a heterogeneous-firm New Keynesian model with oligopsonistic labor markets in which the muted response of high-monopsony firms arises naturally, decomposing the aggregate effect into passthrough and misallocation channels. The calibrated model is used to ask how the decline in monopsony since the 1980s changed monetary transmission and the slope of the Phillips curve.</t>
+          <t>An empirical design comparing hedge-fund advisers' disclosures (from regulatory filings) against other public information to flag 'inconsistent' disclosures, then relating inconsistency to future fund performance and to investor responses (flows, flow-performance, ownership). The unit of analysis is the fund/adviser; identification is cross-sectional.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Monetary Policy, Labor Market Power, Macroeconomics</t>
+          <t>Disclosure &amp; Hedge Funds, Investor Sophistication, Financial Reporting</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>U.S. Census Bureau — LEHD merged with Longitudinal Business Database (LBD)</t>
+          <t>SEC Form ADV (hedge-fund adviser filings)</t>
         </is>
       </c>
       <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting Research - 2026 - Liu et al. - Strategic (Inconsistent) Disclosures and Sophisticated Investors Evidence from Hedge Funds.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n"/>
+          <t>Journal of Accounting Research - 2026 - Gao and Lu - Aggregated Compensation Peer Group Disclosure and Managerial Labor Market Competition A Network Analysis</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting Research</t>
+        </is>
+      </c>
       <c r="C16" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Thesmar, Verner</t>
+          <t>Gao, Lu</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Beliefs and Stock Market Fluctuations: New Evidence from the Past Seven Decades</t>
+          <t>Aggregated Compensation Peer Group Disclosure and Managerial Labor Market Competition: A Network Analysis</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>This paper builds a new seven-decade series of subjective expected equity returns (1956-2024) from an independent equity-analysis firm and uses it to reassess how beliefs move markets. Unlike the expectations of individual investors and professional forecasters, this measure is strongly positively correlated with the earnings-price ratio, responds negatively to past returns, and positively predicts future returns. Individual and professional-forecaster expectations are only weakly or negatively correlated with the new series, and disagreement between sophisticated and individual investors is associated with higher trading volume. The evidence fits a model of heterogeneous beliefs in which naive investors extrapolate past returns while sophisticated investors are close to rational. The paper offers a rare long-run window on the belief dynamics behind valuations.</t>
+          <t>This paper uses network analysis of firms' disclosed compensation peer groups to study managerial labor-market competition. By aggregating peer-group disclosures across firms, the authors map the network of which firms benchmark against which, and use its structure to characterize competition for executive talent. The analysis links a firm's position in the peer network to compensation and labor-market outcomes. The paper shows that compensation peer-group disclosures, taken together, reveal the structure of the managerial labor market. It provides a network-based lens on executive-pay benchmarking.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Testing how beliefs move markets has been hampered by the lack of a long, consistent measure of what sophisticated investors expect returns to be, so the paper's first move is to construct one, hand-collected over nearly seven decades from an independent equity-analysis firm. With this new series in hand, it characterizes the properties any belief-based theory must confront: sophisticated expected returns co-move positively with the earnings-price ratio, respond negatively to recent past returns (they are mean-reverting), and positively predict future returns. It contrasts these with survey measures of individual investors and professional forecasters, which are only weakly or even negatively correlated with the new series, implying different groups hold systematically different beliefs. The paper then notes that disagreement between sophisticated and individual investors lines up with trading volume, consistent with heterogeneous beliefs generating trade. Because no single-agent, single-belief model can match this joint pattern, it argues for a framework with at least two types of investor. It then shows that a model in which naive investors extrapolate past returns while sophisticated investors are close to rational reproduces the co-movement with valuations, the mean reversion, the predictability, and the volume-disagreement link, providing a unified account of the belief dynamics behind valuations over seventy years.</t>
+          <t>The paper starts from the fact that firms disclose the peer groups they use to benchmark executive pay, and argues these disclosures, aggregated across firms, form a network revealing labor-market linkages. It constructs this network by connecting firms that name each other (or common peers) in compensation benchmarking. It then uses network structure—centrality, clustering, and connections—to characterize competition for executive talent. Relating network position to pay and outcomes shows that where a firm sits in the network matters for compensation. The authors interpret the network as a map of managerial labor-market competition that individual disclosures cannot reveal in isolation. The paper concludes that aggregated peer-group disclosures are informative about the structure of the executive labor market.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Primarily a measurement and asset-pricing study. Its foundation is a new, hand-collected 1956-2024 series of sophisticated investors' expected returns. Using it, the authors run correlation and predictive regressions, linking expected returns to the earnings-price ratio, to past returns, and to realized future returns, and compare them with survey expectations of individuals and forecasters, while relating disagreement across groups to trading volume. A two-type model (extrapolative naive investors, near-rational sophisticated investors) is then shown to reproduce this whole set of facts. The unit of analysis is the market over time.</t>
+          <t>A network-analysis design that aggregates firms' disclosed compensation peer groups into a network and relates network structure and firm position to compensation and labor-market outcomes. The unit of analysis is the firm within the peer network; identification is descriptive/associational from network structure.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Behavioral Finance, Asset Pricing, Expectations &amp; Beliefs</t>
+          <t>Executive Compensation, Peer Benchmarking, Networks</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Value Line Investment Survey; Robert Shiller — Investor Confidence Survey; UBS/Gallup and Livingston Survey</t>
+          <t>Compensation peer-group disclosures (SEC proxy filings)</t>
         </is>
       </c>
       <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting Research - 2026 - Gao and Lu - Aggregated Compensation Peer Group Disclosure and Managerial Labor Market Competition A Network A.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n"/>
+          <t>Journal of Accounting Research - 2026 - Ferrell et al. - Corporate Litigation, Governance, and the Role of Law Firms</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting Research</t>
+        </is>
+      </c>
       <c r="C17" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Ahern</t>
+          <t>Ferrell, Manconi, Neretina, Powley, Renneboog</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+          <t>Corporate Litigation, Governance, and the Role of Law Firms</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>This paper shows that the industrial composition of a city's economy shapes its cost of municipal borrowing. In a panel of 1,177 U.S. cities from 2005 to 2022, greater sectoral concentration raises default risk and municipal bond spreads, especially where dominant industries are associated with low property values. Instrumental variables built from national sector-employment trends and regional house-price variation support a causal reading. A calibrated city-default model implies the estimated spread effect understates the gross risk from concentration, because concentration also brings agglomeration benefits that lower spreads, particularly in high-property-value cities. The paper connects local economic structure to public finance and credit risk.</t>
+          <t>This paper studies plaintiff law firms in corporate litigation, focusing on 'star' firms that dominate settlement outcomes. Star firms are associated with larger settlements, but much of this is predicted by the defendant's litigation-insurance coverage, suggesting assortative matching of stars with lawsuits that have larger expected payoffs. Stars also charge higher fees for a given settlement size. Additional tests suggest visibility and information asymmetry toward less sophisticated plaintiffs sustain the stars' market position. The paper illuminates how the market for plaintiff legal services shapes corporate-litigation outcomes.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>A city whose economy depends on only a few industries bears more concentrated economic risk, which the paper argues should raise the probability of fiscal distress and therefore the yields investors demand on its municipal bonds. The key refinement is that the sign and size of this effect should depend on what kind of industries dominate, because concentration in sectors associated with low property values is more dangerous when the property-tax base that backs municipal debt is weaker. The paper first documents the concentration-spread relationship in a large panel of cities and shows it is stronger where dominant industries imply low property values. Recognizing that industrial structure is not randomly assigned, it constructs instruments from national, city-external variation, namely industry-level employment trends interacted with regional house-price movements, to isolate plausibly exogenous changes in local concentration. It then confronts a subtlety: concentration is not purely bad, since agglomeration can raise productivity and property values and thereby lower spreads, so the reduced-form spread effect nets these opposing forces. To recover the gross risk, the authors calibrate a city-default model, which implies that the true risk contribution of concentration is larger than the estimated net spread effect, especially in high-property-value cities where agglomeration benefits offset it.</t>
+          <t>The paper focuses on plaintiff law firms as key but understudied players in corporate litigation, asking why a few 'star' firms dominate. It first documents that star firms obtain larger settlements, which could reflect skill or selection. To distinguish these, it shows much of the star-settlement relation is explained by the defendant's litigation-insurance coverage, implying stars match with cases that already have larger expected payoffs. This points to assortative matching rather than pure skill. The authors then show stars charge higher fees for a given settlement, indicating market power. Tests on visibility and information asymmetry toward less sophisticated plaintiffs suggest how stars sustain that power. The paper concludes that the structure of the plaintiff-lawyer market, including matching and information frictions, shapes litigation outcomes.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>A panel regression of municipal bond spreads on city industrial concentration, made causal with an instrumental-variables (shift-share) strategy. Because a city's industry mix is not random, the authors instrument local concentration using national industry-employment trends interacted with the city's initial composition and regional house-price movements, isolating variation unlikely to be driven by the city's own fiscal shocks. The unit of analysis is the city-year, and interactions separate concentration in low- versus high-property-value industries. A calibrated city-default model then shows the gross risk from concentration exceeds the net spread effect once offsetting agglomeration benefits are accounted for.</t>
+          <t>An empirical study of plaintiff law firms in corporate litigation, relating 'star' firm involvement to settlement size, fees, and defendant litigation-insurance coverage to separate skill from assortative matching. Additional tests examine visibility and plaintiff sophistication as sources of star firms' market power. The unit of analysis is the lawsuit/law-firm.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Municipal Finance, Credit Risk, Urban &amp; Regional Economics</t>
+          <t>Corporate Litigation, Governance, Legal Services</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>MSRB — Municipal Securities Rulemaking Board trade data; U.S. Census Bureau — LODES (LEHD Origin-Destination Employment Statistics); FHFA — House Price Index</t>
+          <t>Corporate litigation and settlement data</t>
         </is>
       </c>
       <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting Research - 2026 - Ferrell et al. - Corporate Litigation, Governance, and the Role of Law Firms.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Clayton and Coppola - The Optimal Use of AI in Financial Regulation</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n"/>
+          <t>Journal of Accounting Research - 2026 - Ferracuti and Lind - Macroeconomic Information Acquisition Around Earnings Clusters</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting Research</t>
+        </is>
+      </c>
       <c r="C18" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Clayton, Coppola</t>
+          <t>Ferracuti, Lind</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>The Optimal Use of AI in Financial Regulation</t>
+          <t>Macroeconomic Information Acquisition Around Earnings Clusters</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>This paper asks whether modern AI methods applied to granular portfolio-holdings data can improve macroprudential regulation, and how policymakers should use such tools. The authors build a graph-based deep learning model over security-level holdings of financial intermediaries that embeds economic priors and learns latent representations of both assets and investors from the network of positions. Applied to the near-universe of non-bank financial intermediaries (about $40 trillion), the model forecasts intermediary trading far better than existing approaches, including during crises, and has more than ten times the explanatory power for cross-sectional stress-period returns. Its learned embeddings encode economically interpretable information about fire-sale vulnerability, and the architecture is inductive enough to produce estimates even for withheld asset classes or investors. The authors then embed the empirical model in a macroprudential optimal-policy framework, addressing the Lucas critique, to show why these objects matter for welfare.</t>
+          <t>This paper shows that investors gather more macroeconomic information during earnings clusters—periods when many firms report earnings. This behavior is amplified during negative economic shocks and when macroeconomic announcements occur concurrently. The authors show these information-acquisition patterns have implications for equity valuations. The evidence suggests that clustered earnings news prompts investors to update their macro views, not just firm-specific ones. The paper links the timing of earnings news to macroeconomic learning and asset prices.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>The paper frames systemic-risk measurement as a prediction problem defined over the network of who holds which assets, arguing that the structure of intermediary holdings encodes fire-sale vulnerability that standard, low-dimensional risk metrics miss. It proposes that modern representation-learning methods can extract this information if they are constrained by economic priors rather than applied as black boxes. Concretely, the authors build a graph-based deep-learning model that learns latent embeddings of both assets and investors from the bipartite network of positions, so that assets held by similar investors, and investors holding similar assets, end up close in the learned space. They validate that these learned objects are economically meaningful by showing the model forecasts intermediary trading, including during crises, far better than existing approaches and explains an order of magnitude more of the cross-section of stress-period returns. Because the architecture is inductive, it can generate estimates even for asset classes or investors held out of training, which matters for a regulator facing new or incompletely observed exposures. The paper then asks the normative question of how a regulator should optimally use such predictions, embedding the empirical model inside a macroprudential optimal-policy framework designed to survive the Lucas critique so that the learned vulnerability measures inform welfare-improving policy rather than merely describing risk.</t>
+          <t>The paper starts from the idea that earnings announcements convey not only firm-specific but also macroeconomic information, especially when many firms report at once. It hypothesizes that during earnings clusters investors have more incentive to acquire macroeconomic information, because clustered reports are informative about the aggregate economy. Using proxies for information acquisition, the authors show macro information gathering rises during earnings clusters. They further show this rises more during negative economic shocks and alongside macroeconomic announcements, when aggregate uncertainty is higher. They then connect these acquisition patterns to equity valuations, indicating the learning affects prices. The paper concludes that clustered earnings news is a trigger for macroeconomic learning with asset-pricing consequences.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Two connected pieces. The empirical piece is a graph (network) neural network trained on security-level holdings of nearly all non-bank intermediaries; it learns compact representations of assets and investors from the web of who holds what, and is judged out-of-sample against existing risk metrics on two tasks, predicting intermediary trading and explaining returns during stress. The model's inductive design lets it score even assets or investors left out of training. The normative piece plugs these learned vulnerability measures into a macroprudential optimal-policy problem built to withstand the Lucas critique, showing how a regulator should use them.</t>
+          <t>An empirical design relating measures of investor information acquisition (e.g., access to macro-relevant information) to the timing of earnings clusters, with amplification during negative economic shocks and concurrent macroeconomic announcements, and links to equity valuations. The unit of analysis is the time period/firm; identification relies on variation in earnings clustering and macro conditions.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning in Finance, Financial Regulation, Systemic Risk</t>
+          <t>Information Acquisition, Macroeconomic Information, Capital Markets</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>FactSet &amp; Morningstar — Security-level intermediary holdings</t>
+          <t>SEC EDGAR log files; RavenPack</t>
         </is>
       </c>
       <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting Research - 2026 - Ferracuti and Lind - Macroeconomic Information Acquisition Around Earnings Clusters.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n"/>
+          <t>Journal of Accounting Research - 2026 - Caskey et al. - Amendment Thresholds and Voting Rules in Debt Contracts</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting Research</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Ebsim, Lian, Ma, Ottonello, Perez</t>
+          <t>Caskey, Huang, Saavedra</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Sophisticated Borrowing Constraints and Macroeconomic Dynamics</t>
+          <t>Amendment Thresholds and Voting Rules in Debt Contracts</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>This paper argues that the way debt constraints are modeled fundamentally changes their macroeconomic implications. Traditional models impose hard borrowing limits that force firms to cut borrowing and investment whenever adverse shocks bind, producing financial acceleration. The authors instead model 'sophisticated borrowing constraints' resembling real-world financial covenants, where breaching an earnings-based debt threshold transfers control rights to creditors who then act to maximize their own value rather than mechanically shrinking credit. Calibrated to micro evidence on investment and earnings around covenant violations, the model matches firm-level dynamics while, at the macro level, generating no financial acceleration because violations do not trigger indiscriminate downscaling. The result challenges a workhorse mechanism linking credit conditions to aggregate fluctuations.</t>
+          <t>This paper studies the optimal voting rule that lets lenders waive a covenant violation. When lenders have heterogeneous preferences, lenient voting rules raise the chance of waivers that permit inefficient investment, while stringent rules can allocate the pivotal vote to lenders who deny waivers after false alarms in order to renegotiate and extract value, incurring deadweight costs. The optimal rule balances these forces to improve contracting efficiency. The authors derive comparative statics on how the optimal voting rule varies with contract and firm characteristics and test them empirically. The paper explains why debt contracts use the amendment thresholds and voting rules they do.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Standard macro models impose 'hard' borrowing limits under which any binding constraint mechanically forces firms to cut debt and investment, generating financial acceleration that amplifies aggregate shocks. The paper's central claim is that this modeling choice, rather than the existence of debt limits per se, drives the acceleration result. In reality, debt contracts are governed by financial covenants, so breaching an earnings-based threshold does not force proportional deleveraging but instead transfers control rights to creditors, who then choose firm policies to maximize their own claim value. The authors formalize this as a 'sophisticated' constraint in which the consequence of a violation is a state-contingent reallocation of control, not a fixed borrowing rule. They show first that such a model reproduces the microeconomic facts, matching how investment and earnings actually behave around covenant violations, so the mechanism is disciplined by observed firm behavior. They then embed it in general equilibrium and show that, because violations do not trigger indiscriminate, simultaneous downscaling across firms, the economy exhibits little or no financial acceleration. The upshot is that a more institutionally realistic constraint overturns a workhorse channel linking credit conditions to business cycles, implying that credit frictions may transmit very differently than standard models assume.</t>
+          <t>The paper begins from the observation that debt contracts specify voting rules governing how lenders can waive covenant violations, and asks what makes a voting rule optimal. It sets up a model with lenders who have heterogeneous preferences over waiving, so the choice of threshold determines whose vote is pivotal. Lenient rules make waivers easy but risk approving inefficient investments; stringent rules can hand the marginal vote to holdout lenders who deny waivers to renegotiate and extract value, which is costly. The optimal rule trades off these two inefficiencies. The authors derive comparative statics predicting how the optimal threshold shifts with contract and firm characteristics. They then test these predictions in data on debt-contract voting provisions, linking theory to observed contract design.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>A quantitative macro-finance model, distinguished by how it treats debt limits. Instead of a hard cap that forces proportional deleveraging when it binds, a covenant violation transfers control to creditors, who then choose the firm's policies. The model is first disciplined at the micro level by matching the observed behavior of investment and earnings around covenant violations, then solved in general equilibrium to ask whether it produces financial acceleration. Identification of the mechanism comes from comparing this covenant-style constraint against the standard hard-constraint benchmark while holding the rest of the model fixed.</t>
+          <t>A contract-theory model of lender voting rules for covenant waivers, yielding comparative statics that are then tested empirically on debt-contract provisions. The model characterizes the optimal amendment threshold as a balance between approving inefficient investment and enabling value-extracting renegotiation; the empirical tests relate observed voting rules to firm and contract characteristics. The unit of analysis is the debt contract.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Macro-Finance, Corporate Debt &amp; Covenants, Firm Investment</t>
+          <t>Debt Contracts &amp; Covenants, Contract Theory, Corporate Finance</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Refinitiv LPC — DealScan; Greg Nini (Nini, Smith &amp; Sufi) — Financial covenant violation data</t>
+          <t>Debt-contract voting/amendment provisions (EDGAR)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting Research - 2026 - Caskey et al. - Amendment Thresholds and Voting Rules in Debt Contracts.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n"/>
+          <t>Journal of Accounting Research - 2026 - Boulland et al. - Company Websites A New Measure of Disclosure</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting Research</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Dou, Wang, Wang</t>
+          <t>Boulland, Bourveau, Breuer</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>The Cost of Intermediary Market Power for Distressed Borrowers</t>
+          <t>Company Websites: A New Measure of Disclosure</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>This paper measures how much lender market power raises borrowing costs for firms in financial distress, who must raise urgent financing in thin, concentrated credit markets. The authors show that distressed borrowers pay very high loan spreads even after stripping out compensation for credit risk, liquidity risk, and ordinary loan-making costs. To decompose the residual, they build and estimate a dynamic game-theoretic model of distressed lending featuring latent demand heterogeneity, endogenous lender participation, creditor blocking power, and tacit collusion sustained by repeated syndication. Lender market power explains 533 basis points of risk-adjusted spreads in debtor-in-possession (DIP) loans and 300 basis points in highly speculative loans, with roughly 140 basis points from tacit collusion in each. Because this markup reduces survival-critical liquidity by 16–20%, market power emerges as a major, previously underappreciated source of financial-distress costs.</t>
+          <t>This paper proposes a new measure of firms' disclosure based on the content of their company websites, which are widely available and information-rich. Using historical website data for U.S. public firms, the authors construct the measure, validate it against existing disclosure and information-asymmetry proxies, and study its determinants. They then apply it to settings where standard measures are unavailable—U.S. private firms and French firms' compliance with a nonfinancial disclosure mandate. The applications show the website-based measure captures disclosure where other data cannot. The paper offers a broadly applicable, low-cost measure of corporate disclosure.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Distressed firms must raise financing quickly and in markets served by only a handful of specialized lenders, often from existing creditors who hold contractual blocking power, so the high spreads these borrowers pay may reflect lender market power rather than compensation for risk. The paper first establishes the puzzle empirically, showing that even after removing compensation for credit risk, liquidity risk, and ordinary loan-making costs, debtor-in-possession and highly speculative loans still carry very large spreads. To interpret this residual, the authors build a dynamic game-theoretic model of distressed lending whose ingredients are latent heterogeneity in borrower demand, endogenous lender participation, the blocking power incumbent creditors wield in bankruptcy, and tacit collusion sustained by lenders' repeated interaction in syndication. The model makes the markup identifiable and, importantly, decomposable into a piece from unilateral market power and a piece from collusion. Estimating it lets the authors quantify how much of the spread is a pure markup, and then translate that markup into a real cost, because the markup drains cash from firms that need liquidity to survive and so maps into a measurable reduction in survival-critical funds. The argument thus moves from an unexplained pricing fact, to a structural mechanism, to a welfare-relevant consequence, reframing lender market power as a first-order and previously under-appreciated cost of financial distress.</t>
+          <t>The paper notes that existing disclosure measures rely on filings or databases that are unavailable for many firms, such as private companies, limiting research. It proposes that company websites, which nearly all firms maintain, contain rich disclosure that can be measured from archived web data. The authors build the measure from historical website snapshots and validate it by showing it correlates with established disclosure and information-asymmetry proxies for public firms. Having established credibility, they apply it where standard data are missing—characterizing U.S. private firms' disclosure and testing French firms' compliance with a nonfinancial disclosure mandate. These applications demonstrate the measure's reach. The paper concludes that website content is a practical, general source for measuring disclosure across firm types and jurisdictions.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>A structural estimation of a dynamic game of distressed lending. The authors first show, in a reduced-form step, that DIP and highly speculative loan spreads stay large even after subtracting compensation for credit risk, liquidity, and normal lending costs, leaving an unexplained residual. They then build a model in which a few lenders decide whether to lend, exploit the blocking power incumbent creditors hold in bankruptcy, and sustain tacit collusion through repeated syndication; fitting it to loan-level data lets them split the residual spread into unilateral-market-power and collusion components. The estimated model is finally used to express the markup as the reduction in liquidity it imposes on distressed borrowers. The unit of observation is the loan facility.</t>
+          <t>A measurement paper that constructs a website-based disclosure metric from archived (historical) website data for U.S. public firms, validates it against existing disclosure and information-asymmetry measures, and applies it to U.S. private firms and to French firms subject to a nonfinancial disclosure mandate. The unit of analysis is the firm; validation is cross-sectional, and the French application uses the mandate as a setting.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Financial Distress &amp; Bankruptcy, Banking &amp; Lending, Market Power / Industrial Organization</t>
+          <t>Disclosure Measurement, Text &amp; Web Data, Financial Reporting</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Refinitiv LPC — DealScan; LPC (Refinitiv) — LSTA/LPC Mark-to-Market Pricing Data; PACER — Public Access to Court Electronic Records; Moody's — Default and Recovery Database</t>
+          <t>Internet Archive — Historical website (Wayback) data; French nonfinancial disclosure filings</t>
         </is>
       </c>
       <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting Research - 2026 - Boulland et al. - Company Websites A New Measure of Disclosure.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - He et al. - Homemade Foreign Trading</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n"/>
+          <t>Journal of Accounting and Economics - 2026 - Guay et al. - Internal information quality and performance metric selection</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics</t>
+        </is>
+      </c>
       <c r="C21" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>Guay, Kim, Timmermans</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Internal information quality and performance metric selection</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>This paper examines how firms' internal information quality (IIQ) shapes the design of executive incentive contracts. Higher IIQ is associated with using more performance metrics and with greater dissimilarity from peers' contracts, especially along non-financial dimensions. These relations hold using changes in IIQ likely induced by plausibly exogenous shifts in two financial accounting standards. Incorporating more numerous and more dissimilar non-financial metrics is positively associated with future profitability, but only when IIQ is high. The paper links the quality of firms' internal information to how they structure managerial incentives and to the payoff from doing so.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>The paper argues that designing executive incentives around multiple, tailored performance metrics requires firms to have high-quality internal information to measure those metrics reliably. It hypothesizes that firms with better internal information quality will use more performance metrics and design contracts that differ more from peers', particularly on harder-to-measure non-financial dimensions. Because IIQ is endogenous, the authors use changes induced by plausibly exogenous shifts in two financial accounting standards to sharpen identification. They then relate IIQ to the number and dissimilarity of performance metrics in executive contracts. They further test whether these design choices pay off, finding that more numerous and dissimilar non-financial metrics are associated with higher future profitability only when IIQ is high. The paper concludes that internal information quality is a key determinant of, and complement to, sophisticated incentive-contract design.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>An empirical design relating firms' internal information quality to executive performance-metric choices, using changes in information quality induced by two plausibly exogenous accounting-standard changes for identification. Outcomes include the number and peer-dissimilarity of performance metrics and their association with future profitability; the unit of analysis is the firm. Identification leans on the standard-change-induced shifts in information quality.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Executive Compensation, Internal Information Quality, Corporate Governance</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>ISS Incentive Lab — Executive incentive-plan data</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting and Economics - 2026 - Guay et al. - Internal information quality and performance metric selection.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Liu - Website cookies and voluntary disclosure</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Website cookies and voluntary disclosure</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>This paper uses website cookie information from U.S. firms' websites to measure the consumer data firms collect and examines how such data affect their accounting information environments. Cookies provide granular, real-time consumer data that can improve the quality of firms' internal information for external reporting. Firms with more cookies issue management sales forecasts more frequently and devote more of their 10-K disclosures to customer, marketing, and product topics. The effects are stronger when cookie-collected data are more relevant to the firm. The paper links a novel, technology-based measure of consumer-data collection to firms' disclosure behavior.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>The paper starts from the idea that firms increasingly collect granular consumer data online, and that such data may improve the internal information managers use for external reporting. It proposes website cookies as a measurable proxy for the intensity of consumer-data collection, since cookies capture real-time behavior of a firm's website visitors. The author reasons that firms with richer cookie-based data have better internal information about demand and customers, which should show up in more frequent and more customer-oriented disclosure. Measuring cookies across U.S. firms' websites, the paper relates cookie intensity to the frequency of management sales forecasts and to the content of 10-K filings. It finds firms with more cookies forecast sales more often and devote more disclosure to customer, marketing, and product topics, with stronger effects where the data are more relevant. The paper concludes that consumer-data collection technology shapes firms' voluntary disclosure and information environment.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>An empirical design using website cookie data as a proxy for firms' consumer-data collection, related to disclosure outcomes (management forecast frequency and 10-K content). Cross-sectional and within-firm variation in cookie intensity is linked to disclosure behavior, with heterogeneity by data relevance; the unit of analysis is the firm. The novelty is the cookie-based measure of internal information inputs.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Voluntary Disclosure, Data &amp; Technology, Information Environment</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Website cookie / web-tracking data</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting and Economics - 2026 - Liu - Website cookies and voluntary disclosure.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Huber et al. - Information flows in trading networks</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Huber, Watts, Zhu</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Information flows in trading networks</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>This paper studies the informational value of trading networks in over-the-counter markets using transaction-level corporate bond data. Investors with larger dealer networks make superior trading decisions before changes in credit fundamentals, earning better risk-adjusted performance. The authors trace this outperformance to trading connections where dealers are most likely to have access to novel credit-relevant information, supporting an interpretation of private information flowing through networks. The results show that whom an investor trades with, not just what they trade, carries information. The paper provides evidence on how information diffuses through OTC market structure.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>The paper begins from the feature of OTC markets that trades occur through dealers, so an investor's set of dealer relationships forms a network through which information can travel. It asks whether investors with more or better-connected dealer networks obtain an informational advantage. Using detailed transaction-level bond data that reveal who trades with whom, the authors measure investors' dealer networks and their trading performance around changes in credit fundamentals. They hypothesize that investors with larger networks—especially connections to dealers likely to see novel credit information—should trade profitably ahead of fundamental changes. The data show these investors do make superior, better-risk-adjusted trades before credit news, and the advantage is concentrated in information-rich connections. The paper concludes that trading networks are conduits for private information in OTC markets.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>An empirical network design using transaction-level corporate bond data (with dealer identities) to construct investors' dealer networks and relate network size/position to trading performance around credit-fundamental changes. The analysis links network characteristics to risk-adjusted returns and isolates information-rich connections; the unit of analysis is the investor (and trade). Identification of information flows comes from performance concentrated in connections where dealers likely hold novel information.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Market Microstructure, Information &amp; Networks, Fixed Income</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>FINRA — TRACE (enhanced, with dealer identifiers)</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting and Economics - 2026 - Huber et al. - Information flows in trading networks.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Hanlon et al. - Taxes and Competition Evidence from the airline industry</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Hanlon, Shroff, Yoon</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Taxes and Competition: Evidence from the airline industry</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>This paper examines whether corporate tax cuts alter product-market competition by differentially affecting firms with high versus low tax burdens. Because tax cuts raise after-tax cash flows for profitable firms but do little for loss-making firms, they can shift competitive positions. Studying the 1986 Tax Reform Act, which cut the top corporate rate by 12 percentage points, and route-level price and quantity data from U.S. airlines, the authors find that profitable airlines cut ticket prices by 4.2% relative to loss-making rivals and gain 3.3 percentage points of market share. The results show taxes affect not only firm value but also competitive dynamics. The paper documents a competition channel of corporate taxation.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>The paper argues that corporate taxes may reshape competition because a tax cut benefits profitable firms—who owe taxes—far more than loss-making firms, changing the two groups' relative cost positions. It uses the 1986 Tax Reform Act as a large, discrete cut in the top corporate tax rate, generating a differential shock across profitable and loss-making firms. The airline industry provides an ideal testing ground because route-level prices and quantities are observable, allowing precise measurement of competitive responses. The authors predict that after the Act, profitable airlines will use their improved after-tax cash flows to cut prices and gain share relative to loss-making rivals. The data confirm this: profitable airlines lower fares by 4.2% and gain 3.3 percentage points of market share relative to loss makers. The paper concludes that corporate taxation has real competitive consequences beyond its direct effect on firm value.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>A difference-in-differences design using the 1986 Tax Reform Act as a differential shock to profitable versus loss-making firms, applied to route-level price and quantity data from the U.S. airline industry. Profitable airlines (which benefit from the rate cut) are compared to loss-making rivals on prices and market share around the reform; the unit of analysis is the airline-route. Identification comes from the differential tax impact across firms.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Taxation, Industrial Organization, Competition</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Department of Transportation — DB1B (Airline Origin and Destination Survey)</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting and Economics - 2026 - Hanlon et al. - Taxes and Competition Evidence from the airline industry.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Weber et al. - SEC scrutiny and corporate risk-taking</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Weber, Xu, Zhang</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>SEC scrutiny and corporate risk-taking</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>This paper examines whether heightened SEC scrutiny of financial reporting affects corporate risk-taking. Tighter oversight could raise risk-taking by strengthening accounting's governance role, or reduce it by constraining managers' ability to shield themselves through earnings management. Using the SEC's 2007 elevation of six district offices to regional status—which expanded their authority and enforcement resources—in a difference-in-differences design, the authors identify the effect on firms in the affected jurisdictions. The results speak to how regulatory monitoring shapes managerial risk choices. The paper connects the geography of SEC enforcement to real corporate decisions.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>The paper poses a genuinely two-sided question: because managers are risk-averse and can hide poor outcomes through earnings management, stronger SEC oversight might either encourage risk-taking (by improving governance and reducing the payoff to concealment) or discourage it (by limiting managers' ability to manage earnings and thus their willingness to take risks). To adjudicate, it needs exogenous variation in scrutiny, which it finds in the SEC's 2007 reorganization that elevated six district offices to regional level, expanding their enforcement reach. Firms headquartered in the newly elevated offices' jurisdictions become treated, while others serve as controls. The authors compare risk-taking outcomes for treated versus control firms around the reorganization in a difference-in-differences framework. The estimated effect reveals which force dominates in practice. The paper interprets the result as evidence on how the intensity and reach of regulatory monitoring shapes corporate risk-taking.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>A difference-in-differences design exploiting the SEC's 2007 elevation of six district offices to regional status, which expanded their authority and enforcement resources, as a shock to local SEC scrutiny. Firms in the elevated offices' jurisdictions are treated and compared to firms elsewhere; outcomes are measures of corporate risk-taking. The unit of analysis is the firm; identification comes from the office reorganization's geographic variation.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Financial Regulation, Corporate Risk-Taking, Enforcement</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>SEC — Office jurisdictions / enforcement geography</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting and Economics - 2026 - Weber et al. - SEC scrutiny and corporate risk-taking.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Kim and Valentine - Earnings targets, strategic patent sales, and patent trolls</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Kim, Valentine</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Earnings targets, strategic patent sales, and patent trolls</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>This paper shows that innovative public firms sell significantly more patents in the last month of their fiscal year than earlier, consistent with reporting incentives driving these sales. Final-month sales are disproportionately internally generated, non-core patents with high potential accounting gains, and are more pronounced among firms with incentives to meet earnings expectations—especially when firms narrowly beat expectations and when executive incentives dominate. Managers also increase insider equity sales following these strategic patent sales. The paper documents earnings-motivated asset sales in the specific context of patents, some of which flow to patent-assertion entities. It links financial-reporting incentives to real decisions about intellectual property.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>The paper begins from the observation that firms can realize accounting gains by selling assets, and asks whether earnings incentives drive the timing and composition of patent sales. It documents a sharp increase in patent sales in the final month of the fiscal year, a pattern hard to reconcile with pure operating motives but consistent with meeting reporting targets. Examining which patents are sold, it finds they are disproportionately internally generated, non-core, and carry high potential accounting gains—exactly the assets useful for boosting reported earnings. The authors then show these sales concentrate among firms with strong incentives to hit earnings benchmarks, particularly narrow beaters and firms where executive incentives are salient. They further link the sales to subsequent insider equity sales, reinforcing the reporting-and-incentive interpretation. The paper concludes that financial-reporting incentives shape patent divestitures, with some patents ending up in the hands of patent-assertion entities.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>An empirical design documenting within-fiscal-year timing of patent sales and relating it to earnings-management incentives, using USPTO patent assignment (reassignment) records linked to firm financials and earnings-expectation data. Tests compare final-month versus earlier sales, characterize the patents sold, and split by benchmark-beating and executive-incentive proxies. The unit of analysis is the firm (and patent sale).</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Earnings Management, Innovation &amp; Intellectual Property, Financial Reporting</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>USPTO — Patent assignment (reassignment) records</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting and Economics - 2026 - Kim and Valentine - Earnings targets, strategic patent sales, and patent trolls.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Armstrong and Glaeser - Does taxpayer assistance encourage entrepreneurship</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Armstrong, Glaeser</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Does taxpayer assistance encourage entrepreneurship?</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>This paper examines whether help with tax filing and compliance affects entrepreneurship, focusing on IRS Taxpayer Assistance Centers that help taxpayers navigate the tax system. The authors find that Taxpayer Assistance Centers are positively associated with local entrepreneur entry and with overall Schedule C business income. They interpret this as evidence that assistance encourages traditional business entrepreneurship by reducing the compliance costs that stem from tax complexity. The paper highlights an underappreciated channel—tax administration and support—through which the tax system affects business formation. It connects the accessibility of tax assistance to real entrepreneurial activity.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>The paper starts from the idea that tax complexity imposes compliance costs that may deter people from starting businesses, and asks whether reducing those costs through assistance encourages entrepreneurship. It focuses on IRS Taxpayer Assistance Centers, which help taxpayers—including would-be entrepreneurs—file correctly and navigate tax rules. The authors reason that easier access to such help should lower the effective cost of entering self-employment and thus raise local business formation. They relate the presence of Taxpayer Assistance Centers to local entrepreneur entry and to Schedule C business income. Finding positive associations on both margins, they interpret assistance as lowering compliance barriers to entrepreneurship. The paper concludes that the administrative side of the tax system, not just tax rates, shapes business formation.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>An empirical design relating the local presence of IRS Taxpayer Assistance Centers to entrepreneurship outcomes, using IRS Statistics of Income Schedule C data and measures of local business entry. The analysis associates access to tax assistance with entrepreneur entry and business income across localities; the unit of analysis is the locality/area. The interpretation is that assistance reduces tax-compliance costs to entry.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Taxation, Entrepreneurship, Public Economics</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>IRS — Taxpayer Assistance Center locations; IRS — Statistics of Income (Schedule C)</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting and Economics - 2026 - Armstrong and Glaeser - Does taxpayer assistance encourage entrepreneurship.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Berger and Tomy - Supply chain shocks and firm productivity The role of reporting quality</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Berger, Tomy</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Supply chain shocks and firm productivity: The role of reporting quality</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>This paper studies how reporting quality shapes firms' responses to an adverse supply-chain shock, using the 1999 Taiwan earthquake that disrupted supply chains for certain U.S. high-technology manufacturers. Affected firms experience increases in total factor productivity relative to unaffected firms, and this effect is stronger when pre-shock reporting quality is higher. The findings suggest that better information helps firms restructure effectively after shocks, not just in routine decisions. The paper extends the literature on reporting quality from recurring operating choices to crisis-driven restructuring. It links accounting information quality to real productivity outcomes.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>The paper notes that prior work links reporting quality to routine operating and investing decisions but says little about its role when firms must restructure after an adverse shock. It uses the 1999 Taiwan earthquake as an exogenous disruption to the supply chains of specific U.S. high-technology manufacturers, creating affected and unaffected groups. The authors hypothesize that firms with higher pre-shock reporting quality have better internal information to reallocate resources and adapt, so they should recover or even improve productivity more. Comparing affected to unaffected firms, they find total factor productivity rises for affected firms, and more so where pre-shock reporting quality was higher. This pattern indicates that information quality is especially valuable precisely when firms face large, non-routine disruptions. The paper concludes that reporting quality has real effects that show up in how firms weather shocks.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>A difference-in-differences design using the 1999 Taiwan earthquake as an exogenous supply-chain shock, comparing exposed U.S. high-technology manufacturers to unexposed firms and interacting exposure with pre-shock reporting quality. The outcome is firm total factor productivity; the unit of analysis is the firm. Identification comes from the earthquake's disruption of specific supply chains.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Financial Reporting Quality, Supply Chains, Firm Productivity</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Supply-chain relationship data</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting and Economics - 2026 - Berger and Tomy - Supply chain shocks and firm productivity The role of reporting quality.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Miller et al. - Mandatory disclosure of investors' fossil fuel holdings</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Miller, Stockbridge, Williams</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory disclosure of investors' fossil fuel holdings</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>This paper examines whether mandatory disclosure of fossil-fuel investments changes investors' portfolios, using a 2016 California mandate that required some U.S. insurers to publicly disclose their fossil-fuel holdings. Disclosing insurers reduced fossil-fuel investments by roughly 20% relative to non-disclosers. The average effect masks substantial heterogeneity across insurers. The results show that requiring firms to reveal environmentally sensitive holdings can shift capital away from those assets. The paper provides causal evidence on how disclosure mandates affect institutional portfolios rather than just disclosure itself.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>The paper addresses a growing regulatory push to require investors to disclose fossil-fuel holdings, asking whether such disclosure changes behavior or is merely cosmetic. It uses a 2016 California mandate that applied to some U.S. insurers and made their fossil-fuel investments public, creating a treated group subject to disclosure and a comparison group that was not. The authors reason that if public scrutiny raises the cost of holding fossil-fuel assets, disclosing insurers should reduce those holdings relative to non-disclosers. Comparing the two groups around the mandate, they find a roughly 20% reduction in fossil-fuel investments by disclosers. They then explore heterogeneity, showing the response varies across insurers. The paper concludes that mandatory holdings disclosure can meaningfully reallocate institutional capital, with implications for climate-related disclosure policy.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>A difference-in-differences design exploiting a 2016 California mandate requiring some U.S. insurers to publicly disclose fossil-fuel investments, comparing disclosing insurers to non-disclosers around the mandate. Outcomes are insurers' fossil-fuel holdings and investment policies; the unit of analysis is the insurer. Identification comes from which insurers were subject to the disclosure requirement.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Sustainable Finance &amp; ESG, Disclosure Regulation, Institutional Investors</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>California / NAIC insurer disclosures — Fossil-fuel investment filings</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting and Economics - 2026 - Miller et al. - Mandatory disclosure of investors' fossil fuel holdings.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Leonelli et al. - How do consumers use ESG disclosure Evidence from a randomized field experiment with everyday product purchases</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Leonelli, Muhn, Rauter, Sran</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>How do consumers use ESG disclosure? Evidence from a randomized field experiment with everyday product purchases</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>This paper combines a large-scale field experiment with a customized survey of over 24,000 U.S. households to study how consumers use ESG disclosure. The authors first establish that while consumers moderately prefer ESG-responsible firms, they rarely consult corporate reporting directly and face frictions in learning about firm activities. In the experiment, households are randomly informed about real firm-disclosed activities, and consumers raise their purchase intent when exogenously shown positive ESG signals. The results show that ESG information can move consumer behavior, but only once frictions in accessing it are removed. The paper provides causal, individual-level evidence on the demand-side value of ESG disclosure.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>The paper starts from the debate over whether ESG disclosure actually matters to the consumers it is often meant to inform. It first documents, via survey, that consumers say they prefer responsible firms but seldom read corporate reports and struggle to learn what firms actually do, implying an information friction rather than an absence of preferences. This motivates an experiment that removes the friction by exogenously delivering real firm-disclosed ESG information to randomly selected households. The authors predict that if the friction is what suppresses ESG-based choice, then providing information should raise purchase intent for firms with positive disclosures. The experiment confirms this, with purchase intent rising when households receive positive ESG signals. The paper concludes that ESG disclosure has demand-side value that is latent until consumers are actually exposed to the information.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>A randomized field experiment paired with a customized survey of more than 24,000 U.S. households. The survey establishes baseline preferences and frictions, and the experiment randomly assigns households to information treatments that reveal real firm-disclosed ESG activities, identifying the causal effect on purchase intent. The unit of analysis is the household; identification comes from the random assignment of ESG information.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Sustainable Finance &amp; ESG, Disclosure, Consumer Behavior</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Authors' field experiment and survey</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Accounting and Economics - 2026 - Leonelli et al. - How do consumers use ESG disclosure Evidence from a randomized field experiment with ev.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Kaviani et al. - Reaching for influence Do banks use loans to establish political connections</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Kaviani, Maleki, Savor</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Reaching for influence: Do banks use loans to establish political connections?</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>This paper asks whether U.S. banks lend on favorable terms to firms with political ties in order to buy influence, using close congressional elections for identification. Firms connected to members of Congress receive more favorable loan terms despite no observable improvement in performance or default risk. The effect is strongest among banks facing regulatory challenges—FDIC enforcement actions, misconduct investigations, or low Community Reinvestment Act ratings—which also lend more often to connected firms, suggesting a heightened demand for influence. Politically motivated lending yields tangible benefits for banks, including reduced misconduct penalties and easier M&amp;A approval. The paper documents a channel through which banks convert lending into political capital.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>The paper starts from the idea that banks, which are heavily regulated, may value political influence and could try to acquire it by lending cheaply to politically connected firms. To identify politically motivated lending, it uses close elections, where whether a firm's favored candidate barely wins or loses is close to random, generating quasi-exogenous variation in a firm's political connections. It first shows that firms newly connected to winning members of Congress receive better loan terms even though their fundamentals do not improve, indicating the favorable terms reflect influence-seeking rather than credit quality. It then asks which banks do this most, finding that banks under regulatory pressure lend more to connected firms, consistent with their greater demand for political protection. Finally, it tests whether this pays off, showing connected lending is followed by reduced penalties and easier merger approvals. The paper concludes that banks strategically use loans to build political connections that yield regulatory benefits.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>A regression-discontinuity-style design around close congressional elections, using the narrow victory or defeat of a firm's connected candidate as quasi-random variation in political connections. The authors compare loan terms to connected versus non-connected firms and test heterogeneity by banks' regulatory pressure (FDIC actions, misconduct investigations, CRA ratings), then relate connected lending to later bank outcomes (penalties, M&amp;A approvals). The unit of analysis is the loan/firm-bank; identification comes from the close-election discontinuity.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Banking, Political Economy &amp; Finance, Corporate Governance</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Refinitiv LPC — DealScan; Close-election and political-connection data; Bank regulatory records</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Financial Economics - 2026 - Kaviani et al. - Reaching for influence Do banks use loans to establish political connections.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Lindsey and Stein - Angels, entrepreneurship, and employment dynamics Evidence from investor accreditation rules</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Lindsey, Stein</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Angels, entrepreneurship, and employment dynamics: Evidence from investor accreditation rules</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>This paper examines how a shock to the supply of angel finance affects entrepreneurship, using Dodd-Frank's removal of housing wealth from the definition of an accredited investor. Using U.S. Census data, the authors estimate the state-level fraction of households that lost accreditation and show that larger reductions in the investor pool reduce angel investment, firm entry, and employment at small entrants. Employment rises at small and young incumbents, suggesting competitive effects, and angel finance appears to complement other capital sources despite partial substitution. The paper provides causal evidence on the real effects of angel finance and where it matters most.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>The paper studies angel investors, an important but hard-to-observe source of early-stage capital, and asks what happens to entrepreneurship when their supply shrinks. It exploits a specific rule change: Dodd-Frank stopped counting housing wealth toward the wealth threshold that defines an accredited (eligible angel) investor, which pushed some households below the threshold. Because house values differ across places, the fraction of households losing accreditation varies by state, generating quasi-exogenous cross-state variation in the angel-investor pool. The authors predict that a larger reduction in potential angels lowers angel investment, firm entry, and employment at small new firms. Using Census data, they confirm these effects, and additionally find employment rising at small and young incumbents, consistent with reduced entry easing competition. Documenting partial substitution toward other capital, they conclude angel finance complements rather than merely substitutes for other funding in the entrepreneurial ecosystem.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>A quasi-experimental design exploiting Dodd-Frank's removal of housing wealth from accredited-investor eligibility, which reduced the angel-investor pool differentially across states depending on local house values. Using confidential U.S. Census firm and employment data, the authors relate state-level exposure (the fraction of households losing accreditation) to angel investment, firm entry, and employment at entrants and incumbents. The unit of analysis is the state/firm; identification comes from cross-state variation in exposure to the rule change.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Finance, Firm Dynamics, Financial Regulation</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Census Bureau — Longitudinal Business Database / firm microdata; Angel investment and accreditation data</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Financial Economics - 2026 - Lindsey and Stein - Angels, entrepreneurship, and employment dynamics Evidence from investor accreditation rul.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Woeppel and Yavuz - Measuring firms' capability to absorb external knowledge</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Woeppel, Yavuz</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Measuring firms' capability to absorb external knowledge</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>This paper builds a measure of firms' capability to benefit from external knowledge—'absorption intensity'—from information in their patents. To validate it, the authors exploit the American Inventors Protection Act (AIPA), which exogenously increased the availability of patent information, in a triple-difference design: firms with higher absorption intensity see greater innovation growth when more exposed to the reform. Beyond AIPA, absorption intensity predicts stronger innovation outcomes and firm growth. The measure offers a tool to study how differences in absorptive capability shape the returns to external knowledge. It contributes a patent-based proxy for a concept that was previously hard to measure.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>The paper argues that as the economy becomes knowledge-based, a firm's ability to absorb and use external knowledge is increasingly important, yet this absorptive capability is hard to measure. The authors propose to infer it from patents, constructing an 'absorption intensity' measure that captures how well a firm draws on outside knowledge. To show the measure is meaningful rather than mechanical, they need a setting where the value of absorptive capability changes exogenously. AIPA, which increased the disclosure of patent information, provides such a shock: firms better able to absorb external knowledge should benefit more when more information becomes available. A triple-difference design comparing high- and low-absorption firms by exposure to AIPA confirms that high-absorption firms experience greater innovation growth. The paper then shows absorption intensity predicts innovation and growth more broadly, establishing it as a useful, validated proxy.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>A measurement paper validated with a triple-difference design around the American Inventors Protection Act (AIPA), which exogenously increased patent-information availability. The absorption-intensity measure is built from patent data, and the triple difference compares high- versus low-absorption firms with greater versus lesser exposure to the reform, before versus after. Broader predictive regressions relate the measure to innovation and firm growth; the unit of analysis is the firm-year.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Innovation &amp; Intellectual Property, Corporate Finance, Firm Growth</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>KPSS patent value database — Kogan, Papanikolaou, Seru &amp; Stoffman (2017); USPTO patent data</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Financial Economics - 2026 - Woeppel and Yavuz - Measuring firms' capability to absorb external knowledge.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Benguria et al. - Trade credit and relationships</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Benguria, Garcia-Marin, Schmidt-Eisenlohr</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Trade credit and relationships</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>This paper uses transaction-level international trade data to show that long-term firm-to-firm relationships facilitate the use of trade credit. The strength of this effect varies with firm size, payment delays, and multinational-affiliate status, and depends on the strength of contract enforcement across countries and the complexity of traded products. Because trade credit substitutes for borrowing from the financial sector, long-term relationships can reduce firms' external credit demand. A corollary is that destroying trade relationships—for example through trade conflicts—may raise firms' leverage. The paper connects relationship lending in trade to firms' financing needs.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>The paper begins from the observation that firms often finance trade through credit extended by their trading partners rather than by banks, and asks what determines the use of such trade credit. It proposes that repeated, long-term relationships between buyers and sellers build the trust and information needed to extend credit, so relationship length should predict trade-credit use. Using detailed transaction-level trade data, it tests whether longer relationships are associated with more trade credit and how this varies with firm characteristics. It then examines institutional moderators, showing the effect is stronger where contract enforcement is weaker and products are more complex, consistent with relationships substituting for formal enforcement. Because trade credit can replace bank borrowing, the paper draws the implication that relationships reduce firms' demand for external finance. It concludes that shocks that sever trade relationships, such as trade conflicts, could push firms back toward bank debt and raise leverage.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>A descriptive/reduced-form design using transaction-level (customs) international trade data to relate the length of firm-to-firm trading relationships to the use of trade credit, with heterogeneity by firm size, payment delays, and multinational status. Institutional interactions use cross-country contract-enforcement measures and product-complexity classifications. The unit of analysis is the firm-to-firm trade transaction.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Trade Credit &amp; Financing, International Finance, Firm Financing</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Transaction-level international trade (customs) data; Contract-enforcement and product-complexity measures</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Financial Economics - 2026 - Benguria et al. - Trade credit and relationships.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Fisman et al. - Dirty air and green investments The impact of pollution information on portfolio allocations</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Fisman, Ghosh, Sen</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Dirty air and green investments: The impact of pollution information on portfolio allocations</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>This paper asks whether access to local pollution information causes investors to make greener portfolio choices, exploiting the staggered rollout of air-quality monitoring stations across India. Using a triple-differences design on the trading records of 19 million retail investors, the authors show that holdings in 'brown' (high-pollution) stocks become more negatively related to local pollution once a nearby monitoring station appears. The effect is stronger on 'alert' dates when air quality is reported harmful, among tech-savvy investors likely exposed to real-time data, and among younger investors. The results show that making environmental information salient shifts capital away from polluting firms. The paper links information provision to sustainable investing behavior.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>The paper starts from the idea that investors may want to avoid polluting firms but lack salient, local information about pollution, so providing it should change behavior. Air-quality monitoring stations, rolled out at different times across Indian locations, make local pollution observable and are used as a source of quasi-exogenous variation in information access. The authors reason that if information drives green investing, retail holdings in brown stocks should become more negatively related to local pollution after a nearby station appears, and especially on days when pollution is reported harmful. A triple-differences design compares brown-stock holdings, across investors near versus far from new stations, before versus after, and on alert versus normal days. Finding the predicted patterns—strongest for tech-savvy and younger investors—they conclude that salient pollution information causally shifts portfolios. The paper interprets this as evidence that information frictions, not just preferences, shape sustainable investment.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>A triple-differences design exploiting the staggered rollout of air-quality monitoring stations across India as quasi-exogenous variation in local pollution information, estimated on the trading records of 19 million retail investors. The comparison combines proximity to a new station, timing before/after, and 'alert' versus normal pollution days, with heterogeneity by investor tech-savviness and age. The unit of analysis is the investor-stock-time; identification comes from the station rollout.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Sustainable Finance &amp; ESG, Household Finance, Information &amp; Markets</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Indian retail investor trading records; Central Pollution Control Board (India) — Air-quality monitoring stations</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Financial Economics - 2026 - Fisman et al. - Dirty air and green investments The impact of pollution information on portfolio allocations.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Goldstein et al. - Market feedback Evidence from the horse's mouth</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Goldstein, Liu, Yang</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Market feedback: Evidence from the horse's mouth</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>This paper uses near-population surveys of Chinese public firms (2019 and 2022, via the CSRC, ~99% response) to provide direct evidence on whether and how the stock market affects firms, focusing on the contested learning channel. Over 90% of firms monitor the market, and the two most common reasons are learning new information relevant to investment and dependence on prices for financing. Firms that report learning have characteristics implying greater benefit and show higher investment-to-price sensitivity. The paper documents which information dimensions firms learn about and links learning to better M&amp;A outcomes and fewer trading suspensions. It offers rare direct evidence on the real effects of markets.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>The paper situates itself in the debate over the real effects of markets, distinguishing a financing channel from a learning channel whose existence is hard to identify because information sets are unobservable. Rather than infer learning indirectly, the authors ask managers directly through near-population surveys, establishing that monitoring is widespread and that learning and financing dominate. They then open the black box of what information is learned, a dimension prior work largely could not address. To counter the concern that survey answers are noise, they derive and test predictions about which firm characteristics should predict learning. They further test whether reported learning maps into real actions—investment-to-price sensitivity, M&amp;A performance, and trading suspensions. Finding that responses line up with characteristics and behavior, they argue the survey evidence is credible and that learning from prices materially shapes firm decisions.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>A survey-based, direct-evidence design using two rounds of near-population firm surveys, validated with cross-sectional Probit models linking responses to firm characteristics and panel investment-to-price sensitivity regressions, plus M&amp;A and trading-suspension tests. The unit of analysis is the firm; credibility comes from tying stated learning to observable characteristics and subsequent actions.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Real Effects of Financial Markets, Corporate Investment, Survey Methods in Finance</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>CSMAR — China Stock Market &amp; Accounting Research; WIND; CSRC &amp; Tsinghua PBCSF — Survey of Chinese public firms (2019, 2022)</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Financial Economics - 2026 - Goldstein et al. - Market feedback Evidence from the horse's mouth.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Goyal, Wahal, Yavuz</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Picking partners: Manager selection in private markets</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>This paper studies how limited partners select private-market managers across more than 61,000 commitments (1995-2019) by constructing feasible 'opportunity sets.' LPs chase past performance but are strikingly willing to back first-time or young GPs: the probability of selecting a first-time GP is about as high as selecting a top-quartile GP, even though first-time funds earn lower expected and realized returns. After ruling out expected performance, lottery preferences, star-fund access, and co-investment, the authors show the main driver is pressure to invest as private-market allocations grow. The paper reframes manager selection around demand and supply rather than skill.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>The paper frames manager selection as a discrete-choice problem whose central difficulty is that the feasible choice set is unobserved, which it resolves by constructing opportunity sets from institutional detail, interviews, and investment-policy statements. Estimating selection against these sets, it documents robust performance chasing alongside a high propensity to pick first-time and young GPs. It then eliminates candidate explanations, showing first-time GPs do not deliver higher expected or realized returns, greater skewness, privileged access to later star funds, or more co-investment. Having ruled these out, it develops a demand-supply account and constructs a measure of pressure to invest. It shows LPs facing high pressure move down the performance ladder toward first-time GPs. The paper concludes that excess demand for private-market exposure, met by new GP entry, explains the willingness to back unproven managers.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Discrete-choice selection modeling (conditional logit and linear-probability specifications) estimated on curated LP-year opportunity sets with two-way exclusion restrictions ('feasible-set shifters'). Robustness comes from alternative opportunity-set constructions, Heckman selection for missing performance, and expected-performance estimation. The unit of analysis is the LP-fund choice within a feasible set.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Private Equity &amp; Venture Capital, Institutional Investors &amp; Asset Management, Manager Selection</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Preqin; CEM Benchmarking; Institute for Private Capital — Failed-fund data; SEC — Form D filings; RelSci; Fundmap</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Cassella et al. - Constrained by law The impact of fiduciary duties on portfolios and prices in US equity markets</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Cassella, Rizzo, Spalt, Zimmerer</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Constrained by law: The impact of fiduciary duties on portfolios and prices in US equity markets</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>This paper studies how a change in trust fiduciary law reshaped institutional portfolios and equity prices. The Uniform Prudent Investor Act (UPIA), adopted by U.S. states in staggered fashion from 1985 to 2006, replaced asset-by-asset prudent-man rules with a portfolio-level prudent-investor standard. The authors show trusts tilted toward 'prudent' stocks before the reform and undid these tilts after adoption, improving trust risk-return. Consistent with inelastic markets, the demand shift moved relative prices, implying demand elasticities between 0.10 and 0.36. The paper documents a decades-long, law-induced investment distortion and adds novel estimates of equity demand elasticity.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>The paper contrasts the diversification prescriptions of modern portfolio theory with prudent-man laws that forced trustees to justify each holding in isolation, creating a binding tilt toward 'prudent' stocks. A CARA-normal model with trust managers facing a prudence-tilted benchmark yields three predictions: regulatory tilts before UPIA, an unwinding after UPIA, and price changes under inelastic markets. Because UPIA was adopted state-by-state and applies only to trusts, the design compares trusts to other institutions within state and time. The empirical sections move from holdings, to risk-return consequences, to relative prices. Finding that trusts undid their tilts and that prices moved as predicted, the authors back out demand elasticities from the regulation-induced demand shock. The result ties a legal constraint to portfolio behavior and to the inelasticity of equity markets.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Staggered difference-in-differences exploiting state-level UPIA adoption, supported by a CARA-normal inelastic-markets model. The design uses investor and state-by-quarter fixed effects and the Sun-Abraham estimator for heterogeneous treatment effects; Fama-French five-factor tests measure risk-return changes and an instrumented demand system recovers elasticities. The unit of analysis is the institution-stock-quarter; identification comes from the timing of UPIA across states.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Investors &amp; Asset Management, Demand-Based Asset Pricing, Law and Finance</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>DeVault, Sias &amp; Starks (2019) — Institutional classification (57 types); FDIC / WestLaw — UPIA adoption dates</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Financial Economics - 2026 - Cassella et al. - Constrained by law The impact of fiduciary duties on portfolios and prices in US equity mark.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Hvide and Nielsen - Flying below the radar Insider trading by executives below the top</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Hvide, Nielsen</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Flying below the radar: Insider trading by executives below the top</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>This paper studies whether executives just below the reportable-insider threshold trade profitably on material inside information, using Norwegian administrative register data on the population of trades. It finds abnormal returns of roughly 50-100 basis points at the one-month horizon on these executives' own-company purchases, rising over longer horizons. Because the same individuals earn no abnormal returns on non-inside or same-industry purchases, general stock-picking skill and industry knowledge are ruled out. The evidence indicates that a broad group of executives beyond top management trades on material information that escapes mandatory disclosure. It is the first transaction-level test of below-the-top executives trading on inside information.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>The paper begins from the regulatory design that requires only primary insiders to disclose own-company trades, leaving below-the-top executives unmonitored despite their proximity to inside information. Whether they actually trade on that information is posed as an open question, since they might instead buy own-company stock out of familiarity or loyalty, which would not generate abnormal returns. Using positional codes to isolate below-the-top executives, the authors compare returns on their inside versus non-inside trades. Crucially, they benchmark inside purchases against the same individuals' other trades to net out ability and industry knowledge. Finding abnormal returns only on inside purchases, they conclude these executives trade on material information. The paper extends the analysis to indirect trades and job changes to interpret the source of the returns.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Long-run abnormal-return estimation on administrative (population) register data using a control-firm bootstrap and a calendar-time Carhart four-factor portfolio approach, with individual-specific benchmarks that difference out stock-picking ability. The unit of analysis is the individual trade; identification of information-based trading comes from comparing inside purchases to the same person's non-inside and same-industry purchases.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Insider Trading, Financial Regulation, Empirical Asset Pricing</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Norwegian Central Securities Depository (VPS); Statistics Norway — Employer-employee register (ISCO-88); Oslo Stock Exchange; Norwegian registers (LLC ownership; population)</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Financial Economics - 2026 - Hvide and Nielsen - Flying below the radar Insider trading by executives below the top.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language models</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Acikalin, Caskurlu, Hoberg, Phillips</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Intellectual property protection lost and competition: An examination using large language models</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>This paper examines who gains and who loses when intellectual-property protection is broadly weakened, using the 2014 Alice v. CLS Bank Supreme Court decision that invalidated many business-method patents. The authors use a large language model (ModernBERT) to score each firm's pre-Alice patents for their exposure to the decision and build a firm-level treatment. Using difference-in-differences with entropy balancing, they find an unequal impact: large firms gain while small firms lose. Small treated firms face more venture-backed entry, product-market encroachment, more litigation, and lower profits and valuations, and respond by raising R&amp;D and nondisclosure. The paper contributes both an LLM-based method for measuring legal shocks and evidence that patents matter most for small firms.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>The paper enters the long debate over whether patents help or hinder innovation by treating the Alice decision as a broad, technology-area-wide weakening of IP rather than the loss of a single rival's patent. Because the ex-post fate of any patent is uncertain, the authors argue a language model is needed to gauge each patent's similarity to those invalidated under Alice, yielding a continuous firm-level exposure measure. They hypothesize, following leader-versus-laggard logic, that smaller firms with fewer resources and weaker barriers to entry are hurt more, while larger firms defend their positions. These hypotheses generate predictions about differential effects on patenting, competition, performance, valuation, and litigation. The empirical design then tests each prediction, and the pattern of small-firm losses and large-firm gains supports the view that IP protection disproportionately shields smaller innovators. The paper closes by drawing out the policy implication that uniform changes in patent strength have highly unequal effects across firm size.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>A continuous-treatment difference-in-differences design exploiting the Alice Supreme Court decision as a quasi-exogenous shock, with entropy balancing for covariate balance and firm/year fixed effects. The treatment is constructed from a fine-tuned ModernBERT model applied to patent text, validated against USPTO post-grant reviews. Effects on innovation, competition, performance, valuation, and litigation are compared across small and large treated firms; the unit of analysis is the firm-year.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Innovation &amp; Intellectual Property, Industrial Organization, Machine Learning in Finance</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>KPSS patent value database — Kogan, Papanikolaou, Seru &amp; Stoffman (2017); USPTO — Patent application office actions; Hoberg-Phillips — TNIC; Stanford NPE Litigation Database / PACER; Unified Patents — Post-grant review data; Venture Expert (Refinitiv)</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language mo.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Lu and Wu - Banking on Inattention</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Lu, Wu</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Banking on Inattention</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>This paper argues that depositor inattention is a source of banks' deposit market power. The authors develop a model in which inattentive depositors adjust their balances sluggishly to changes in deposit rates, allowing banks to pay rates that respond incompletely to the policy rate and to earn rents on deposits. Using transaction-level evidence together with Call Reports and the FDIC Summary of Deposits, they show that more inattentive depositors adjust balances less and that this inattention maps into weaker deposit-rate pass-through. The framework links a behavioral friction—limited attention—to bank funding costs and the transmission of monetary policy. It implies that inattention, not just market concentration, underpins deposit market power.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>The paper begins from the puzzle that bank deposit rates respond only partially to the policy rate, which is usually attributed to market concentration, and proposes an alternative, behavioral source: depositor inattention. It builds a model in which depositors do not continuously monitor deposit rates and therefore adjust their balances sluggishly, so banks can widen the spread between the policy rate and the deposit rate without losing funds quickly. In this setting, inattention directly generates deposit market power and incomplete pass-through, independent of how concentrated the market is. The authors then bring evidence to bear, using transaction-level data to show that more inattentive depositors move their balances less in response to rate changes, and linking this to aggregate patterns in Call Reports and the FDIC Summary of Deposits. The empirical mapping from inattention to weaker pass-through supports the model's central mechanism. The paper concludes that limited attention is a key micro-foundation for banks' deposit franchise and matters for how monetary policy transmits through deposits.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>A theoretical model of depositor inattention generating deposit market power and incomplete deposit-rate pass-through, combined with empirical evidence. The empirical work uses transaction-level data to measure how depositor inattention relates to balance adjustment and pass-through, with U.S. Call Reports and the FDIC Summary of Deposits used for aggregate deposit sizes and branch-level patterns. Identification of the mechanism comes from relating measured inattention to the sensitivity of balances and deposit rates rather than from a single external shock.</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Banking, Monetary Economics, Household Finance</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>FDIC — Summary of Deposits; Proprietary transaction-level data provider</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Lu and Wu - Banking on Inattention.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Argyle et al. - The Dynamics of Retail Deposit Balances</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Argyle, Iverson, Kotter, Nadauld, Palmer</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>The Dynamics of Retail Deposit Balances</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>This paper uses transaction-level data on retail deposit accounts to study how households manage their deposit balances. The authors document substantial skewness and inertia in balances, with many depositors holding large amounts—including balances above the FDIC insurance limit—and adjusting slowly to interest-rate incentives. They identify notches at product-specific thresholds (such as service or rate tiers) and show how balances bunch and respond around them. These patterns imply that retail deposits are stickier and less rate-sensitive than frictionless models assume, with implications for banks' funding costs and market power. The paper provides granular evidence on the microstructure of household deposit behavior.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>The paper motivates that retail deposits are a huge and stable source of bank funding, yet how individual households actually manage their balances is not well documented at the transaction level. Using granular account data, the authors first characterize the distribution of balances, finding it highly skewed, with a large share of deposits held by high-balance depositors and substantial amounts above the FDIC insurance limit. They then examine dynamics, showing that balances are inert and adjust slowly to interest-rate incentives, contrary to models in which depositors quickly chase yield. To sharpen the analysis, they exploit product-specific notches—thresholds at which the interest rate or services change—and study how balances bunch and respond around them, which reveals the frictions governing deposit adjustment. These patterns imply that deposits are stickier and less rate-elastic than standard assumptions, giving banks funding stability and pricing power. The paper draws out implications for how deposit inertia shapes banks' funding costs and the transmission of interest rates.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>An empirical, descriptive study using proprietary transaction-level retail deposit account data to characterize the distribution and dynamics of household deposit balances. The authors document skewness and inertia and use product-specific notches (thresholds where rates or services change) as a bunching/quasi-experimental design to identify how balances respond to incentives. The unit of analysis is the account over time; regulatory data (Call Reports, FDIC) are used to benchmark aggregate patterns.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Household Finance, Banking, Deposits</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary retail deposit data provider</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2026 - Argyle et al. - The Dynamics of Retail Deposit Balances.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Review of Economic Studies - 2026 - Ivanov et al. - Taxes Depress Corporate Borrowing Evidence from Private Firms</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Review of Economic Studies</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Ivanov, Pettit, Whited</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Taxes Depress Corporate Borrowing: Evidence from Private Firms</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>This paper uses variation in U.S. state corporate income tax rates to re-examine how taxes affect corporate leverage, focusing on small private firms. Contrary to prior research, the authors find that corporate leverage rises after tax cuts for these firms. An estimated dynamic equilibrium model explains why: tax cuts make capital more productive and spur investment financed partly with debt, and they push default thresholds further away, making borrowing safer. The combination overturns the standard prediction that lower taxes reduce the debt tax shield and hence leverage. The paper shows that for financially constrained private firms, the investment and risk channels of taxes dominate the classic tax-shield channel.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>The paper revisits the textbook relationship between taxes and leverage, where higher tax rates raise the value of the interest tax shield and should therefore increase debt, a prediction that has received mixed empirical support. The authors focus on small private firms, for which financing frictions and investment responses may reshape the tax–leverage link, and exploit changes in state corporate income tax rates as variation in the tax environment. Empirically, they find the opposite of the standard prediction: leverage rises after tax cuts for these firms. To interpret this, they build and estimate a dynamic equilibrium model in which taxes affect not only the debt tax shield but also the productivity of capital and the firm's distance to default. In the model, a tax cut raises the return to investing, and firms fund the extra investment partly with debt, while the improved cash flows move the default threshold further away and make additional borrowing safer. These investment and risk channels dominate the tax-shield channel for constrained private firms, producing the observed rise in leverage after tax cuts and reconciling the evidence with theory.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>A reduced-form design exploiting staggered changes in U.S. state corporate income tax rates (and tax-base rules) to estimate their effect on the leverage of small private firms, combined with an estimated dynamic equilibrium (structural) model of firm investment and financing. The reduced-form estimates identify the sign of the tax–leverage relationship from cross-state, over-time tax variation, and the structural model decomposes the response into tax-shield, capital-productivity, and default-risk channels. Confidential bank-reported loan-level data on commercial and industrial loans provide firm borrowing outcomes.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Finance, Taxation, Capital Structure</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Federal Reserve — FR Y-14 supervisory data; State corporate income tax data</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Review of Economic Studies - 2026 - Ivanov et al. - Taxes Depress Corporate Borrowing Evidence from Private Firms.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Review of Economic Studies - 2026 - Miranda-Agrippino et al. - Patents, News, and Business Cycles</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Review of Economic Studies</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Miranda-Agrippino, Hacıoğlu-Hoke, Bluwstein</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Patents, News, and Business Cycles</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>This paper builds a new instrument for technology news shocks—anticipated future improvements in productivity—using information contained in patent applications. The instrument relaxes the identifying assumptions traditionally used to recover news shocks and, by construction, isolates shocks that have no immediate effect on aggregate productivity. Embedding the instrument in a structural VAR, the authors trace how technology news propagates through the economy and drives business-cycle fluctuations. They find news shocks are an important source of aggregate dynamics. The paper contributes a patent-based identification strategy that sidesteps the fragilities of earlier approaches to measuring news shocks.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>The paper addresses a core difficulty in the news-shock literature: news about future productivity is hard to identify because it does not move current productivity, and existing approaches rely on strong and contestable identifying assumptions. The authors propose that patent applications contain forward-looking information about coming technological improvements, and can therefore be used to build an instrument for technology news. They construct this instrument so that it captures anticipated future productivity gains while having, by design, no contemporaneous effect on aggregate productivity, which is exactly the signature of a news shock. Plugging the instrument into a structural VAR with rich macro aggregates, they identify the dynamic response of the economy to technology news without imposing the traditional restrictions. The estimated responses show that news shocks generate meaningful business-cycle comovement, supporting the view that expectations about future technology matter for fluctuations. The paper thus both provides a cleaner identification tool and reinforces the empirical relevance of news-driven cycles.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>An instrumental-variables / structural-VAR design in which an external instrument for technology news shocks is constructed from patent-application data (via the NBER-USPTO historical patent files). The instrument is built to capture anticipated future productivity while having no contemporaneous productivity effect, and is used to identify news shocks in a VAR without the traditional identifying restrictions. The analysis is macro time-series; identification comes from the patent-based instrument's relevance and its exogeneity to current productivity.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Macroeconomics, Business Cycles, Innovation</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>NBER–USPTO — Historical Patent Data Files (Marco et al. 2015)</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Review of Economic Studies - 2026 - Miranda-Agrippino et al. - Patents, News, and Business Cycles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Review of Economic Studies - 2026 - Cullen et al. - What's My Employee Worth The Effects of Salary Benchmarking</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Review of Economic Studies</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Cullen, Li, Perez-Truglia</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>What's My Employee Worth? The Effects of Salary Benchmarking</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>This paper studies salary benchmarking—firms using aggregated market-salary data to set pay. Using national payroll data, the authors examine firms that gain access to a tool revealing market benchmarks for each job title, and use a difference-in-differences design around that access. They find the benchmark information reduces within-firm salary dispersion by about 25%, as firms move pay toward the market rate for each role. The results show that widely available wage information meaningfully compresses pay differences rather than simply raising or lowering wages. The paper documents a concrete channel through which information affects wage setting and dispersion.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>The paper begins with the observation that firms increasingly use aggregated market-salary data—salary benchmarking—to set pay, and asks how access to such information changes wage-setting. It frames the question around a tool that gives firms market benchmarks for each specific job title, so the relevant information is granular and directly usable in pay decisions. Exploiting the timing of when firms gain access to this tool, the authors set up a difference-in-differences comparison between firms that adopt it and otherwise similar firms that have not yet done so. They predict that benchmarking pulls each firm's pay for a given role toward the market rate, which should compress the spread of salaries within the firm rather than uniformly shift them. The data confirm a roughly 25% reduction in salary dispersion following access, consistent with firms anchoring on role-specific benchmarks. The paper interprets this as evidence that market wage information is a powerful force compressing pay differences, with implications for inequality and for debates over the transparency of compensation data.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>A difference-in-differences design exploiting the staggered timing with which firms gain access to a salary-benchmarking tool that reveals market pay by job title, estimated on national payroll data. Treated firms (which adopt the tool) are compared to not-yet-treated firms, with outcomes measured as within-firm salary dispersion and pay relative to market benchmarks by O*NET job code. The unit of analysis is the firm (and job title within firm) over time; the identifying variation is the change in information availability at adoption.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Labor Economics, Personnel Economics, Wage Inequality</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Compensation-software provider (national payroll)</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Review of Economic Studies - 2026 - Cullen et al. - What's My Employee Worth The Effects of Salary Benchmarking.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Review of Economic Studies - 2026 - Dempsey - Capital Requirements with Non-Bank Finance</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Review of Economic Studies</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Dempsey</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Capital Requirements with Non-Bank Finance</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>This paper quantitatively analyzes the macroeconomic effects of raising bank capital requirements in a model where heterogeneous firms can choose between intermediated (bank) and direct (bond-market) finance. Banks compete with each other and with the bond market, fund loans with insured deposits and costly equity subject to a minimum capital ratio, and monitor borrowers. Tighter capital requirements reduce costly bank failures but, because firms can substitute toward direct finance, have only small effects on aggregate lending and output. The availability of non-bank finance thus dampens the real costs of higher capital requirements. The paper shows that ignoring the bank–bond substitution margin overstates the output cost of bank regulation.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>The paper starts from the policy debate over how costly higher bank capital requirements are for the real economy, noting that standard analyses often hold fixed the set of firms that borrow from banks. It builds a quantitative general-equilibrium model in which heterogeneous firms endogenously choose between bank loans and bond-market finance, and in which banks fund themselves with insured deposits and costly equity and must satisfy a capital requirement. Because firms can substitute toward direct finance when bank credit becomes more expensive, the model creates a margin absent from bank-only frameworks. Raising the capital requirement makes bank funding costlier and reduces bank lending, but much of the affected borrowing migrates to the bond market rather than disappearing, so aggregate lending and output fall only modestly. At the same time, higher capital buffers reduce the incidence of costly bank failures, generating a stability benefit. Weighing these forces, the model implies that accounting for non-bank finance substantially lowers the estimated output cost of tighter capital requirements relative to bank-only models.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>A quantitative (structurally calibrated) general-equilibrium model with heterogeneous firms that endogenously choose between bank and bond finance and heterogeneous banks subject to capital requirements, deposit funding, and costly equity. The model is calibrated to standard macro-financial targets and used for counterfactual experiments that raise capital requirements and trace the effects on bank failures, the bank–bond financing mix, aggregate lending, and output. There is no external natural experiment; identification of the mechanism comes from the model's structure and the endogenous financing-choice margin.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Banking, Macro-Finance, Financial Regulation</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Quantitative model calibrated to standard aggregates; no distinctive datasets.</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Review of Economic Studies - 2026 - Dempsey - Capital Requirements with Non-Bank Finance.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly Journal of Economics - 2026 - Bostanci and Ordoñez - Business, Liquidity, and Information Cycles</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly Journal of Economics</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Bostanci, Ordoñez</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Business, Liquidity, and Information Cycles</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>This paper studies the dual role of stock markets as both a source of information about firm fundamentals and a source of liquidity, and shows these roles interact. When stocks are used more intensively for liquidity, their prices reveal less information about fundamentals, worsening resource allocation. The authors structurally estimate stock price informativeness for several countries and document that it declines when alternative liquidity sources contract and stocks are used more for liquidity. They embed this mechanism in a model linking business, liquidity, and information cycles. The framework connects financial-market liquidity conditions to the real economy through the informativeness of prices.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>The paper begins by noting that stock markets serve two functions economists usually study separately: they aggregate information that guides real investment, and they provide liquid assets that agents can trade when they need cash. The authors argue these functions are in tension, because trading motivated by liquidity needs is uninformed and, when it grows, dilutes the information content of prices. They formalize a setting in which the intensity of liquidity-motivated trading endogenously reduces how much prices reveal about fundamentals, so liquidity and information become linked. To take this to data, they structurally estimate price informativeness across several countries and show it falls precisely when alternative liquidity sources dry up and stocks are used more for liquidity. This co-movement supports the model's central prediction that liquidity and information cycles are connected. The paper concludes that fluctuations in market liquidity feed into the real economy by changing the informativeness of prices and hence the quality of investment decisions.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>A theoretical model in which liquidity-motivated trading endogenously lowers stock price informativeness, combined with structural estimation of price informativeness across several countries. The structural estimates are related to measures of alternative liquidity availability to test the model's prediction that informativeness falls when stocks are used more intensively for liquidity. The analysis is cross-country and structural rather than based on a single natural experiment; the unit of analysis is the country (and firm) over time.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Asset Pricing &amp; Information, Macro-Finance, International Finance</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Uses standard cross-country data (Worldscope and I/B/E/S via WRDS, plus World Bank GDP); no distinctive/nonstandard datasets identified.</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Quarterly Journal of Economics - 2026 - Bostanci and Ordoñez - Business, Liquidity, and Information Cycles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly Journal of Economics - 2026 - Cirera et al. - Technology Sophistication Across Establishments</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly Journal of Economics</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Cirera, Comin, Cruz</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Technology Sophistication Across Establishments</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>This paper introduces a new way to measure technology sophistication by separately capturing the most advanced (MAX) and the most widely used (MOST) technologies in key business functions within establishments. Using a survey of over 21,000 establishments across 15 countries, the authors find that firms generally underutilize the most sophisticated technologies they have available. These MAX–MOST gaps are large and persistent and are strongly associated with lower productivity. The paper shows that raising the intensity of use of already-available advanced technologies is an important and underappreciated margin of technology adoption. It reframes the adoption problem as one of use, not just acquisition.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>The paper argues that standard measures of technology adoption—whether a firm has a technology—miss a crucial distinction between having an advanced technology and actually using it widely. To capture this, the authors design a measurement approach that records, for each key business function, both the most sophisticated technology an establishment can access (MAX) and the technology it uses most intensively (MOST). Applying this to a large multi-country establishment survey, they document that MAX typically exceeds MOST, meaning firms underuse the sophisticated technologies available to them, and that these gaps are widespread across functions and countries. They then show the gaps are persistent rather than transitory and are systematically related to lower productivity, implying the underuse is economically costly. This leads them to argue that the intensity of use of existing technologies is a distinct and important adoption margin, separate from acquiring new technologies. The paper thus shifts the policy question from helping firms obtain technology toward helping them use what they already have.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>A measurement-and-descriptive study built on a purpose-designed survey instrument that separately elicits the most advanced (MAX) and most widely used (MOST) technologies in each business function of an establishment. Using the resulting data on 21,000+ establishments across 15 countries, the authors construct MAX–MOST gaps and relate them cross-sectionally to firm characteristics and productivity. The design's novelty is in the measurement approach itself; the analysis documents the size, persistence, and productivity correlates of the gaps rather than exploiting an external shock.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Technology Adoption, Development Economics, Firm Productivity</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>World Bank — Firm-level Adoption of Technology (FAT) survey</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Quarterly Journal of Economics - 2026 - Cirera et al. - Technology Sophistication Across Establishments.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly Journal of Economics - 2026 - Sangani - Complete Pass-Through in Levels</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly Journal of Economics</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Sangani</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Complete Pass-Through in Levels</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>This paper revisits the long-standing finding that cost pass-through to prices is incomplete. Using microdata from gas stations, food products, and manufacturing, the author shows that incomplete pass-through measured in percentages often masks complete pass-through in levels: a one-dollar-per-unit rise in input costs raises downstream prices by about one dollar per unit. The apparent incompleteness arises because percentage measures mix together products with different markups. The paper argues that dollar-for-dollar (level) pass-through is the empirically robust regularity and derives its implications for how cost shocks propagate through supply chains. The result revises a widely used input to models of inflation and market power.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>The paper starts from the robust empirical finding that pass-through of input costs to prices looks incomplete when measured in percentages, even over long horizons, which has shaped models of markups and inflation. The author points out that percentage pass-through conflates the size of a cost change with the level of a product's price and markup, so a common dollar cost increase can look like different percentage pass-through across products. Re-examining the data in levels rather than percentages, the paper finds that a one-dollar increase in per-unit input costs translates into roughly a one-dollar increase in per-unit prices—complete pass-through in levels. It documents this across very different settings (retail gasoline, packaged food, and manufacturing), suggesting the regularity is general rather than sector-specific. The paper then works through the theoretical implications, showing which demand and cost structures generate level pass-through and how this changes the transmission of cost shocks. The upshot is that the 'incomplete pass-through' puzzle largely dissolves once pass-through is measured in the right units.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>An empirical measurement study that recomputes cost pass-through in levels (dollars per unit) rather than percentages, using price and cost microdata from three distinct settings—retail gasoline, packaged food (retail scanner data), and manufacturing (Census production data). The core comparison contrasts level and percentage pass-through estimates to show the former is complete while the latter appears incomplete because it mixes products with different markups. The analysis is descriptive and cross-sectional across products and industries, complemented by a simple model clarifying when level pass-through holds.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Industrial Organization &amp; Prices, Macroeconomics, Applied Microeconomics</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>NielsenIQ (Nielsen Consumer LLC) — Retail scanner data; U.S. Census Bureau — Annual Survey of Manufactures / Census of Manufactures; Retail gasoline price microdata</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Quarterly Journal of Economics - 2026 - Sangani - Complete Pass-Through in Levels.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly Journal of Economics - 2026 - Acemoglu and Restrepo - Automation and Rent Dissipation Implications for Wages, Inequality, and Productivity</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly Journal of Economics</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Acemoglu, Restrepo</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Automation and Rent Dissipation: Implications for Wages, Inequality, and Productivity</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>This paper studies automation in a task-based economy where some jobs pay workers rents—wages above their outside options. The authors show that automation disproportionately targets high-rent tasks, dissipating those rents, amplifying wage losses for exposed workers, and compressing wage dispersion within exposed groups. Because dissipating rents is socially inefficient, this channel partly offsets the productivity gains automation would otherwise deliver. The framework reconciles observed wage declines and falling within-group inequality with modest aggregate productivity effects. It reframes part of automation's distributional cost as the destruction of labor rents rather than pure efficiency-enhancing substitution.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>The paper begins from the task-based view of production, in which firms can automate individual tasks, and adds the realistic feature that some tasks pay workers rents above their outside options. It argues that firms have a heightened incentive to automate precisely the high-rent tasks, because doing so lets them capture the rent, so automation is not distributionally neutral but concentrated where labor was best paid. This implies that automation dissipates rents, which amplifies wage losses for exposed workers beyond the standard displacement effect and, because the highest-paid exposed workers lose the most, compresses within-group wage dispersion. The authors then show that this rent dissipation is socially inefficient: the resources spent automating to capture rents do not correspond to genuine productivity gains, so measured productivity rises less than a frictionless model would predict. The model thus links three observations—wage declines, falling within-group inequality in exposed groups, and disappointing aggregate productivity—to a single mechanism. It closes by drawing out the welfare implication that some automation is privately profitable but socially wasteful because it merely redistributes rents from workers to firms.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>A task-based theoretical model of automation extended so that some tasks earn workers rents, solved to characterize how automation targets high-rent tasks and what that implies for wages, within-group inequality, and productivity. The predictions are illustrated with standard industry and productivity data (for example, BLS multifactor-productivity and capital-share measures) rather than a single natural experiment. The contribution is primarily conceptual: isolating rent dissipation as a distinct channel through which automation lowers wages and inequality while offsetting productivity gains.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Labor Economics, Automation &amp; Technology, Macroeconomics</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Bureau of Labor Statistics — Total Multifactor Productivity Tables</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Quarterly Journal of Economics - 2026 - Acemoglu and Restrepo - Automation and Rent Dissipation Implications for Wages, Inequality, and Productivity.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Egan et al. - Who Pays for Payments</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Egan, Matvos, Seru, Wang, Yao</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Who Pays for Payments?</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>This paper uses novel data on the composition and cost of payments across U.S. merchants to quantify redistribution in the payment system. Card interchange fees fund consumer rewards, and when merchants raise prices for everyone, users of low-cost methods like cash and debit cross-subsidize high-reward credit-card users at the same merchant. The authors show incidence actually depends on the joint distribution of payment choices across merchants, not the standard assumption that everyone shops at the same stores facing the same fees. Two forces shape redistribution: consumer sorting, where users of different payment methods shop at different merchants, limits cash and debit users' exposure to high interchange fees; and interchange fees vary across merchants, being lower where payment types overlap (e.g., large grocery stores) due to sector discounts and negotiations. Embedding these forces in a sufficient-statistics framework, the paper revises who ultimately bears payment-system costs.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>The paper reconsiders the common claim that users of low-cost payment methods subsidize high-reward credit-card users, showing this conclusion rests on assumptions that fail in the data. The standard argument is that card interchange fees fund rewards, merchants raise prices for everyone to cover the fees, and so cash and debit users cross-subsidize card users at the same store. The authors point out this implicitly assumes that consumers using different payment methods shop at the same merchants and that merchants face similar fees. Using novel data on payment composition and cost across merchants, they document two forces that overturn the simple incidence. First, consumer sorting, since users of different payment methods often shop at different merchants, which limits cash and debit users' exposure to high-interchange environments. Second, interchange fees vary across merchants, and where payment types overlap, such as large grocery stores, fees are lower due to sector discounts and private negotiations. They embed these forces in a sufficient-statistics framework that makes incidence depend on the joint distribution of payment choices across merchants rather than on a single representative store. The result is a substantially revised picture of who ultimately bears payment-system costs, in which sorting and fee heterogeneity blunt the cross-subsidy the standard view predicts.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>A sufficient-statistics incidence design estimated on proprietary merchant-acquirer data (payment composition and cost across merchants) plus consumer payment-diary data. The framework makes who bears payment costs depend on the joint distribution of payment choices across merchants, so the authors estimate the two forces that matter, how consumers using different payment methods sort across merchants and how interchange fees vary across merchants, and feed them into the incidence formulas. Identification of the revised incidence comes from measuring where different payment users actually shop together and the fees they face there; the units are the merchant and the consumer or payment method.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Payments, Household Finance, Industrial Organization</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Fiserv; Federal Reserve Bank of Atlanta — Diary of Consumer Payment Choice (DCPC); Nilson Report</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Drechsler, Savov, Schnabl</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Credit Crunches and the Great Stagflation</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>This paper argues that severe banking-system credit crunches helped cause the Great Stagflation of the 1970s, working through Regulation Q, which capped deposit rates. Under Reg Q, Fed tightening triggered large deposit outflows that forced banks to contract lending, and these credit crunches line up closely with stagflation over time. Adding Reg Q to a standard model where firms finance working capital with bank loans, the authors show binding caps make working capital costlier, leading firms to raise prices and cut output. This yields an augmented Phillips curve in which monetary tightening reduces aggregate supply as well as demand, with effects increasing in credit-crunch severity, external-finance dependence, and working-capital intensity. Cross-industry tests confirm that more exposed manufacturing industries raised prices and cut output relative to others.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>The paper advances a novel explanation for the 1970s Great Stagflation: severe credit crunches in the banking system, operating through Regulation Q, which capped the interest rates banks could pay on deposits. The mechanism is that when the Fed tightened, market rates rose above the Reg Q ceilings, triggering large deposit outflows that forced banks to contract lending. The authors first show these credit crunches line up closely with stagflation in the time series, motivating a causal role. To explain how a credit crunch produces stagflation, they add Reg Q to a standard model in which firms need bank loans to finance working capital, so that when credit contracts, working capital becomes more expensive, leading firms to raise prices and cut output simultaneously. This yields an augmented Phillips curve in which monetary tightening reduces aggregate supply, not just demand, with the supply effect increasing in the severity of the credit crunch, firms' dependence on external finance, and their working-capital intensity. The paper then tests these three cross-sectional predictions across manufacturing industries and finds that more exposed industries raised prices and cut output relative to others, supporting the claim that under severe financial frictions monetary policy has a supply-side channel that can generate stagflation.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>A model paired with cross-industry tests. The authors add Regulation Q deposit-rate ceilings to a working-capital model, deriving an augmented Phillips curve in which credit contractions shift aggregate supply, and generating predictions that grow with credit-crunch severity, external-finance dependence, and working-capital intensity. Empirically, they first show that Reg Q-driven credit crunches (deposit outflows when Fed tightening pushes rates above the ceilings) track stagflation over time, then test the cross-sectional predictions across manufacturing industries by exposure. Bank-level regulatory data back to 1959 measure the deposit outflows and lending contractions; the industry-by-time comparison provides the identifying variation.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Monetary Economics, Banking, Macro-Finance</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Call Reports (via FOIA); NBER-CES — Manufacturing Industry Database; FDIC — Historical Bank Data; Federal Reserve — Senior Loan Officer Opinion Survey (SLOOS)</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Chen and Sacerdote - Capital in the Capitol Congressional Trades Resemble Uninformed Retail Trading</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Chen, Sacerdote</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Capital in the Capitol: Congressional Trades Resemble Uninformed Retail Trading</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>This paper asks whether members of Congress exploit informational advantages in their personal stock trading, using a new hand-collected dataset of all U.S. legislators' and their families' trades from 2012 to 2023. After the STOCK Act, legislators' portfolios on average underperform or merely match market benchmarks. To explain this mediocre performance, the authors show legislators' positions track financial professionals' recommendations and that their trade timing reflects prevailing market sentiment - estimated from retail investors' social-media posts - rather than anticipating price moves. Congressional trading thus looks like public-signal-following and resembles uninformed retail behavior. The paper pushes back on the view that legislators systematically trade on private information.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>The paper revisits whether members of Congress exploit informational advantages in their personal trading, noting prior studies relied on limited samples and offered little on mechanisms. It first builds a comprehensive, hand-collected dataset of all legislators' and their families' trades from 2012-2023, then evaluates portfolio performance against multiple benchmarks, finding that after the STOCK Act legislators on average underperform or merely match the market. The interesting question becomes why performance is mediocre, and the paper tests two possibilities about how legislators actually trade. It shows their positions track the recommendations of financial professionals, suggesting they follow public expert signals rather than private information. It then shows their trade timing aligns with prevailing market sentiment, estimated from retail investors' social-media posts, rather than anticipating future price changes, indicating they buy and sell with the crowd. Together these results imply that legislators' observable trading behavior resembles uninformed retail trading, following public signals and sentiment, which reconciles the lack of outperformance with the popular perception of informational advantage and pushes back on the view that congressional trading systematically exploits inside information.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>A performance-evaluation-plus-mechanism design on a hand-collected record of congressional and family trades (2012-2023), a period defined by the STOCK Act disclosure regime. Portfolio performance is measured with event-study and calendar-time methods against several benchmarks to test for out- or under-performance. Mechanism tests then relate legislators' trades to analyst recommendations and to a social-media sentiment measure, examining whether their timing follows public signals rather than anticipating price moves. The unit of analysis is the trade and legislator.</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Political Economy, Informed Trading, Behavioral Finance</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Chen &amp; Sacerdote (this paper) — Congressional trading records; Context Analytics — S-Score (Twitter/X sentiment)</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Pagel et al. - Bank Fees and Household Financial Well-Being</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Pagel, Sridhar, Williams</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Bank Fees and Household Financial Well-Being</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>This paper studies 2017-2022 policy changes at large U.S. banks that eliminated non-sufficient-funds (NSF) fees and relaxed overdraft policies, using individual transaction-level data. Eliminating NSF fees immediately reduced NSF charges across the income distribution, as expected. Relaxing overdraft policies, however, reduced overdraft fees only for wealthier (higher-income, higher-liquidity) households, and only they saw subsequent declines in late fees, interest, maintenance fees, and use of alternatives like payday loans. The authors conclude the changes were not substantial enough to meaningfully relieve financial stress for the most vulnerable households. Methodologically, the multi-treatment, varying-intensity setting motivates a new stacked event-study estimator related to de Chaisemartin et al. (2024) to handle staggered-DiD biases.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>The paper studies whether widely publicized reductions in bank fees actually improved household financial well-being, exploiting 2017-2022 policy changes at large U.S. banks that eliminated non-sufficient-funds fees and relaxed overdraft policies. Using individual transaction-level data, it first confirms the mechanical effect, since eliminating NSF fees immediately lowered NSF charges across the income distribution. The more subtle question is distributional, namely who benefited from the overdraft relaxation, and here the paper finds the gains were concentrated among wealthier households (higher income and liquidity), who alone experienced overdraft-fee reductions and, subsequently, declines in late fees, interest payments, maintenance fees, and use of alternatives like payday loans. Vulnerable households, by contrast, saw little relief, implying the policy changes were not substantial enough to reduce their financial stress. Methodologically, the setting features multiple treatments with varying intensities, which standard staggered difference-in-differences estimators handle poorly, so the paper motivates and implements a new stacked event-study estimator related to recent econometric work. The argument thus connects a seemingly consumer-friendly reform to a distributional outcome, benefits accruing to those least in need, while contributing an estimation approach suited to its complicated treatment structure.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>A stacked event-study (staggered difference-in-differences) design exploiting a wave of policy changes at large banks between 2017 and 2022 that eliminated NSF fees and relaxed overdraft terms. Because these changes hit different banks at different times and with different intensity, which trips up conventional staggered-DiD estimators, the authors develop and apply a new stacked estimator (related to de Chaisemartin et al., 2024). They estimate effects separately across the income and liquidity distribution to recover who actually benefited, using individual transaction-level data. The unit of analysis is the household or account over time.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Household Finance, Banking, Consumer Protection</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Consumer transaction-data provider; FDIC — Summary of Deposits</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Matvos et al. - Private Credit, Balance Sheets and Financial Stability</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Matvos, Piskorski, Seru</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Private Credit, Balance Sheets and Financial Stability</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>This paper uses new, comprehensive fund- and asset-level data covering most of the private-credit industry to assess its balance sheets and financial-stability implications. Private-credit funds are highly capitalized, with equity typically 65-80% of assets - more than six times the capitalization of U.S. banks - and use only moderate debt, largely bank credit lines for liquidity management. Fund lives of 10-12 years exceed the shorter maturities of underlying loans, implying little maturity mismatch, unlike banks that fund long-term assets with short-term callable deposits. Portfolios are diversified across industries, geographies, and strategies, and performance shows positive average net returns with losses borne mainly by equity. The authors conclude that, as currently structured, private-credit funds are conservatively built and unlikely to pose bank-like systemic risks.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Debate over whether the fast-growing private-credit industry poses bank-like systemic risk has been hampered by limited data, so the paper brings comprehensive fund- and asset-level data to bear on how these funds are actually financed. It documents that private-credit funds are highly capitalized, with equity typically 65-80% of assets, more than six times banks' roughly 10%, and that their debt use is moderate and mostly bank credit lines for liquidity management rather than leverage. It then examines maturity structure and finds fund lives of 10-12 years exceed the maturities of the underlying loans, implying little maturity mismatch, in sharp contrast to banks that fund long-term assets with short-term callable deposits. Turning to portfolio risk, it shows holdings are diversified across industries, geographies, and strategies, limiting exposure to correlated shocks. On performance, it finds positive average net returns with limited downside to creditors because equity investors absorb losses first. Assembling these facts, the paper argues that as currently structured, private-credit funds are conservatively built and unlikely to generate the runnable, mismatch-driven fragility that makes banks systemically risky, while noting that this conclusion is conditional on current balance-sheet configurations.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>A descriptive, comparative design using new proprietary data on roughly 1,300 private-credit funds and their loans, benchmarked against U.S. banks' regulatory data. The authors characterize how these funds are capitalized and funded, their maturity structure, portfolio diversification, and loss-bearing, and contrast each dimension with the analogous bank figures. The financial-stability conclusions follow from the documented balance-sheet structure rather than from a causal estimate; the units of analysis are the fund and the underlying loan.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Private Credit, Financial Stability, Banking</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary private-credit data provider; Preqin</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Baslandze et al. - Artificial Intelligence, Productivity, and the Workforce Evidence from Corporate Executives</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Baslandze, Edwards, Graham, McClure, Meyer, Sparks, Waddell, Weitz</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Productivity, and the Workforce: Evidence from Corporate Executives</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>This paper uses a novel survey of nearly 750 corporate executives to study how artificial intelligence is affecting productivity and the workforce. Adoption is highly heterogeneous: more than half of firms have already invested, though many smaller firms are just starting. Labor-productivity gains are positive, vary by sector, are expected to strengthen in 2026, and are concentrated in high-skill services and finance; they reflect higher revenue-based total factor productivity through innovation and demand channels rather than capital deepening. The authors document a 'productivity paradox' in which perceived gains exceed measured gains, likely due to delayed revenue realization. In labor markets they find little near-term aggregate employment decline, though large firms anticipate AI-driven reductions while smaller firms expect modest gains, alongside compositional labor reallocation.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Firm-level effects of AI are hard to observe in standard datasets, so the paper gathers direct evidence through a novel survey of nearly 750 corporate executives about adoption, productivity, and workforce plans. It first documents wide heterogeneity in adoption, since over half of firms have already invested while many smaller firms are only beginning, establishing that AI diffusion is uneven. It then characterizes productivity effects, which are positive, vary across sectors, are expected to strengthen going forward, and are largest in high-skill services and finance. Digging into the source of these gains, the paper argues they are not primarily due to capital deepening but reflect higher revenue-based total factor productivity operating through innovation- and demand-oriented channels. It surfaces a 'productivity paradox' in which perceived gains exceed measured gains, interpreting the gap as a lag between AI adoption and the realization of revenue. Turning to labor, it finds little evidence of near-term aggregate employment decline, but a divergence in expectations, since large firms anticipate AI-driven workforce reductions while smaller firms expect modest gains, alongside compositional reallocation of labor within and across firms. The narrative thus links where AI is adopted to how and when its productivity shows up, and to who gains or loses in the labor market.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>A survey-based, descriptive design. A new survey of nearly 750 corporate executives measures AI adoption, its perceived and measured productivity effects, and workforce expectations, with responses weighted to match the U.S. Census industry and size distribution. The analysis documents how adoption and productivity effects vary across sectors and firm sizes, separates productivity gains coming from capital deepening versus revenue-based TFP, and quantifies the gap between perceived and measured gains. Results are cross-sectional patterns rather than causal estimates; the unit of analysis is the firm or executive respondent.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Economics of AI, Productivity, Labor Economics</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Federal Reserve Bank of Atlanta &amp; Duke University — Survey of corporate executives</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Eisfeldt et al. - Intangible Intensity</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Eisfeldt, Hartman-Glaser, Kim, Lee</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Intangible Intensity</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>This paper builds a text-based measure of firms' intangible investment intensity from 10-K filings and introduces a general 'semantic theme scoring' (STS) methodology. The approach further decomposes disclosure text into knowledge, customer, and organization capital. High-intangible-intensity firms are smaller, younger, and invest heavily in R&amp;D and human capital, and the three subcomponents map to distinct firm types - knowledge-intensive (R&amp;D-driven, high valuation, skilled labor), customer-intensive (mature, profitable, commercial), and organization-intensive (large, asset-heavy incumbents). The authors show managerial expenditure descriptions carry informative signals about intangible capital that complement financial statements. The paper offers both a new measure and a reusable NLP methodology for capturing corporate intangibles.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Because accounting statements poorly capture intangible capital, the paper turns to the language firms use to describe their spending and builds a text-based measure of intangible investment intensity from 10-K filings, introducing a general 'semantic theme scoring' methodology along the way. It further decomposes the disclosure text into three components, knowledge, customer, and organization capital, arguing these correspond to economically distinct kinds of intangible investment. It then validates the measure by relating it to firm characteristics, showing high-intangible firms are smaller, younger, and invest heavily in R&amp;D and human capital, consistent with what intangible intensity should proxy. The decomposition is shown to map cleanly onto distinct firm types, where knowledge-intensive firms are R&amp;D-driven with high valuations and skilled labor, customer-intensive firms are mature, profitable, and commercially oriented, and organization-intensive firms are large, asset-heavy incumbents, demonstrating the subcomponents carry different information. The broader argument is that managerial expenditure descriptions contain informative signals about intangible capital stocks that complement, rather than duplicate, financial-statement data, opening a path to measuring where firms sit in the intangible lifecycle. The methodological contribution, semantic theme scoring, is offered as a reusable tool for extracting economic constructs from disclosure text.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>A text-as-data measurement exercise. The authors apply a new 'semantic theme scoring' method to firms' 10-K filings to build a measure of intangible-investment intensity and to split it into knowledge, customer, and organization capital. They validate the measure cross-sectionally by relating it and its three components to firm size, age, R&amp;D, valuation, profitability, and workforce skill, showing the constructs behave as expected and that the components pick out distinct firm types. The unit of analysis is the firm-year, with filings as the raw input.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Intangible Capital, Text-as-Data / NLP, Corporate Finance</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>SEC (WRDS SEC Analytics Suite) — 10-K filings; S&amp;P Capital IQ</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Amiti et al. - Why Do Firms Pay Different Interest Rates on Their Bank Loans</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Amiti, Kashyap, Kovner, Weinstein</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Why Do Firms Pay Different Interest Rates on Their Bank Loans?</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>This paper documents large dispersion in interest rates on similar commercial and industrial loans using confidential supervisory data on the largest U.S. banks, and argues the spread is not explained by risk. The authors rationalize the dispersion with a search-cost model in which borrowers pay to solicit competing quotes. Estimated search costs are highest for smaller and riskier borrowers and lowest for public firms, matching predictable differences in screening and monitoring costs. The search costs are economically large: over a third of firms behave as if they never comparison-shop, half appear to obtain only two quotes, and the rest search widely. The paper interprets loan-rate dispersion as evidence of substantial search frictions in credit markets rather than pure risk pricing.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>The paper documents a puzzle in confidential supervisory data: observably similar commercial-and-industrial borrowers pay markedly different interest rates, and this dispersion does not appear attributable to differences in credit risk. It proposes that the residual dispersion reflects search frictions, since firms must expend costly effort to solicit competing quotes and those that search less pay more. To formalize this, the authors adopt a search-cost model in which each borrower trades off the cost of obtaining another quote against the expected rate savings, so equilibrium rates depend on borrower-specific search costs. The model predicts that search costs should be systematically higher for borrowers who are more expensive to screen and monitor, namely smaller and riskier firms, and lower for transparent public firms. Estimating the model on the loan data, they recover these search costs and find them large and patterned exactly as predicted. The estimates also imply striking behavior, since a substantial share of firms act as if they never comparison-shop, about half appear to obtain only two quotes, and the remainder search widely. The paper thus reinterprets loan-rate dispersion not as mispriced risk but as the footprint of costly search, with implications for competition and borrower welfare in bank lending.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>A structural estimation of a borrower search-cost model on confidential loan-level supervisory data. After showing that risk cannot explain why similar borrowers pay different C&amp;I loan rates, the authors specify a model in which each firm decides how many competing quotes to gather, trading the cost of searching against the rate savings. Estimating the model recovers the distribution of search costs across borrower types, by size, risk, and whether the firm is public. Identification comes from how rate dispersion varies with these observable borrower characteristics under the model's structure; the unit of observation is the loan and borrower.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Banking, Credit Markets, Search Frictions</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Federal Reserve — FR Y-14 supervisory data</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Dyck et al. - Venture Fraud</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Dyck, Fang, Hebert, Xu</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Venture Fraud</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>This paper assembles the first comprehensive sample of venture fraud - 614 U.S. venture-capital-backed startups founded since 2000 that faced fraud allegations - and studies its governance roots. Within a high-detection subsample of newly public firms, VC-backed firms are 54% more likely to face fraud charges than comparable non-VC-backed firms. Fraud is more likely where founders hold stronger control rights, more convex cash-flow rights, more investors, and more non-traditional investors, with founder-controlled boards 88% more likely to commit fraud than VC- or shared-control boards. Governance features predict fraud far better than founder characteristics, and hot funding conditions at the first round - which weaken governance - forecast later fraud. The paper reframes venture fraud as substantially a product of governance structures rather than individual bad actors.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>The paper begins from a measurement gap, since there has been no comprehensive record of fraud among venture-backed startups, and closes it by hand-collecting a large sample of venture-fraud cases. It then asks whether venture capital is associated with more fraud, and finds that within a high-detection subsample of newly public firms, VC-backed firms are substantially more likely to face fraud charges than comparable non-VC-backed firms, a design meant to hold detection roughly constant. The core question is why, and the paper focuses on governance rather than the personal traits of founders. It argues that two features that have grown over time, founder-friendly control structures and complex cap tables with many and non-traditional investors, weaken the monitoring that would otherwise deter fraud. Using a panel prediction model, it shows fraud is more likely when founders have stronger control rights, more convex cash-flow rights, and when there are more and less-traditional investors, with founder-controlled boards far more fraud-prone than VC- or shared-control boards even within the same firm. It further shows that hot funding conditions at the initial round, which erode investors' governance leverage, predict later fraud, and that governance variables dominate founder characteristics in predicting fraud, implying venture fraud is largely a governance phenomenon that ex-ante contract design and market conditions help produce.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Two complementary designs on a hand-collected fraud sample. To test whether VC backing raises fraud without conflating it with better detection, the authors compare VC- and non-VC-backed firms within a set of newly public firms where detection is high and roughly uniform. To study why, they estimate a panel (hazard-style) prediction model over all VC-backed firms founded since 2000, relating the probability of fraud to governance features (founder control and cash-flow rights, number and type of investors, board control) and to funding-market conditions at the first round. The unit of analysis is the startup, and within-firm comparisons of board types help separate governance from other firm traits.</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Venture Capital, Corporate Governance, Financial Fraud</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>PitchBook; Crunchbase; Dyck, Fang, Hebert &amp; Xu (this paper) — Venture-fraud case sample</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="n"/>
+      <c r="L59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Diwan et al. - Competition and Fraud in Health Care</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Diwan, Eliason, League, Leder-Luis, McDevitt, Roberts</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Competition and Fraud in Health Care</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>This paper examines how competition affects fraud when governments procure goods and services from private firms, using Medicare's durable medical equipment (DME) market. The authors argue competition has an ambiguous effect on fraud: it dissipates the rents that attract fraudulent firms, but also squeezes margins so that legitimate firms may exit. Exploiting Medicare's switch from administratively regulated prices to competitive bidding for DME, they show that fraudulent suppliers' cost advantage let them gain market share while legitimate suppliers left the market. The result implies that price competition can perversely concentrate a market in fraudulent providers. The paper connects procurement design to the composition of firms and the prevalence of fraud.</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Governments buy many goods and services from private firms, and competition is generally expected to lower prices, but the paper argues its effect on fraud is theoretically ambiguous. On one hand, competition dissipates the excess profits that attract fraudulent entrants; on the other, it compresses margins so far that honest firms, which bear real costs, can no longer break even, potentially leaving the market to low-cost fraudulent providers. The setting that makes this trade-off visible is Medicare's procurement of durable medical equipment, where a switch from administratively set prices to competitive bidding sharply cut reimbursement. The authors reason that because fraudulent suppliers enjoy an artificial cost advantage, since they need not actually deliver legitimate equipment, the price squeeze from competition should hit legitimate firms harder, causing them to exit while fraudulent firms gain share. They link supplier-level claims to fraud-enforcement records to classify firms and trace market shares and exit around the reform. The finding that fraudulent firms expanded as legitimate firms left implies that price competition, absent complementary screening or enforcement, can perversely concentrate a market in fraud rather than eliminate it, an important qualification to the standard case for competitive procurement.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>An event-study / difference-in-differences design using Medicare's shift from administratively set prices to competitive bidding for durable medical equipment as the policy shock. Because the reform sharply cut reimbursement in affected product-areas and regions, the authors can compare how fraudulent and legitimate suppliers fared afterward. They classify suppliers by linking Medicare claims to fraud-enforcement records, then track market shares, entry, and exit for each group around the reform. The unit of analysis is the supplier (NPI); auction-bid data support the analysis of bidding.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Health Economics, Industrial Organization &amp; Procurement, Fraud &amp; Enforcement</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Centers for Medicare &amp; Medicaid Services (CMS) — Medicare DMEPOS claims; DOJ / HHS-OIG — Fraud enforcement records; Yunan Ji — Medicare DME auction bids</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Correia, Luck, Verner</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Bank Runs with and without Bank Failure</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>This paper builds a comprehensive historical database of U.S. bank runs by applying large language models to historical newspapers, yielding information on 3,984 runs on individual banks from 1863 to 1934. The data show runs are far more likely at weak banks but also occur at strong banks, especially following negative news about the real economy or the broader banking system. Crucially, runs typically cause failure only when a bank's fundamentals are poor; strong banks survive through signaling, interbank cooperation, and temporary suspension. Locally, runs on weak banks produce much larger declines in deposits, lending, and manufacturing activity than runs on strong banks. The findings put poor fundamentals at the center of both when runs occur and when they are economically damaging, tempering pure self-fulfilling-panic accounts.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>The paper's first contribution is measurement: to study bank runs systematically, the authors use large language models to read historical newspapers and assemble a large, bank-level database of runs spanning 1863-1934, far broader than hand-collected samples. Armed with this data, they ask whether runs strike indiscriminately, as pure panic models suggest, or track fundamentals. They find runs concentrate at weak banks but can also hit strong ones, especially after negative news about the real economy or the banking system, indicating an information-driven component. The central distinction they then draw is between a run and a failure, since a run threatens a bank but whether it causes failure depends on fundamentals. Strong banks survive runs through signaling their soundness, cooperation among banks, and temporary suspension of convertibility, whereas weak banks fail. The paper then links runs to the real economy, showing that runs on weak banks cause much larger local declines in deposits, lending, and manufacturing activity than runs on strong banks. Taken together, the evidence places poor fundamentals at the center of both when runs occur and when they do damage, tempering models in which small shocks trigger discontinuous jumps to bad equilibria and favoring accounts in which fundamentals discipline both the incidence and consequences of runs.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>An empirical study built on a newly constructed dataset. Using large language models to read historical newspapers, the authors assemble information on 3,984 bank runs (1863-1934). They then relate the incidence of runs to bank fundamentals and to news about the economy and banking system, separate runs that caused failure from those that did not, and identify the mechanisms (signaling, interbank cooperation, suspension) that let strong banks survive. A local analysis compares deposits, lending, and manufacturing activity around runs on weak versus strong banks. The units of analysis are the bank and its local economy.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Banking History, Financial Crises, Text-as-Data / LLMs</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Correia, Luck &amp; Verner (this paper) — Historical bank-run database; Library of Congress — Chronicling America; OCC — National bank call reports (Annual Report to Congress)</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Bornstein and Castillo-Martinez - Firm Exit and Financial Frictions</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Bornstein, Castillo-Martinez</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Firm Exit and Financial Frictions</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>This paper examines whether financial frictions cause too many firms to fail, motivating government interventions that prevent closures during crises. The authors build a firm-dynamics model with incomplete financial markets and show that frictions generate excessive firm exit, with a key sufficient statistic being the marginal propensity to exit with debt. Using confidential U.S. Census data, they estimate the debt–exit relationship and use it to discipline the model. The calibrated model implies that eliminating financial frictions would cut firm exit from 9.3% to 5.0% and deliver welfare gains of 3.6% in consumption-equivalent terms, with costs that spike during financial crises but not during ordinary productivity recessions. Comparing government-guaranteed loans and grants, the paper quantifies the trade-off between fiscal cost and effectiveness in preventing excessive exit.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Policymakers routinely intervene to prevent firm closures during crises on the presumption that financial frictions push otherwise-viable firms out of business, but whether exit is actually inefficient is theoretically ambiguous, and the paper sets out to answer it. It builds a firm-dynamics model with incomplete financial markets in which frictions can distort the exit margin, and it identifies the marginal propensity to exit with respect to debt as the sufficient statistic that governs whether exit is excessive. The intuition is that if firms carrying more debt are disproportionately likely to exit, the frictions are inducing closures that would not occur in a frictionless world. To make this operational, the authors estimate the debt-exit relationship directly in confidential firm-level data and use it to discipline the model's key parameter. They then use the calibrated model to compute how much frictions inflate the exit rate and the associated welfare loss, and to show that this loss is state-dependent, spiking during financial crises but not during ordinary productivity recessions, precisely because crises tighten the financial channel. Finally, the paper compares policy instruments, government-guaranteed loans versus grants, evaluating each on the trade-off between fiscal cost and effectiveness at curbing excessive exit.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>A quantitative firm-dynamics model with incomplete markets, disciplined by one reduced-form estimate. The theoretical contribution is to show that the marginal propensity to exit with respect to debt is a sufficient statistic for whether financial frictions make exit excessive. The authors estimate that debt-exit relationship in confidential Census microdata covering all employers, use it to pin down the model's key parameter, and then use the model to compute how much frictions inflate exit and reduce welfare, and how that cost differs between financial crises and ordinary recessions. Finally they compare guaranteed loans against grants as interventions.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Firm Dynamics, Financial Frictions, Macroeconomic Policy</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Census Bureau — Longitudinal Business Database (LBD); Bureau van Dijk — Orbis (Italy)</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="n"/>
+      <c r="L62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Malenko et al. - Fragmentation of Shareholder Power</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Malenko, Malenko, Tsoy</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Fragmentation of Shareholder Power</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>This paper develops a theoretical framework to evaluate how the asset-management industry's shift toward tailored portfolios, fund proliferation, and decentralized stewardship affects corporate governance. Growing heterogeneity in investor preferences better aligns products with demand but can fragment ownership and weaken managerial oversight. The authors show fund proliferation does not necessarily weaken governance: stronger manager incentives and concentrated portfolios of specialized funds can offset fragmentation, especially when investor preferences are intense. However, intense preferences can also push asset managers to compete by granting investors control—decentralizing stewardship and adopting pass-through voting—without internalizing the resulting governance costs. The paper clarifies when investor-driven customization helps or harms oversight.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>The asset-management industry has moved toward tailored portfolios, a proliferation of funds, and decentralized stewardship, and the paper asks whether these trends necessarily weaken the corporate oversight that concentrated ownership traditionally provides. It sets up the tension: greater heterogeneity in investor preferences improves the match between products and demand, but it can also fragment ownership and dilute any single manager's incentive to monitor. The authors build a model in which asset managers choose how concentrated their portfolios are, how much monitoring effort to exert, and how much control to pass through to their investors, all given the intensity of investor preferences. Analyzing it, they show that fund proliferation does not mechanically degrade governance, because stronger managerial incentives and the concentrated portfolios of specialized funds can offset fragmentation, and this offset is strongest when investor preferences are intense. However, the same intensity creates a countervailing force, since competition among managers on the 'control' dimension can lead them to hand voting power to investors even when doing so is socially costly, because each manager does not internalize the governance externality. The framework thus delineates conditions under which investor-driven customization helps versus harms oversight, rather than predicting a uniform decline.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>A theoretical (mechanism-design) model, with no external data. Asset managers choose how concentrated their portfolios are, how much effort to put into monitoring firms, and how much voting control to hand to their investors, all as functions of how intense investor preferences are. The analysis derives comparative statics showing when fund proliferation is offset by stronger incentives and specialization (so governance holds up) and when competition on the 'control' margin leads managers to decentralize stewardship inefficiently. The key results characterize which force dominates as preference intensity varies.</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Governance, Asset Management, Financial Theory</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Theoretical paper; no nonstandard datasets identified.</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Bardóczy et al. - Monopsony Power and the Transmission of Monetary Policy</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Bardóczy, Bornstein, Salgado</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Monopsony Power and the Transmission of Monetary Policy</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>This paper studies how employer labor-market power changes the way monetary policy transmits to wages and employment. Using administrative U.S. Census data, the authors show that high-monopsony firms—those accounting for over 10 percent of their local wage bill—adjust their wage bill and employment less in response to monetary policy. They rationalize this with a New Keynesian model featuring heterogeneous firms and oligopsonistic labor competition, where wage stickiness combined with labor-market power drives the muted response. The model isolates two channels—partial passthrough and misallocation—through which oligopsony shapes aggregate effects. Calibrated to U.S. labor markets, it implies that the decline in labor-market power since the 1980s raised the output response to monetary policy by about 10 percent and accounts for roughly 15 percent of the flattening of the Phillips curve.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>The paper starts from the observation that firms with labor-market (monopsony) power set wages strategically rather than taking them as given, so their response to monetary policy need not resemble that of competitive firms. It hypothesizes that when wages are sticky and a firm holds monopsony power, the firm absorbs monetary shocks differently, adjusting its wage bill and employment less, because its wage-setting margin interacts with nominal rigidity. Using administrative data, the authors first document exactly this, showing that high-monopsony firms, those accounting for a large share of their local labor market, react less to monetary-policy shocks. To interpret the fact and quantify aggregate implications, they build a heterogeneous-firm New Keynesian model with oligopsonistic labor markets in which the muted response emerges from the interaction of wage stickiness and market power. The model isolates two channels through which oligopsony shapes aggregate outcomes, incomplete passthrough of shocks to wages and misallocation of labor across firms. Calibrating it to U.S. labor markets lets the authors run counterfactuals, and they find that the secular decline in labor-market power since the 1980s made monetary policy more potent and accounts for a meaningful share of the flattening of the Phillips curve, linking a structural labor-market trend to the changing behavior of monetary policy.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>A two-part design combining reduced-form estimates with a calibrated model. Empirically, the authors measure how individual firms' wage bills and employment respond to surprise (high-frequency identified) monetary-policy shocks, and compare firms with more versus less local labor-market power using confidential Census data. They then build and calibrate a heterogeneous-firm New Keynesian model with oligopsonistic labor markets in which the muted response of high-monopsony firms arises naturally, decomposing the aggregate effect into passthrough and misallocation channels. The calibrated model is used to ask how the decline in monopsony since the 1980s changed monetary transmission and the slope of the Phillips curve.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Monetary Policy, Labor Market Power, Macroeconomics</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Census Bureau — LEHD merged with Longitudinal Business Database (LBD)</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Thesmar, Verner</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Beliefs and Stock Market Fluctuations: New Evidence from the Past Seven Decades</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>This paper builds a new seven-decade series of subjective expected equity returns (1956-2024) from an independent equity-analysis firm and uses it to reassess how beliefs move markets. Unlike the expectations of individual investors and professional forecasters, this measure is strongly positively correlated with the earnings-price ratio, responds negatively to past returns, and positively predicts future returns. Individual and professional-forecaster expectations are only weakly or negatively correlated with the new series, and disagreement between sophisticated and individual investors is associated with higher trading volume. The evidence fits a model of heterogeneous beliefs in which naive investors extrapolate past returns while sophisticated investors are close to rational. The paper offers a rare long-run window on the belief dynamics behind valuations.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Testing how beliefs move markets has been hampered by the lack of a long, consistent measure of what sophisticated investors expect returns to be, so the paper's first move is to construct one, hand-collected over nearly seven decades from an independent equity-analysis firm. With this new series in hand, it characterizes the properties any belief-based theory must confront: sophisticated expected returns co-move positively with the earnings-price ratio, respond negatively to recent past returns (they are mean-reverting), and positively predict future returns. It contrasts these with survey measures of individual investors and professional forecasters, which are only weakly or even negatively correlated with the new series, implying different groups hold systematically different beliefs. The paper then notes that disagreement between sophisticated and individual investors lines up with trading volume, consistent with heterogeneous beliefs generating trade. Because no single-agent, single-belief model can match this joint pattern, it argues for a framework with at least two types of investor. It then shows that a model in which naive investors extrapolate past returns while sophisticated investors are close to rational reproduces the co-movement with valuations, the mean reversion, the predictability, and the volume-disagreement link, providing a unified account of the belief dynamics behind valuations over seventy years.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Primarily a measurement and asset-pricing study. Its foundation is a new, hand-collected 1956-2024 series of sophisticated investors' expected returns. Using it, the authors run correlation and predictive regressions, linking expected returns to the earnings-price ratio, to past returns, and to realized future returns, and compare them with survey expectations of individuals and forecasters, while relating disagreement across groups to trading volume. A two-type model (extrapolative naive investors, near-rational sophisticated investors) is then shown to reproduce this whole set of facts. The unit of analysis is the market over time.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Behavioral Finance, Asset Pricing, Expectations &amp; Beliefs</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Value Line Investment Survey; Robert Shiller — Investor Confidence Survey; UBS/Gallup and Livingston Survey</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Ahern</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>This paper shows that the industrial composition of a city's economy shapes its cost of municipal borrowing. In a panel of 1,177 U.S. cities from 2005 to 2022, greater sectoral concentration raises default risk and municipal bond spreads, especially where dominant industries are associated with low property values. Instrumental variables built from national sector-employment trends and regional house-price variation support a causal reading. A calibrated city-default model implies the estimated spread effect understates the gross risk from concentration, because concentration also brings agglomeration benefits that lower spreads, particularly in high-property-value cities. The paper connects local economic structure to public finance and credit risk.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>A city whose economy depends on only a few industries bears more concentrated economic risk, which the paper argues should raise the probability of fiscal distress and therefore the yields investors demand on its municipal bonds. The key refinement is that the sign and size of this effect should depend on what kind of industries dominate, because concentration in sectors associated with low property values is more dangerous when the property-tax base that backs municipal debt is weaker. The paper first documents the concentration-spread relationship in a large panel of cities and shows it is stronger where dominant industries imply low property values. Recognizing that industrial structure is not randomly assigned, it constructs instruments from national, city-external variation, namely industry-level employment trends interacted with regional house-price movements, to isolate plausibly exogenous changes in local concentration. It then confronts a subtlety: concentration is not purely bad, since agglomeration can raise productivity and property values and thereby lower spreads, so the reduced-form spread effect nets these opposing forces. To recover the gross risk, the authors calibrate a city-default model, which implies that the true risk contribution of concentration is larger than the estimated net spread effect, especially in high-property-value cities where agglomeration benefits offset it.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>A panel regression of municipal bond spreads on city industrial concentration, made causal with an instrumental-variables (shift-share) strategy. Because a city's industry mix is not random, the authors instrument local concentration using national industry-employment trends interacted with the city's initial composition and regional house-price movements, isolating variation unlikely to be driven by the city's own fiscal shocks. The unit of analysis is the city-year, and interactions separate concentration in low- versus high-property-value industries. A calibrated city-default model then shows the gross risk from concentration exceeds the net spread effect once offsetting agglomeration benefits are accounted for.</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Finance, Credit Risk, Urban &amp; Regional Economics</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>MSRB — Municipal Securities Rulemaking Board trade data; U.S. Census Bureau — LODES (LEHD Origin-Destination Employment Statistics); FHFA — House Price Index</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Clayton and Coppola - The Optimal Use of AI in Financial Regulation</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Clayton, Coppola</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>The Optimal Use of AI in Financial Regulation</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>This paper asks whether modern AI methods applied to granular portfolio-holdings data can improve macroprudential regulation, and how policymakers should use such tools. The authors build a graph-based deep learning model over security-level holdings of financial intermediaries that embeds economic priors and learns latent representations of both assets and investors from the network of positions. Applied to the near-universe of non-bank financial intermediaries (about $40 trillion), the model forecasts intermediary trading far better than existing approaches, including during crises, and has more than ten times the explanatory power for cross-sectional stress-period returns. Its learned embeddings encode economically interpretable information about fire-sale vulnerability, and the architecture is inductive enough to produce estimates even for withheld asset classes or investors. The authors then embed the empirical model in a macroprudential optimal-policy framework, addressing the Lucas critique, to show why these objects matter for welfare.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>The paper frames systemic-risk measurement as a prediction problem defined over the network of who holds which assets, arguing that the structure of intermediary holdings encodes fire-sale vulnerability that standard, low-dimensional risk metrics miss. It proposes that modern representation-learning methods can extract this information if they are constrained by economic priors rather than applied as black boxes. Concretely, the authors build a graph-based deep-learning model that learns latent embeddings of both assets and investors from the bipartite network of positions, so that assets held by similar investors, and investors holding similar assets, end up close in the learned space. They validate that these learned objects are economically meaningful by showing the model forecasts intermediary trading, including during crises, far better than existing approaches and explains an order of magnitude more of the cross-section of stress-period returns. Because the architecture is inductive, it can generate estimates even for asset classes or investors held out of training, which matters for a regulator facing new or incompletely observed exposures. The paper then asks the normative question of how a regulator should optimally use such predictions, embedding the empirical model inside a macroprudential optimal-policy framework designed to survive the Lucas critique so that the learned vulnerability measures inform welfare-improving policy rather than merely describing risk.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Two connected pieces. The empirical piece is a graph (network) neural network trained on security-level holdings of nearly all non-bank intermediaries; it learns compact representations of assets and investors from the web of who holds what, and is judged out-of-sample against existing risk metrics on two tasks, predicting intermediary trading and explaining returns during stress. The model's inductive design lets it score even assets or investors left out of training. The normative piece plugs these learned vulnerability measures into a macroprudential optimal-policy problem built to withstand the Lucas critique, showing how a regulator should use them.</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning in Finance, Financial Regulation, Systemic Risk</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>FactSet &amp; Morningstar — Security-level intermediary holdings</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="n"/>
+      <c r="L67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Ebsim, Lian, Ma, Ottonello, Perez</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Sophisticated Borrowing Constraints and Macroeconomic Dynamics</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>This paper argues that the way debt constraints are modeled fundamentally changes their macroeconomic implications. Traditional models impose hard borrowing limits that force firms to cut borrowing and investment whenever adverse shocks bind, producing financial acceleration. The authors instead model 'sophisticated borrowing constraints' resembling real-world financial covenants, where breaching an earnings-based debt threshold transfers control rights to creditors who then act to maximize their own value rather than mechanically shrinking credit. Calibrated to micro evidence on investment and earnings around covenant violations, the model matches firm-level dynamics while, at the macro level, generating no financial acceleration because violations do not trigger indiscriminate downscaling. The result challenges a workhorse mechanism linking credit conditions to aggregate fluctuations.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Standard macro models impose 'hard' borrowing limits under which any binding constraint mechanically forces firms to cut debt and investment, generating financial acceleration that amplifies aggregate shocks. The paper's central claim is that this modeling choice, rather than the existence of debt limits per se, drives the acceleration result. In reality, debt contracts are governed by financial covenants, so breaching an earnings-based threshold does not force proportional deleveraging but instead transfers control rights to creditors, who then choose firm policies to maximize their own claim value. The authors formalize this as a 'sophisticated' constraint in which the consequence of a violation is a state-contingent reallocation of control, not a fixed borrowing rule. They show first that such a model reproduces the microeconomic facts, matching how investment and earnings actually behave around covenant violations, so the mechanism is disciplined by observed firm behavior. They then embed it in general equilibrium and show that, because violations do not trigger indiscriminate, simultaneous downscaling across firms, the economy exhibits little or no financial acceleration. The upshot is that a more institutionally realistic constraint overturns a workhorse channel linking credit conditions to business cycles, implying that credit frictions may transmit very differently than standard models assume.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>A quantitative macro-finance model, distinguished by how it treats debt limits. Instead of a hard cap that forces proportional deleveraging when it binds, a covenant violation transfers control to creditors, who then choose the firm's policies. The model is first disciplined at the micro level by matching the observed behavior of investment and earnings around covenant violations, then solved in general equilibrium to ask whether it produces financial acceleration. Identification of the mechanism comes from comparing this covenant-style constraint against the standard hard-constraint benchmark while holding the rest of the model fixed.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Macro-Finance, Corporate Debt &amp; Covenants, Firm Investment</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Refinitiv LPC — DealScan; Greg Nini (Nini, Smith &amp; Sufi) — Financial covenant violation data</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Dou, Wang, Wang</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>The Cost of Intermediary Market Power for Distressed Borrowers</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>This paper measures how much lender market power raises borrowing costs for firms in financial distress, who must raise urgent financing in thin, concentrated credit markets. The authors show that distressed borrowers pay very high loan spreads even after stripping out compensation for credit risk, liquidity risk, and ordinary loan-making costs. To decompose the residual, they build and estimate a dynamic game-theoretic model of distressed lending featuring latent demand heterogeneity, endogenous lender participation, creditor blocking power, and tacit collusion sustained by repeated syndication. Lender market power explains 533 basis points of risk-adjusted spreads in debtor-in-possession (DIP) loans and 300 basis points in highly speculative loans, with roughly 140 basis points from tacit collusion in each. Because this markup reduces survival-critical liquidity by 16–20%, market power emerges as a major, previously underappreciated source of financial-distress costs.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Distressed firms must raise financing quickly and in markets served by only a handful of specialized lenders, often from existing creditors who hold contractual blocking power, so the high spreads these borrowers pay may reflect lender market power rather than compensation for risk. The paper first establishes the puzzle empirically, showing that even after removing compensation for credit risk, liquidity risk, and ordinary loan-making costs, debtor-in-possession and highly speculative loans still carry very large spreads. To interpret this residual, the authors build a dynamic game-theoretic model of distressed lending whose ingredients are latent heterogeneity in borrower demand, endogenous lender participation, the blocking power incumbent creditors wield in bankruptcy, and tacit collusion sustained by lenders' repeated interaction in syndication. The model makes the markup identifiable and, importantly, decomposable into a piece from unilateral market power and a piece from collusion. Estimating it lets the authors quantify how much of the spread is a pure markup, and then translate that markup into a real cost, because the markup drains cash from firms that need liquidity to survive and so maps into a measurable reduction in survival-critical funds. The argument thus moves from an unexplained pricing fact, to a structural mechanism, to a welfare-relevant consequence, reframing lender market power as a first-order and previously under-appreciated cost of financial distress.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>A structural estimation of a dynamic game of distressed lending. The authors first show, in a reduced-form step, that DIP and highly speculative loan spreads stay large even after subtracting compensation for credit risk, liquidity, and normal lending costs, leaving an unexplained residual. They then build a model in which a few lenders decide whether to lend, exploit the blocking power incumbent creditors hold in bankruptcy, and sustain tacit collusion through repeated syndication; fitting it to loan-level data lets them split the residual spread into unilateral-market-power and collusion components. The estimated model is finally used to express the markup as the reduction in liquidity it imposes on distressed borrowers. The unit of observation is the loan facility.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Financial Distress &amp; Bankruptcy, Banking &amp; Lending, Market Power / Industrial Organization</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Refinitiv LPC — DealScan; LPC (Refinitiv) — LSTA/LPC Mark-to-Market Pricing Data; PACER — Public Access to Court Electronic Records; Moody's — Default and Recovery Database</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - He et al. - Homemade Foreign Trading</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
           <t>He, Wang, Zhu</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Homemade Foreign Trading</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>This paper documents how Chinese mainland insiders disguise domestic trades as foreign investment by round-tripping capital through the Stock Connect program, a practice the authors term 'homemade foreign trading.' Using cross-border holding data from all custodians in Stock Connect, they show that northbound flows predict returns and correlate with insider trading, but that this predictability decays after the 2018 Northbound Investor Identification reform introduced see-through surveillance. The decay is concentrated among less prestigious foreign custodians and cross-operating mainland custodians, precisely where insiders can most easily hide. The reform also reduces price informativeness in stocks most exposed to homemade foreign investors. The paper highlights regulatory cooperation as a key ingredient for the integrity of cross-border capital market integration.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>Stock Connect lets mainland Chinese capital leave the country and return disguised as 'northbound' foreign investment, which opens a channel for informed mainland insiders to trade on private information while appearing to be offshore investors. The paper reasons that if such round-tripping is quantitatively important, aggregate northbound flows should predict future returns and should co-move with measured insider trading, because the disguised insiders are the ones driving the flow. It then argues that a reform giving regulators the ability to see through to the ultimate investor should break this link: once insiders can be identified, the informational rent they extract through the channel should shrink. The authors therefore treat the 2018 Northbound Investor Identification reform as a shock to surveillance and predict a decline in the return-predictability of northbound flows afterward. Crucially, they sharpen identification with cross-sectional heterogeneity in how easy it is to hide, since the effect should concentrate at less prestigious foreign custodians and at 'cross-operating' mainland custodians, precisely where disguising a domestic trade is cheapest. Because informed trading also contributes to price discovery, the paper predicts that removing the disguised-insider channel should reduce price informativeness for the most exposed stocks, tying the micro mechanism to an aggregate market-quality outcome.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>A difference-in-differences design built around the 2018 Northbound Investor Identification reform, treated as a natural experiment. The test is intuitive: if disguised insiders drive northbound flows, those flows should predict stock returns before the reform and predict them less once regulators can see who is trading. Using custodian-level flow data, the authors estimate how strongly northbound flows forecast returns and check whether that predictive power falls after the reform, concentrating the comparison on custodians where hiding was easiest. A complementary test asks whether prices became less informative for the most exposed stocks. The unit of analysis is the stock over time.</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>International Finance, Insider Trading, Market Microstructure</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>China Securities Depository and Clearing (CSDC) / Stock Connect; CSMAR — China Stock Market &amp; Accounting Research; WIND</t>
         </is>
       </c>
-      <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="n"/>
+      <c r="L70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2025 - Cabral and Dillender - Doctor Discretion in Medical Evaluations</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Cabral, Dillender</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Discretion in Medical Evaluations</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>This paper analyzes how the discretion of doctors conducting independent medical exams affects injured workers' outcomes. Exploiting the quasi-random assignment of claimants to more- or less-generous independent examiners, the authors trace downstream outcomes over three years—duration out of work, cash disability benefits, and subsequent medical care. Reduced-form estimates show that claimants assigned a more generous examiner experience longer durations out of work and receive more benefits and care. The results reveal that examiner discretion has large, persistent effects on disability outcomes. The paper documents the consequences of doctor discretion in a high-stakes evaluation setting.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>The paper studies independent medical exams, where a doctor's assessment shapes an injured worker's eligibility for disability benefits, and asks how much the specific examiner matters. It exploits the fact that claimants are effectively randomly assigned to examiners who differ in generosity, creating an examiner-leniency design. Because assignment is quasi-random, differences in outcomes across examiners of different generosity can be attributed to the examiner rather than the claimant. The authors follow claimants for three years, measuring duration out of work, cash benefits, and medical care. They find that being assigned a more generous examiner leads to longer time out of work and more benefits and care, though these also depend on later actions by claimants, insurers, and treating doctors. The paper concludes that doctor discretion in evaluations has substantial and lasting effects on disability outcomes.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>An examiner-assignment (leniency) design exploiting the quasi-random assignment of injured workers to independent medical examiners who differ in generosity, using administrative data. Reduced-form estimates relate assigned-examiner generosity to downstream outcomes—duration out of work, cash disability benefits, and subsequent medical care—over three years. The unit of analysis is the claimant; identification comes from quasi-random examiner assignment.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Health Economics, Disability Insurance, Public Economics</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Administrative workers' compensation / disability claims</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="n"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2025 - Cabral and Dillender - Doctor Discretion in Medical Evaluations.pdf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L21"/>
+  <autoFilter ref="A1:L71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1489,7 +4265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1553,29 +4329,25 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bureau van Dijk</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Orbis (Italy)</t>
-        </is>
-      </c>
+          <t>Administrative workers' compensation / disability claims</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Italian firm-level data used to replicate the U.S. analysis in a setting with deeper financial frictions.</t>
+          <t>Administrative records of injured workers, their independent medical exam assignments, benefits, and medical care, used in the examiner-assignment design.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>firm-level; Italy; cross-country</t>
+          <t>workers' compensation; disability; medical exams</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
@@ -1583,25 +4355,21 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Bornstein and Castillo-Martinez - Firm Exit and Financial Frictions</t>
+          <t>Working Paper - 2025 - Cabral and Dillender - Doctor Discretion in Medical Evaluations</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centers for Medicare &amp; Medicaid Services (CMS)</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Medicare DMEPOS claims</t>
-        </is>
-      </c>
+          <t>Angel investment and accreditation data</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Supplier- (NPI-) level Medicare durable medical equipment claims used to measure market shares, entry, and exit around the competitive-bidding reform.</t>
+          <t>Measures of angel investment activity and household accreditation (via housing-wealth thresholds) used to build the exposure shock.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1612,7 +4380,7 @@
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Medicare; DME; claims; suppliers</t>
+          <t>angel finance; accreditation</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
@@ -1620,36 +4388,32 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Diwan et al. - Competition and Fraud in Health Care</t>
+          <t>Journal of Financial Economics - 2026 - Lindsey and Stein - Angels, entrepreneurship, and employment dynamics Evidence from investor accreditation rules</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Chen &amp; Sacerdote (this paper)</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Congressional trading records</t>
-        </is>
-      </c>
+          <t>Authors' field experiment and survey</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Hand-collected transactions of all U.S. members of Congress and their immediate families, 2012-2023, from periodic financial-disclosure (STOCK Act) filings.</t>
+          <t>Randomized information treatments and a customized survey covering 24,000+ U.S. households, measuring ESG preferences, information frictions, and purchase intent.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>congressional trades; disclosures; hand-collected</t>
+          <t>field experiment; survey; ESG; consumers</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
@@ -1657,21 +4421,21 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Chen and Sacerdote - Capital in the Capitol Congressional Trades Resemble Uninformed Retail Trading</t>
+          <t>Journal of Accounting and Economics - 2026 - Leonelli et al. - How do consumers use ESG disclosure Evidence from a randomized field experiment with everyday product purchases</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>China Securities Depository and Clearing (CSDC) / Stock Connect</t>
+          <t>Auto loan / consumer credit data</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Cross-border holding and order data from all custodians in China's Stock Connect (northbound), including the 2018 Northbound Investor Identification reform, used to trace round-tripping insider flows.</t>
+          <t>Loan-level auto financing and purchase data used to measure the pass-through of tariffs to consumers.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1682,7 +4446,7 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>China; Stock Connect; custodians; cross-border holdings</t>
+          <t>auto loans; consumer credit; incidence</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
@@ -1690,32 +4454,36 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - He et al. - Homemade Foreign Trading</t>
+          <t>American Economic Review - 2026 - Hankins et al. - Consumer Credit and the Incidence of Tariffs Evidence from the Auto Industry</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Consumer transaction-data provider</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr"/>
+          <t>Banco de España</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Spanish Credit Register (CIRBE)</t>
+        </is>
+      </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Individual account- and transaction-level banking data used to measure NSF, overdraft, late, and maintenance fees and use of alternative financial services across households.</t>
+          <t>Supervisory loan-level credit-register data on Spanish banks' lending, rates, and performance, used to study merger effects.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>transaction-level; bank fees; households</t>
+          <t>credit register; Spain; bank mergers</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
@@ -1723,36 +4491,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Pagel et al. - Bank Fees and Household Financial Well-Being</t>
+          <t>Review of Financial Studies - 2026 - Mayordomo et al. - The Impact of Bank Consolidation on Credit Supply and Performance</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Context Analytics</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>S-Score (Twitter/X sentiment)</t>
-        </is>
-      </c>
+          <t>Bank regulatory records</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Security-level social-media sentiment scores derived from the Twitter/X firehose via proprietary NLP, used to proxy retail market sentiment.</t>
+          <t>FDIC enforcement actions, misconduct investigations, and Community Reinvestment Act ratings used to measure banks' regulatory pressure and outcomes.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>social media sentiment; retail; NLP</t>
+          <t>FDIC; CRA; enforcement</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
@@ -1760,25 +4524,25 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Chen and Sacerdote - Capital in the Capitol Congressional Trades Resemble Uninformed Retail Trading</t>
+          <t>Journal of Financial Economics - 2026 - Kaviani et al. - Reaching for influence Do banks use loans to establish political connections</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Correia, Luck &amp; Verner (this paper)</t>
+          <t>Bureau of Labor Statistics</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Historical bank-run database</t>
+          <t>Total Multifactor Productivity Tables</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Newly constructed database of 3,984 bank runs on individual U.S. banks, 1863-1934, extracted from historical newspapers using large language models.</t>
+          <t>Industry-level multifactor productivity and capital/automation-share measures used to discipline the model's quantitative illustrations.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1789,7 +4553,7 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>bank runs; historical; LLM-constructed</t>
+          <t>productivity; capital share; industries</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
@@ -1797,21 +4561,25 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+          <t>Quarterly Journal of Economics - 2026 - Acemoglu and Restrepo - Automation and Rent Dissipation Implications for Wages, Inequality, and Productivity</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Crunchbase</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr"/>
+          <t>Bureau van Dijk</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Orbis (Italy)</t>
+        </is>
+      </c>
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Startup and news-feed data used alongside PitchBook to identify fraud allegations.</t>
+          <t>Italian firm-level data used to replicate the U.S. analysis in a setting with deeper financial frictions.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1822,7 +4590,7 @@
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>startups; news; allegations</t>
+          <t>firm-level; Italy; cross-country</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
@@ -1830,36 +4598,36 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dyck et al. - Venture Fraud</t>
+          <t>Working Paper - 2026 - Bornstein and Castillo-Martinez - Firm Exit and Financial Frictions</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CSMAR</t>
+          <t>California / NAIC insurer disclosures</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>China Stock Market &amp; Accounting Research</t>
+          <t>Fossil-fuel investment filings</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Chinese firms' financial statements and corporate announcements used for firm characteristics and insider-trading events.</t>
+          <t>Publicly disclosed fossil-fuel investment holdings of U.S. insurers under the California mandate, with insurers' broader investment portfolios.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>China; accounting; announcements</t>
+          <t>insurers; fossil fuel; disclosure</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
@@ -1867,36 +4635,32 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - He et al. - Homemade Foreign Trading</t>
+          <t>Journal of Accounting and Economics - 2026 - Miller et al. - Mandatory disclosure of investors' fossil fuel holdings</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DOJ / HHS-OIG</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Fraud enforcement records</t>
-        </is>
-      </c>
+          <t>CEM Benchmarking</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Federal fraud enforcement actions - indictments, civil settlements, and program exclusions - used to identify fraudulent suppliers.</t>
+          <t>LP target and actual allocations used to measure underweighting and pressure to invest.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>fraud enforcement; exclusions; indictments</t>
+          <t>target allocations</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
@@ -1904,36 +4668,36 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Diwan et al. - Competition and Fraud in Health Care</t>
+          <t>Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Dyck, Fang, Hebert &amp; Xu (this paper)</t>
+          <t>Centers for Medicare &amp; Medicaid Services (CMS)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Venture-fraud case sample</t>
+          <t>Medicare DMEPOS claims</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Hand-collected sample of 614 U.S. VC-backed startups facing fraud charges (SEC, DOJ, and civil litigation) since 2000, with fraud commitment periods.</t>
+          <t>Supplier- (NPI-) level Medicare durable medical equipment claims used to measure market shares, entry, and exit around the competitive-bidding reform.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>venture fraud; hand-collected; litigation</t>
+          <t>Medicare; DME; claims; suppliers</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
@@ -1941,36 +4705,36 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dyck et al. - Venture Fraud</t>
+          <t>Working Paper - 2026 - Diwan et al. - Competition and Fraud in Health Care</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FactSet &amp; Morningstar</t>
+          <t>Central Pollution Control Board (India)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Security-level intermediary holdings</t>
+          <t>Air-quality monitoring stations</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Holdings data covering the universe of non-bank financial intermediaries (mutual funds, ETFs, separate accounts, etc.), ~$40 trillion, used to train the holdings-network model.</t>
+          <t>Locations, timing, and readings of air-quality monitoring stations, providing the pollution-information shock.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>holdings network; non-bank intermediaries; fire sales</t>
+          <t>air quality; monitoring stations; India</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
@@ -1978,25 +4742,25 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Clayton and Coppola - The Optimal Use of AI in Financial Regulation</t>
+          <t>Journal of Financial Economics - 2026 - Fisman et al. - Dirty air and green investments The impact of pollution information on portfolio allocations</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FDIC</t>
+          <t>Chen &amp; Sacerdote (this paper)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Summary of Deposits</t>
+          <t>Congressional trading records</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Branch/deposit data used to determine which metropolitan areas were exposed to each bank's policy change.</t>
+          <t>Hand-collected transactions of all U.S. members of Congress and their immediate families, 2012-2023, from periodic financial-disclosure (STOCK Act) filings.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2007,7 +4771,7 @@
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>deposits; branch exposure; MSA</t>
+          <t>congressional trades; disclosures; hand-collected</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
@@ -2015,36 +4779,32 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Pagel et al. - Bank Fees and Household Financial Well-Being</t>
+          <t>Working Paper - 2026 - Chen and Sacerdote - Capital in the Capitol Congressional Trades Resemble Uninformed Retail Trading</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FDIC</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Historical Bank Data</t>
-        </is>
-      </c>
+          <t>China Securities Depository and Clearing (CSDC) / Stock Connect</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Aggregate historical deposits and deposit interest expense used to characterize Reg Q-era bank funding.</t>
+          <t>Cross-border holding and order data from all custodians in China's Stock Connect (northbound), including the 2018 Northbound Investor Identification reform, used to trace round-tripping insider flows.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>historical deposits; Reg Q</t>
+          <t>China; Stock Connect; custodians; cross-border holdings</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
@@ -2052,36 +4812,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
+          <t>Working Paper - 2026 - He et al. - Homemade Foreign Trading</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Federal Reserve</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>FR Y-14 supervisory data</t>
-        </is>
-      </c>
+          <t>Close-election and political-connection data</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Confidential loan-level data on commercial and industrial loans at the largest U.S. banks, collected for Dodd-Frank stress testing, used to measure rate dispersion and borrower/loan characteristics.</t>
+          <t>Congressional election margins and firm-politician ties used to construct quasi-random political connections.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>supervisory; C&amp;I loans; bank stress test</t>
+          <t>close elections; connections</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
@@ -2089,25 +4845,21 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Amiti et al. - Why Do Firms Pay Different Interest Rates on Their Bank Loans</t>
+          <t>Journal of Financial Economics - 2026 - Kaviani et al. - Reaching for influence Do banks use loans to establish political connections</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Federal Reserve</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Senior Loan Officer Opinion Survey (SLOOS)</t>
-        </is>
-      </c>
+          <t>Compensation peer-group disclosures</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Bank lending-standards survey (back to 1964) used as a measure of credit tightening.</t>
+          <t>Firms' disclosed executive-compensation peer groups (proxy statements) used to measure peer additions and drops.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2118,7 +4870,7 @@
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>lending standards; SLOOS</t>
+          <t>peer groups; executive pay</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
@@ -2126,25 +4878,21 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
+          <t>Working Paper - 2026 - Ormazabal and Shi - Industry (Re)Classifications and Corporate Governance</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Atlanta</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Diary of Consumer Payment Choice (DCPC)</t>
-        </is>
-      </c>
+          <t>Compensation peer-group disclosures (SEC proxy filings)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Consumer payment-diary data on payment-method use and shopping, used to measure sorting across merchant sectors.</t>
+          <t>Firms' disclosed executive-compensation peer groups from proxy statements, aggregated into a benchmarking network.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2155,7 +4903,7 @@
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>consumer payments; diary; sorting</t>
+          <t>peer groups; executive pay; proxy</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
@@ -2163,36 +4911,32 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Egan et al. - Who Pays for Payments</t>
+          <t>Journal of Accounting Research - 2026 - Gao and Lu - Aggregated Compensation Peer Group Disclosure and Managerial Labor Market Competition A Network Analysis</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Atlanta &amp; Duke University</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Survey of corporate executives</t>
-        </is>
-      </c>
+          <t>Compensation-software provider (national payroll)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Novel survey of nearly 750 corporate executives on AI adoption, productivity effects, and workforce plans, benchmarked to the U.S. Census industry/size distribution.</t>
+          <t>Large-scale, anonymized national payroll/compensation records with market salary benchmarks by job title (mapped to O*NET codes), used to study firms adopting a salary-benchmarking tool.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>executive survey; AI adoption; productivity</t>
+          <t>payroll; salaries; benchmarking; O*NET</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
@@ -2200,36 +4944,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Baslandze et al. - Artificial Intelligence, Productivity, and the Workforce Evidence from Corporate Executives</t>
+          <t>Review of Economic Studies - 2026 - Cullen et al. - What's My Employee Worth The Effects of Salary Benchmarking</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FHFA</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>House Price Index</t>
-        </is>
-      </c>
+          <t>Consumer transaction-data provider</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Regional house-price data (pre-sample 1975-2004) used to build instruments and proxy property values.</t>
+          <t>Individual account- and transaction-level banking data used to measure NSF, overdraft, late, and maintenance fees and use of alternative financial services across households.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>house prices; property values</t>
+          <t>transaction-level; bank fees; households</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
@@ -2237,21 +4977,25 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+          <t>Working Paper - 2026 - Pagel et al. - Bank Fees and Household Financial Well-Being</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr"/>
+          <t>Context Analytics</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>S-Score (Twitter/X sentiment)</t>
+        </is>
+      </c>
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Two proprietary datasets from Fiserv, a large U.S. merchant acquirer, on the composition and cost (interchange/settlement) of payments across merchants.</t>
+          <t>Security-level social-media sentiment scores derived from the Twitter/X firehose via proprietary NLP, used to proxy retail market sentiment.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2262,7 +5006,7 @@
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>merchant acquiring; interchange; settlement</t>
+          <t>social media sentiment; retail; NLP</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
@@ -2270,36 +5014,32 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Egan et al. - Who Pays for Payments</t>
+          <t>Working Paper - 2026 - Chen and Sacerdote - Capital in the Capitol Congressional Trades Resemble Uninformed Retail Trading</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Greg Nini (Nini, Smith &amp; Sufi)</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Financial covenant violation data</t>
-        </is>
-      </c>
+          <t>Contract-enforcement and product-complexity measures</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Hand-shared extended data on financial covenant violations disclosed in firms' filings, 1996 onward, used to construct micro moments around violations.</t>
+          <t>Cross-country contract-enforcement indicators and product-complexity/differentiation classifications used as institutional moderators.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>covenant violations; control rights</t>
+          <t>contract enforcement; product complexity</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
@@ -2307,36 +5047,32 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics</t>
+          <t>Journal of Financial Economics - 2026 - Benguria et al. - Trade credit and relationships</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Chronicling America</t>
-        </is>
-      </c>
+          <t>Corporate litigation and settlement data</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Large-scale archive of digitized historical U.S. newspapers, the main source for detecting and dating bank runs.</t>
+          <t>Data on corporate/securities lawsuits, settlements, plaintiff law firms, and defendants' litigation-insurance coverage, used to study star law firms.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>historical newspapers; text source</t>
+          <t>litigation; settlements; law firms</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
@@ -2344,36 +5080,36 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+          <t>Journal of Accounting Research - 2026 - Ferrell et al. - Corporate Litigation, Governance, and the Role of Law Firms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>LPC (Refinitiv)</t>
+          <t>Correia, Luck &amp; Verner (this paper)</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>LSTA/LPC Mark-to-Market Pricing Data</t>
+          <t>Historical bank-run database</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Secondary-market loan trading/pricing data used to measure loan liquidity and pricing.</t>
+          <t>Newly constructed database of 3,984 bank runs on individual U.S. banks, 1863-1934, extracted from historical newspapers using large language models.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>secondary loan prices; liquidity</t>
+          <t>bank runs; historical; LLM-constructed</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
@@ -2381,25 +5117,21 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Moody's</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Default and Recovery Database</t>
-        </is>
-      </c>
+          <t>Crunchbase</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Nominal recovery rates aggregated by industry, used in the risk-adjustment of spreads.</t>
+          <t>Startup and news-feed data used alongside PitchBook to identify fraud allegations.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2410,7 +5142,7 @@
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>defaults; recoveries</t>
+          <t>startups; news; allegations</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
@@ -2418,73 +5150,73 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+          <t>Working Paper - 2026 - Dyck et al. - Venture Fraud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MSRB</t>
+          <t>CSMAR</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Municipal Securities Rulemaking Board trade data</t>
+          <t>China Stock Market &amp; Accounting Research</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Secondary-market municipal bond trades used to construct city-level bond spreads.</t>
+          <t>Chinese firms' financial statements and corporate announcements used for firm characteristics and insider-trading events. Chinese prices, financials, M&amp;A, and suspensions used to build variables and validate responses.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>municipal bonds; spreads; secondary market</t>
+          <t>China; accounting; announcements; prices; M&amp;A</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+          <t>Working Paper - 2026 - He et al. - Homemade Foreign Trading; Journal of Financial Economics - 2026 - Goldstein et al. - Market feedback Evidence from the horse's mouth</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>NBER-CES</t>
+          <t>CSRC &amp; Tsinghua PBCSF</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing Industry Database</t>
+          <t>Survey of Chinese public firms (2019, 2022)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Industry-level prices and quantities (derived from the U.S. Census) used to test cross-industry supply effects.</t>
+          <t>Two near-population surveys (response rates 99.9% and 98.1%) on whether/why firms monitor prices and what they learn.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>manufacturing; prices; quantities</t>
+          <t>survey; learning; China</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
@@ -2492,32 +5224,32 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
+          <t>Journal of Financial Economics - 2026 - Goldstein et al. - Market feedback Evidence from the horse's mouth</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Nilson Report</t>
+          <t>Current Population Survey (CPS)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Industry statistics on interchange and network fees used to benchmark payment costs.</t>
+          <t>Worker-flow data on temporary layoffs, recall, and unemployment transitions used to calibrate and test the model.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>interchange; network fees; benchmarks</t>
+          <t>CPS; layoffs; unemployment flows</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
@@ -2525,25 +5257,21 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Egan et al. - Who Pays for Payments</t>
+          <t>American Economic Review - 2026 - Gertler et al. - Temporary Layoffs, Loss-of-Recall, and Cyclical Unemployment Dynamics</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>OCC</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>National bank call reports (Annual Report to Congress)</t>
-        </is>
-      </c>
+          <t>Debt-contract voting/amendment provisions (EDGAR)</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Balance-sheet data for national banks used to measure bank fundamentals and outcomes.</t>
+          <t>Hand-collected voting-rule and amendment-threshold terms from credit agreements filed with the SEC, used to test the model's comparative statics.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2554,7 +5282,7 @@
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>call reports; bank balance sheets; fundamentals</t>
+          <t>credit agreements; voting rules; covenants</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
@@ -2562,36 +5290,36 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+          <t>Journal of Accounting Research - 2026 - Caskey et al. - Amendment Thresholds and Voting Rules in Debt Contracts</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PACER</t>
+          <t>DeVault, Sias &amp; Starks (2019)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Public Access to Court Electronic Records</t>
+          <t>Institutional classification (57 types)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>U.S. bankruptcy court records used to identify DIP financing and Chapter 11 cases.</t>
+          <t>Fine-grained institution-type classifications used to identify trusts.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>bankruptcy; DIP; court records</t>
+          <t>institution types; trusts</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
@@ -2599,32 +5327,36 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+          <t>Journal of Financial Economics - 2026 - Cassella et al. - Constrained by law The impact of fiduciary duties on portfolios and prices in US equity markets</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PitchBook</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr"/>
+          <t>DOJ / HHS-OIG</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Fraud enforcement records</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Venture-capital-backed startups, their founders, financing rounds, and cap-table/board structures, used to build the sample and governance variables.</t>
+          <t>Federal fraud enforcement actions - indictments, civil settlements, and program exclusions - used to identify fraudulent suppliers.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>venture capital; startups; cap tables</t>
+          <t>fraud enforcement; exclusions; indictments</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
@@ -2632,32 +5364,36 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dyck et al. - Venture Fraud</t>
+          <t>Working Paper - 2026 - Diwan et al. - Competition and Fraud in Health Care</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Preqin</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr"/>
+          <t>Dyck, Fang, Hebert &amp; Xu (this paper)</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Venture-fraud case sample</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Industry-level private-credit assets used to gauge coverage and situate the sample within the broader market.</t>
+          <t>Hand-collected sample of 614 U.S. VC-backed startups facing fraud charges (SEC, DOJ, and civil litigation) since 2000, with fraud commitment periods.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>private credit; industry assets</t>
+          <t>venture fraud; hand-collected; litigation</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
@@ -2665,21 +5401,25 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Matvos et al. - Private Credit, Balance Sheets and Financial Stability</t>
+          <t>Working Paper - 2026 - Dyck et al. - Venture Fraud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Proprietary private-credit data provider</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr"/>
+          <t>FactSet &amp; Morningstar</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Security-level intermediary holdings</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>New proprietary fund- and asset-level data covering roughly 1,300 private-credit funds and their loans (capitalization, funding, maturities, performance), covering most of the industry.</t>
+          <t>Holdings data covering the universe of non-bank financial intermediaries (mutual funds, ETFs, separate accounts, etc.), ~$40 trillion, used to train the holdings-network model.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2690,7 +5430,7 @@
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>private credit; funds; balance sheets</t>
+          <t>holdings network; non-bank intermediaries; fire sales</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
@@ -2698,36 +5438,36 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Matvos et al. - Private Credit, Balance Sheets and Financial Stability</t>
+          <t>Working Paper - 2026 - Clayton and Coppola - The Optimal Use of AI in Financial Regulation</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Refinitiv LPC</t>
+          <t>FDIC</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>DealScan</t>
+          <t>Summary of Deposits</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Loan-level covenant terms (e.g., debt-to-EBITDA covenants) used to identify firms subject to earnings-based constraints. Facility-level syndicated loan terms used to build the sample of debtor-in-possession and highly speculative loans.</t>
+          <t>Branch/deposit data used to determine which metropolitan areas were exposed to each bank's policy change. Annual branch-level deposit data (2007-2021) used to characterize deposit sizes and market structure.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>syndicated loans; DIP; facilities; loan covenants; debt-to-EBITDA</t>
+          <t>deposits; branch exposure; MSA; branches; market structure</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
@@ -2735,25 +5475,25 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers; Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics</t>
+          <t>Working Paper - 2026 - Pagel et al. - Bank Fees and Household Financial Well-Being; Working Paper - 2026 - Lu and Wu - Banking on Inattention</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Robert Shiller</t>
+          <t>FDIC</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Investor Confidence Survey</t>
+          <t>Historical Bank Data</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Investor-confidence survey data used as a comparison measure of investor beliefs.</t>
+          <t>Aggregate historical deposits and deposit interest expense used to characterize Reg Q-era bank funding.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2764,7 +5504,7 @@
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>investor confidence; beliefs</t>
+          <t>historical deposits; Reg Q</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
@@ -2772,32 +5512,36 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P Capital IQ</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr"/>
+          <t>FDIC / WestLaw</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>UPIA adoption dates</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Supplementary financial data used to improve customer-capital expense measures.</t>
+          <t>Hand-collected state-by-state UPIA statutes and effective dates.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>financials; customer capital</t>
+          <t>UPIA; state law</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
@@ -2805,69 +5549,73 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Eisfeldt et al. - Intangible Intensity</t>
+          <t>Journal of Financial Economics - 2026 - Cassella et al. - Constrained by law The impact of fiduciary duties on portfolios and prices in US equity markets</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SEC (WRDS SEC Analytics Suite)</t>
+          <t>Federal Reserve</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>10-K filings</t>
+          <t>FR Y-14 supervisory data</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Full-text corporate 10-K filings, accessed via the WRDS SEC Analytics Suite, used to build the text-based intangible-intensity measure.</t>
+          <t>Confidential loan-level data on commercial and industrial loans at the largest U.S. banks, collected for Dodd-Frank stress testing, used to measure rate dispersion and borrower/loan characteristics. Confidential bank-reported loan-level data on commercial and industrial loans, used to measure private firms' borrowing.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>10-K; disclosure text; NLP</t>
+          <t>supervisory; C&amp;I loans; bank stress test; private firms</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Eisfeldt et al. - Intangible Intensity</t>
+          <t>Working Paper - 2026 - Amiti et al. - Why Do Firms Pay Different Interest Rates on Their Bank Loans; Review of Economic Studies - 2026 - Ivanov et al. - Taxes Depress Corporate Borrowing Evidence from Private Firms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>U.S. Call Reports (via FOIA)</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr"/>
+          <t>Federal Reserve</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Senior Loan Officer Opinion Survey (SLOOS)</t>
+        </is>
+      </c>
       <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Bank-level regulatory balance-sheet data obtained back to 1959 through a Freedom of Information Act request, used to measure deposits and lending contractions.</t>
+          <t>Bank lending-standards survey (back to 1964) used as a measure of credit tightening.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>call reports; bank lending; 1959-</t>
+          <t>lending standards; SLOOS</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
@@ -2882,18 +5630,18 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>U.S. Census Bureau</t>
+          <t>Federal Reserve Bank of Atlanta</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>LODES (LEHD Origin-Destination Employment Statistics)</t>
+          <t>Diary of Consumer Payment Choice (DCPC)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Sector-level job counts used to measure a city's industrial concentration.</t>
+          <t>Consumer payment-diary data on payment-method use and shopping, used to measure sorting across merchant sectors.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2904,7 +5652,7 @@
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>employment; industry concentration; LODES</t>
+          <t>consumer payments; diary; sorting</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
@@ -2912,25 +5660,25 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+          <t>Working Paper - 2026 - Egan et al. - Who Pays for Payments</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>U.S. Census Bureau</t>
+          <t>Federal Reserve Bank of Atlanta &amp; Duke University</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>LEHD merged with Longitudinal Business Database (LBD)</t>
+          <t>Survey of corporate executives</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Confidential administrative data on establishment-level wage bill and employment used to measure local monopsony power and firm responses to monetary policy.</t>
+          <t>Novel survey of nearly 750 corporate executives on AI adoption, productivity effects, and workforce plans, benchmarked to the U.S. Census industry/size distribution.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2941,7 +5689,7 @@
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>administrative; wage bill; employment; monopsony</t>
+          <t>executive survey; AI adoption; productivity</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
@@ -2949,36 +5697,36 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Bardóczy et al. - Monopsony Power and the Transmission of Monetary Policy</t>
+          <t>Working Paper - 2026 - Baslandze et al. - Artificial Intelligence, Productivity, and the Workforce Evidence from Corporate Executives</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>U.S. Census Bureau</t>
+          <t>FHFA</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Business Database (LBD)</t>
+          <t>House Price Index</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Confidential data tracking entry and exit for the universe of U.S. employers, used to estimate the debt–exit relationship.</t>
+          <t>Regional house-price data (pre-sample 1975-2004) used to build instruments and proxy property values.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>firm entry/exit; universe of employers</t>
+          <t>house prices; property values</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
@@ -2986,32 +5734,36 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Bornstein and Castillo-Martinez - Firm Exit and Financial Frictions</t>
+          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>UBS/Gallup and Livingston Survey</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr"/>
+          <t>FINRA</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>TRACE (enhanced, with dealer identifiers)</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Survey measures of individual-investor and professional-forecaster return/earnings expectations used for comparison.</t>
+          <t>Transaction-level corporate bond trades including masked dealer identities, used to reconstruct trading networks and measure performance.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>investor surveys; forecaster expectations</t>
+          <t>corporate bonds; dealers; networks</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
@@ -3019,32 +5771,32 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+          <t>Journal of Accounting and Economics - 2026 - Huber et al. - Information flows in trading networks</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Value Line Investment Survey</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Analyst forecasts hand-collected from microfilm records (1956-2024) used to construct a long-run series of sophisticated investors' subjective expected returns.</t>
+          <t>Two proprietary datasets from Fiserv, a large U.S. merchant acquirer, on the composition and cost (interchange/settlement) of payments across merchants.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>subjective expectations; analyst forecasts; microfilm</t>
+          <t>merchant acquiring; interchange; settlement</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
@@ -3052,32 +5804,32 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+          <t>Working Paper - 2026 - Egan et al. - Who Pays for Payments</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>WIND</t>
+          <t>French nonfinancial disclosure filings</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Adjusted opening prices and free-floating shares for Chinese listed stocks.</t>
+          <t>French firms' nonfinancial disclosures used to test compliance with a mandate as an application of the measure.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>China; prices; shares</t>
+          <t>France; nonfinancial disclosure</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
@@ -3085,49 +5837,2474 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - He et al. - Homemade Foreign Trading</t>
+          <t>Journal of Accounting Research - 2026 - Boulland et al. - Company Websites A New Measure of Disclosure</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Yunan Ji</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Medicare DME auction bids</t>
-        </is>
-      </c>
+          <t>Fundmap</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Bids submitted in Medicare's DME competitive-bidding auctions, shared by the author, used in the bidding analysis.</t>
+          <t>Data on LPs' use of specialized search consultants.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
+          <t>search consultants</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GICS reclassification data (MSCI/S&amp;P)</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Changes in firms' Global Industry Classification Standard codes, used as exogenous variation in industry membership.</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>GICS; reclassification; industry</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Ormazabal and Shi - Industry (Re)Classifications and Corporate Governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Greg Nini (Nini, Smith &amp; Sufi)</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Financial covenant violation data</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Hand-shared extended data on financial covenant violations disclosed in firms' filings, 1996 onward, used to construct micro moments around violations.</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>covenant violations; control rights</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Historical railroad bond prices/yields</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Secondary-market prices, yields, and bid-ask spreads for early-1900s railroad bonds, used to measure market reactions to ratings.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>bond yields; bid-ask; historical</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Bernstein - The Value of Ratings Evidence from Their Introduction in Securities Markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Hoberg-Phillips</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>TNIC</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Text-based product-market similarity network used to measure competitors and encroachment.</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>product market; competition</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language models</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Indian retail investor trading records</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Account-level holdings and trades of ~19 million Indian retail investors, used to measure brown-stock holdings.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>retail investors; India; holdings</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Fisman et al. - Dirty air and green investments The impact of pollution information on portfolio allocations</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Insider trading filings (Form 4)</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Bidder managers' insider trades used to gauge managerial belief in deals.</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>insider trades; managers</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Review of Financial Studies - 2026 - Filipović and Wagner - The Intangibles Song in Takeover Announcements Good Tempo, Hollow Tune</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Institute for Private Capital</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Failed-fund data</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Funds that failed to raise capital, used to build non-selected opportunity sets.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>failed funds</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Internet Archive</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Historical website (Wayback) data</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Archived snapshots of firms' company websites used to construct the disclosure measure.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>websites; disclosure; web archive</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting Research - 2026 - Boulland et al. - Company Websites A New Measure of Disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>IRS</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Taxpayer Assistance Center locations</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Locations and coverage of IRS Taxpayer Assistance Centers used to measure local access to tax help.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>IRS; tax assistance; access</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Armstrong and Glaeser - Does taxpayer assistance encourage entrepreneurship</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>IRS</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Statistics of Income (Schedule C)</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Local self-employment/Schedule C business income and entry data used to measure entrepreneurship.</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Schedule C; entrepreneurship; income</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Armstrong and Glaeser - Does taxpayer assistance encourage entrepreneurship</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>ISS Incentive Lab</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Executive incentive-plan data</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Detailed executive compensation and performance-metric data used to measure the number and dissimilarity of metrics in incentive contracts.</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>executive pay; performance metrics</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Guay et al. - Internal information quality and performance metric selection</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>KPSS patent value database</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Kogan, Papanikolaou, Seru &amp; Stoffman (2017)</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Dollar valuations of individual patents, used to weight firms' Alice-exposed patents. Market-based patent values used in validating innovation outcomes.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>patent value; innovation</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language models; Journal of Financial Economics - 2026 - Woeppel and Yavuz - Measuring firms' capability to absorb external knowledge</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Library of Congress</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Chronicling America</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Large-scale archive of digitized historical U.S. newspapers, the main source for detecting and dating bank runs.</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>historical newspapers; text source</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>LPC (Refinitiv)</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>LSTA/LPC Mark-to-Market Pricing Data</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Secondary-market loan trading/pricing data used to measure loan liquidity and pricing.</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>secondary loan prices; liquidity</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Default and Recovery Database</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Nominal recovery rates aggregated by industry, used in the risk-adjustment of spreads.</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>defaults; recoveries</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Moody's (1909)</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>First-ever railroad bond ratings</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Hand-collected letter ratings from John Moody's 1909 publication covering most listed railroad bonds.</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>ratings; railroad bonds; 1909</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Bernstein - The Value of Ratings Evidence from Their Introduction in Securities Markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>MSRB</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Securities Rulemaking Board trade data</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Secondary-market municipal bond trades used to construct city-level bond spreads.</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>municipal bonds; spreads; secondary market</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>NBER-CES</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing Industry Database</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Industry-level prices and quantities (derived from the U.S. Census) used to test cross-industry supply effects.</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>manufacturing; prices; quantities</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>NBER–USPTO</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Historical Patent Data Files (Marco et al. 2015)</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Comprehensive data on U.S. patent applications used to construct a forward-looking instrument for technology news shocks.</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>patents; applications; news shocks; instrument</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Review of Economic Studies - 2026 - Miranda-Agrippino et al. - Patents, News, and Business Cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>NielsenIQ (Nielsen Consumer LLC)</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Retail scanner data</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Product-level retail prices and quantities for packaged-goods categories, used to measure pass-through in the food-products setting.</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>retail scanner; prices; food</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly Journal of Economics - 2026 - Sangani - Complete Pass-Through in Levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Nilson Report</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Industry statistics on interchange and network fees used to benchmark payment costs.</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>interchange; network fees; benchmarks</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Egan et al. - Who Pays for Payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Norwegian Central Securities Depository (VPS)</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>All individual stock transactions on the Oslo Stock Exchange, 1997-2014.</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>individual trades; Norway</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Hvide and Nielsen - Flying below the radar Insider trading by executives below the top</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Norwegian registers (LLC ownership; population)</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>LLC ownership and family links used to study indirect trades.</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>LLC; family links</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Hvide and Nielsen - Flying below the radar Insider trading by executives below the top</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>OCC</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>National bank call reports (Annual Report to Congress)</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Balance-sheet data for national banks used to measure bank fundamentals and outcomes.</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>call reports; bank balance sheets; fundamentals</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Oslo Stock Exchange</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Daily prices and market capitalization used to compute returns.</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>prices; market cap</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Hvide and Nielsen - Flying below the radar Insider trading by executives below the top</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>PACER</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Public Access to Court Electronic Records</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>U.S. bankruptcy court records used to identify DIP financing and Chapter 11 cases.</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>bankruptcy; DIP; court records</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>PitchBook</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Venture-capital-backed startups, their founders, financing rounds, and cap-table/board structures, used to build the sample and governance variables.</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>venture capital; startups; cap tables</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Dyck et al. - Venture Fraud</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Preqin</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>LP capital commitments and fund-level performance (IRR, TVPI), AuM, and flags for private-market funds 1995-2019. Industry-level private-credit assets used to gauge coverage and situate the sample within the broader market.</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>private credit; industry assets; private equity; commitments; IRR</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Matvos et al. - Private Credit, Balance Sheets and Financial Stability; Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary private-credit data provider</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>New proprietary fund- and asset-level data covering roughly 1,300 private-credit funds and their loans (capitalization, funding, maturities, performance), covering most of the industry.</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>private credit; funds; balance sheets</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Matvos et al. - Private Credit, Balance Sheets and Financial Stability</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary retail deposit data provider</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Transaction- and account-level data on retail deposit balances and activity, used to study the distribution and dynamics of household deposits.</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>transaction-level; retail deposits; accounts</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Argyle et al. - The Dynamics of Retail Deposit Balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary transaction-level data provider</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Household transaction-level data used to measure depositor inattention and the responsiveness of deposit balances to rate changes.</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>transaction-level; deposits; inattention</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Lu and Wu - Banking on Inattention</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>RavenPack</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr"/>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Macroeconomic news and announcement data used to identify concurrent macro information.</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>macro news; announcements</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting Research - 2026 - Ferracuti and Lind - Macroeconomic Information Acquisition Around Earnings Clusters</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Refinitiv LPC</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>DealScan</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Loan-level covenant terms (e.g., debt-to-EBITDA covenants) used to identify firms subject to earnings-based constraints. Facility-level syndicated loan terms used to build the sample of debtor-in-possession and highly speculative loans. Syndicated loan terms used to measure loan pricing and covenants for connected and non-connected firms.</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>syndicated loans; DIP; facilities; loan covenants; debt-to-EBITDA; terms</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers; Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics; Journal of Financial Economics - 2026 - Kaviani et al. - Reaching for influence Do banks use loans to establish political connections</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>RelSci</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Personal/professional links between LP and GP employees.</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>personal networks</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Retail gasoline price microdata</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Station-level retail gasoline prices and wholesale input costs used to measure pass-through at gas stations.</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>gasoline; station prices; pass-through</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly Journal of Economics - 2026 - Sangani - Complete Pass-Through in Levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Robert Shiller</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Investor Confidence Survey</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr"/>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Investor-confidence survey data used as a comparison measure of investor beliefs.</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>investor confidence; beliefs</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P Capital IQ</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Supplementary financial data used to improve customer-capital expense measures.</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>financials; customer capital</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Eisfeldt et al. - Intangible Intensity</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Form D filings</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr"/>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Regulation D filings used to identify failed first-time fundraising.</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Bulk</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Form D; first-time funds</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Office jurisdictions / enforcement geography</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr"/>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Assignment of firms to SEC district/regional offices and the 2007 reorganization, used to define treated jurisdictions.</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>SEC; jurisdictions; enforcement</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Weber et al. - SEC scrutiny and corporate risk-taking</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>SEC (WRDS SEC Analytics Suite)</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>10-K filings</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr"/>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Full-text corporate 10-K filings, accessed via the WRDS SEC Analytics Suite, used to build the text-based intangible-intensity measure.</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>10-K; disclosure text; NLP</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Eisfeldt et al. - Intangible Intensity</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>SEC EDGAR log files</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Records of investors' access to firms' filings, used to proxy information acquisition around earnings clusters.</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>EDGAR logs; information acquisition</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting Research - 2026 - Ferracuti and Lind - Macroeconomic Information Acquisition Around Earnings Clusters</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>SEC Form ADV (hedge-fund adviser filings)</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr"/>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Investment-adviser regulatory disclosures of operational and investment risks, compared with other public information to identify inconsistencies.</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Form ADV; hedge funds; disclosure</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting Research - 2026 - Liu et al. - Strategic (Inconsistent) Disclosures and Sophisticated Investors Evidence from Hedge Funds</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Stanford NPE Litigation Database / PACER</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>U.S. patent-infringement lawsuits (NPE vs operating company) used to measure litigation exposure.</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>patent litigation; NPE</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language models</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>State corporate income tax data</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr"/>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>State-by-year corporate income tax rates and tax-base rules (e.g., depreciation and apportionment), hand-collected/extended, used as variation in the tax incentive to borrow.</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>state taxes; corporate income; leverage</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Review of Economic Studies - 2026 - Ivanov et al. - Taxes Depress Corporate Borrowing Evidence from Private Firms</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Statistics Norway</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Employer-employee register (ISCO-88)</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr"/>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Population employer-employee data identifying each individual's position and demographics.</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>employer-employee; occupation</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Hvide and Nielsen - Flying below the radar Insider trading by executives below the top</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Supply-chain relationship data</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr"/>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Customer-supplier links used to identify U.S. manufacturers exposed to Taiwanese supply-chain disruption, combined with firm financials to compute productivity.</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>supply chain; customer-supplier; productivity</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Berger and Tomy - Supply chain shocks and firm productivity The role of reporting quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Takeover announcement texts (intangibles word list)</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr"/>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Text of takeover announcements scored with a purpose-built intangibles word list, used to measure 'intangibles talk'.</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A; text; intangibles</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Review of Financial Studies - 2026 - Filipović and Wagner - The Intangibles Song in Takeover Announcements Good Tempo, Hollow Tune</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Transaction-level international trade (customs) data</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr"/>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Firm-to-firm customs transactions with values, timing, payment terms, and partner identities, used to measure relationships and trade credit.</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>customs; trade; firm-to-firm</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Benguria et al. - Trade credit and relationships</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Call Reports (via FOIA)</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr"/>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Bank-level regulatory balance-sheet data obtained back to 1959 through a Freedom of Information Act request, used to measure deposits and lending contractions.</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>call reports; bank lending; 1959-</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Census Bureau</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>LODES (LEHD Origin-Destination Employment Statistics)</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr"/>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Sector-level job counts used to measure a city's industrial concentration.</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>employment; industry concentration; LODES</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Census Bureau</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>LEHD merged with Longitudinal Business Database (LBD)</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr"/>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Confidential administrative data on establishment-level wage bill and employment used to measure local monopsony power and firm responses to monetary policy.</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>administrative; wage bill; employment; monopsony</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Bardóczy et al. - Monopsony Power and the Transmission of Monetary Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Census Bureau</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Longitudinal Business Database (LBD)</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr"/>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Confidential data tracking entry and exit for the universe of U.S. employers, used to estimate the debt–exit relationship.</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>firm entry/exit; universe of employers</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Bornstein and Castillo-Martinez - Firm Exit and Financial Frictions</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Census Bureau</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Annual Survey of Manufactures / Census of Manufactures</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr"/>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Establishment-level production, cost, and price data used to measure pass-through in manufacturing.</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>manufacturing; costs; production</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly Journal of Economics - 2026 - Sangani - Complete Pass-Through in Levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Census Bureau</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Longitudinal Business Database / firm microdata</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr"/>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Confidential firm entry and employment data used to measure entrepreneurship outcomes.</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>firm entry; employment; Census</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Lindsey and Stein - Angels, entrepreneurship, and employment dynamics Evidence from investor accreditation rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Department of Transportation</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>DB1B (Airline Origin and Destination Survey)</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr"/>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Route-level airline ticket prices and quantities used to measure competitive responses to the tax reform.</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>airlines; routes; prices; market share</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Hanlon et al. - Taxes and Competition Evidence from the airline industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>U.S. federal district court filings (PACER)</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr"/>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Comprehensive civil case filings against public-company defendants (2006-2021), spanning many allegation types, used to measure litigation incidence and outcomes.</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>federal courts; lawsuits; PACER</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting Research - 2026 - Billings et al. - Incidence, Risk, and Disclosure of Corporate Litigation Insights from Federal Court Filings</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>UBS/Gallup and Livingston Survey</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr"/>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Survey measures of individual-investor and professional-forecaster return/earnings expectations used for comparison.</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>investor surveys; forecaster expectations</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Unified Patents</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Post-grant review data</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr"/>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>USPTO post-grant reviews used to validate the ModernBERT Alice score.</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>post-grant review; validation</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language models</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>USPTO</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Patent application office actions</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr"/>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>U.S. patent applications and examiner rejections used to identify Alice-based rejections and build training labels.</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Bulk</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>patents; rejections</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language models</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>USPTO</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Patent assignment (reassignment) records</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr"/>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Records of patent ownership transfers used to identify the timing and characteristics of firms' patent sales.</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>patents; assignments; sales</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Kim and Valentine - Earnings targets, strategic patent sales, and patent trolls</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>USPTO patent and inventor data</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr"/>
+      <c r="C106" s="2" t="inlineStr"/>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Patents, inventors, and assignment records used to track inventors' retention and reassignment of rights around the ruling.</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Bulk</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>patents; inventors; assignments</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting Research - 2026 - Armstrong et al. - The Assignment of Intellectual Property Rights and Innovation</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>USPTO patent data</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr"/>
+      <c r="C107" s="2" t="inlineStr"/>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Patent grants, citations, and text used to construct firms' absorption-intensity measure.</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>patents; citations; absorption</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Woeppel and Yavuz - Measuring firms' capability to absorb external knowledge</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Value Line Investment Survey</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr"/>
+      <c r="C108" s="2" t="inlineStr"/>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Analyst forecasts hand-collected from microfilm records (1956-2024) used to construct a long-run series of sophisticated investors' subjective expected returns.</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>subjective expectations; analyst forecasts; microfilm</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle tariff exposure data</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr"/>
+      <c r="C109" s="2" t="inlineStr"/>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Data on which vehicles/components were affected by tariffs, used to construct exposure to the trade-policy shock.</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>tariffs; autos; exposure</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>American Economic Review - 2026 - Hankins et al. - Consumer Credit and the Incidence of Tariffs Evidence from the Auto Industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Venture Expert (Refinitiv)</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr"/>
+      <c r="C110" s="2" t="inlineStr"/>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>VC financing rounds and startup descriptions used to measure VC-backed entry.</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>venture capital; entry</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language models</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Website cookie / web-tracking data</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr"/>
+      <c r="C111" s="2" t="inlineStr"/>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Data on cookies and trackers deployed on U.S. firms' websites, used to proxy the intensity of consumer-data collection.</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>cookies; web tracking; consumer data</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Liu - Website cookies and voluntary disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>WIND</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr"/>
+      <c r="C112" s="2" t="inlineStr"/>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Adjusted opening prices and free-floating shares for Chinese listed stocks. Chinese market and firm data used alongside CSMAR.</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>China; prices; shares; firm data</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - He et al. - Homemade Foreign Trading; Journal of Financial Economics - 2026 - Goldstein et al. - Market feedback Evidence from the horse's mouth</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>World Bank</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Firm-level Adoption of Technology (FAT) survey</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr"/>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Novel establishment survey measuring the most advanced and most widely used technologies across business functions for 21,000+ establishments in 15 countries.</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>technology adoption; establishments; cross-country survey</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly Journal of Economics - 2026 - Cirera et al. - Technology Sophistication Across Establishments</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Yunan Ji</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Medicare DME auction bids</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr"/>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Bids submitted in Medicare's DME competitive-bidding auctions, shared by the author, used in the bidding analysis.</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
           <t>auction bids; competitive bidding</t>
         </is>
       </c>
-      <c r="H45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="H114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
         <is>
           <t>Working Paper - 2026 - Diwan et al. - Competition and Fraud in Health Care</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I45"/>
+  <autoFilter ref="A1:I114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3138,7 +8315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3178,194 +8355,788 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Credit Crunches and the Great Stagflation</t>
+          <t>Consumer Credit and the Incidence of Tariffs: Evidence from the Auto Industry</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Drechsler, Savov, Schnabl</t>
+          <t>Hankins, Momeni, Sovich</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Regulation Q-induced credit crunches</t>
+          <t>Auto-industry tariffs</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Quasi-exogenous credit contraction</t>
+          <t>Trade policy shock</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Episodes where Fed tightening pushed market rates above Regulation Q deposit-rate ceilings, triggering deposit outflows (disintermediation) that forced banks to cut lending, driven by the interaction of the ceilings with monetary policy rather than by loan demand.</t>
+          <t>The imposition of tariffs affecting the auto industry, which raised vehicle costs, used as a shock to identify the incidence of tariffs on consumer credit and auto purchases.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Capital in the Capitol: Congressional Trades Resemble Uninformed Retail Trading</t>
+          <t>The Impact of Bank Consolidation on Credit Supply and Performance</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Chen, Sacerdote</t>
+          <t>Mayordomo, Pavanini, Tarantino</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>STOCK Act (2012)</t>
+          <t>Bank mergers (consolidation events)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Legislative / disclosure reform</t>
+          <t>Quasi-experiment</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>The Stop Trading on Congressional Knowledge Act, which required members of Congress and their families to publicly disclose securities transactions, creating the disclosure regime whose trades the paper analyzes.</t>
+          <t>Bank merger events used as quasi-experimental variation in local bank consolidation to identify effects on credit supply, pricing, and performance.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Bank Fees and Household Financial Well-Being</t>
+          <t>Industry (Re)Classifications and Corporate Governance</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Pagel, Sridhar, Williams</t>
+          <t>Ormazabal, Shi</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Large banks' NSF-fee eliminations and overdraft-policy changes (2017-2022)</t>
+          <t>GICS industry reclassifications</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Staggered policy changes</t>
+          <t>Classification change</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>A wave of bank-initiated changes at major U.S. banks that eliminated non-sufficient-funds fees and relaxed overdraft terms, staggered across banks and treated as quasi-exogenous to individual households.</t>
+          <t>Reassignments of firms' Global Industry Classification Standard codes, occurring for reasons outside firms' compensation decisions, used as exogenous variation in industry membership.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Competition and Fraud in Health Care</t>
+          <t>The Value of Ratings: Evidence from Their Introduction in Securities Markets</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Diwan, Eliason, League, Leder-Luis, McDevitt, Roberts</t>
+          <t>Bernstein</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Medicare competitive bidding for durable medical equipment</t>
+          <t>1909 introduction of Moody's bond ratings</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Policy reform</t>
+          <t>Historical natural experiment</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Medicare's staged replacement of administratively set DME reimbursement prices with competitive auctions, sharply lowering prices in affected product-areas and regions and acting as a shock to market competition.</t>
+          <t>John Moody's 1909 publication of the first-ever letter ratings for railroad bonds, which had no regulatory implications, used as a natural experiment isolating the information value of ratings.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Monopsony Power and the Transmission of Monetary Policy</t>
+          <t>The Assignment of Intellectual Property Rights and Innovation</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Bardóczy, Bornstein, Salgado</t>
+          <t>Armstrong, Glaeser, Park</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>High-frequency identified monetary policy shocks</t>
+          <t>U.S. appellate court ruling on IP-rights assignment</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Monetary policy shock</t>
+          <t>Court decision</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>The surprise component of monetary policy extracted from high-frequency movements in interest-rate futures around FOMC announcements, treated as exogenous shifts in the policy stance.</t>
+          <t>An appellate court ruling that shifted the default assignment of patent rights from employee inventors to their employers, used as a natural experiment on employer property rights.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+          <t>Company Websites: A New Measure of Disclosure</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Ahern</t>
+          <t>Boulland, Bourveau, Breuer</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Shift-share instrument for local industrial concentration</t>
+          <t>French nonfinancial disclosure mandate</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Instrument / quasi-exogenous variation</t>
+          <t>Disclosure regulation</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>National industry-employment trends interacted with each city's initial industry mix and regional house prices, producing changes in local concentration that are plausibly unrelated to the city's own fiscal shocks.</t>
+          <t>A French mandate requiring firms to provide nonfinancial disclosure, used as a setting to validate the website-based measure through firms' compliance.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>Internal information quality and performance metric selection</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Guay, Kim, Timmermans</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Two financial accounting standard changes</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Accounting-standard changes</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Plausibly exogenous shifts in two financial accounting standards that changed firms' internal information quality, used to identify the effect of information quality on executive performance-metric design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Taxes and Competition: Evidence from the airline industry</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Hanlon, Shroff, Yoon</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Tax Reform Act of 1986</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Tax reform</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>The 1986 Tax Reform Act, which cut the top corporate tax rate by about 12 percentage points, benefiting profitable firms much more than loss-making ones and used to study competition between differentially taxed airlines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SEC scrutiny and corporate risk-taking</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Weber, Xu, Zhang</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2007 SEC elevation of six district offices to regional status</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory reorganization</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>A 2007 SEC reorganization that raised six district offices to regional level, expanding their authority and enforcement resources, used as a difference-in-differences shock to local financial-reporting scrutiny.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Supply chain shocks and firm productivity: The role of reporting quality</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Berger, Tomy</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1999 Taiwan (Chi-Chi) earthquake</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Natural disaster</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>The 1999 Taiwan earthquake, which disrupted supply chains for certain U.S. high-technology manufacturers, used as an exogenous adverse shock whose productivity effects vary with firms' pre-shock reporting quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory disclosure of investors' fossil fuel holdings</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Miller, Stockbridge, Williams</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2016 California fossil-fuel disclosure mandate</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Disclosure regulation</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>A 2016 California requirement that certain U.S. insurers publicly disclose their fossil-fuel investments, applying to a subset of insurers and used as a quasi-exogenous disclosure shock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>How do consumers use ESG disclosure? Evidence from a randomized field experiment with everyday product purchases</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Leonelli, Muhn, Rauter, Sran</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Randomized field experiment on ESG information</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Randomized field experiment</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Randomized information treatments delivered to 24,000+ U.S. households that exogenously revealed real firm-disclosed ESG activities, enabling causal estimates of how ESG information affects purchases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Reaching for influence: Do banks use loans to establish political connections?</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Kaviani, Maleki, Savor</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Close congressional elections</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Regression discontinuity</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Narrowly decided U.S. congressional elections, where whether a firm's connected candidate barely wins or loses is close to random, used as quasi-exogenous variation in firms' political connections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Angels, entrepreneurship, and employment dynamics: Evidence from investor accreditation rules</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Lindsey, Stein</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Dodd-Frank removal of housing wealth from accredited-investor rules</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory reform</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>A Dodd-Frank change that excluded home equity from the wealth test defining accredited investors, pushing some households below the threshold; because house values differ across states, it reduced the angel-investor pool by varying amounts geographically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Measuring firms' capability to absorb external knowledge</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Woeppel, Yavuz</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>American Inventors Protection Act (AIPA)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Legislative reform</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>A U.S. reform that required publication of most patent applications 18 months after filing, exogenously increasing the availability of patent information and raising the payoff to absorbing external knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Dirty air and green investments: The impact of pollution information on portfolio allocations</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Fisman, Ghosh, Sen</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Rollout of air-quality monitoring stations across India</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Staggered information rollout</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The staggered appearance of local air-quality monitoring stations, which made pollution observable in a location at different times, used as quasi-exogenous variation in access to local pollution information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Constrained by law: The impact of fiduciary duties on portfolios and prices in US equity markets</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Cassella, Rizzo, Spalt, Zimmerer</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Uniform Prudent Investor Act (UPIA) adoption</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Staggered state-law reform</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>States' staggered 1985-2006 replacement of asset-by-asset 'prudent-man' rules with a portfolio-level prudent-investor standard, which applied only to trusts and relaxed a binding constraint on their holdings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Intellectual property protection lost and competition: An examination using large language models</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Acikalin, Caskurlu, Hoberg, Phillips</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Alice v. CLS Bank Supreme Court decision (2014)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Supreme Court decision</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>A 2014 ruling that invalidated many business-method and software patents, broadly and unexpectedly weakening IP protection across affected technology areas, used as a quasi-exogenous shock to firms' patent portfolios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Taxes Depress Corporate Borrowing: Evidence from Private Firms</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Ivanov, Pettit, Whited</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>State corporate income tax rate changes</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Staggered policy variation</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Changes in U.S. state corporate income tax rates and tax-base rules across states and over time, used as quasi-exogenous variation in the tax incentive to use debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Patents, News, and Business Cycles</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Miranda-Agrippino, Hacıoğlu-Hoke, Bluwstein</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Patent-based instrument for technology news shocks</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Instrument / news shock</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>An instrumental variable built from information in patent applications that isolates anticipated future productivity improvements (technology news) while having no contemporaneous effect on aggregate productivity, relaxing the identifying assumptions used in prior work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>What's My Employee Worth? The Effects of Salary Benchmarking</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Cullen, Li, Perez-Truglia</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Rollout of a salary-benchmarking tool</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Staggered access / quasi-experiment</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Firms gaining access to a compensation tool that reveals market salary benchmarks by job title, used in a difference-in-differences design as a quasi-exogenous shock to the wage information available to employers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Credit Crunches and the Great Stagflation</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Drechsler, Savov, Schnabl</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Regulation Q-induced credit crunches</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Quasi-exogenous credit contraction</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Episodes where Fed tightening pushed market rates above Regulation Q deposit-rate ceilings, triggering deposit outflows (disintermediation) that forced banks to cut lending, driven by the interaction of the ceilings with monetary policy rather than by loan demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Capital in the Capitol: Congressional Trades Resemble Uninformed Retail Trading</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Chen, Sacerdote</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>STOCK Act (2012)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Legislative / disclosure reform</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>The Stop Trading on Congressional Knowledge Act, which required members of Congress and their families to publicly disclose securities transactions, creating the disclosure regime whose trades the paper analyzes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Bank Fees and Household Financial Well-Being</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Pagel, Sridhar, Williams</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Large banks' NSF-fee eliminations and overdraft-policy changes (2017-2022)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Staggered policy changes</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>A wave of bank-initiated changes at major U.S. banks that eliminated non-sufficient-funds fees and relaxed overdraft terms, staggered across banks and treated as quasi-exogenous to individual households.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Competition and Fraud in Health Care</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Diwan, Eliason, League, Leder-Luis, McDevitt, Roberts</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Medicare competitive bidding for durable medical equipment</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Policy reform</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Medicare's staged replacement of administratively set DME reimbursement prices with competitive auctions, sharply lowering prices in affected product-areas and regions and acting as a shock to market competition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Monopsony Power and the Transmission of Monetary Policy</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Bardóczy, Bornstein, Salgado</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>High-frequency identified monetary policy shocks</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Monetary policy shock</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>The surprise component of monetary policy extracted from high-frequency movements in interest-rate futures around FOMC announcements, treated as exogenous shifts in the policy stance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Ahern</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Shift-share instrument for local industrial concentration</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Instrument / quasi-exogenous variation</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>National industry-employment trends interacted with each city's initial industry mix and regional house prices, producing changes in local concentration that are plausibly unrelated to the city's own fiscal shocks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>Homemade Foreign Trading</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>He, Wang, Zhu</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>2018 Northbound Investor Identification reform</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Regulatory reform (surveillance)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>A change to China's Stock Connect requiring a unique investor ID on each northbound order, giving regulators see-through visibility of who is trading and stripping mainland insiders of the ability to disguise domestic trades as foreign investment.</t>
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Discretion in Medical Evaluations</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Cabral, Dillender</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Quasi-random assignment of independent medical examiners</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Examiner-leniency (random assignment)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>The quasi-random assignment of injured workers to more- or less-generous independent medical examiners, used as an examiner-leniency design to identify the effect of medical evaluations on disability outcomes.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/knowledge_chest.xlsx
+++ b/docs/knowledge_chest.xlsx
@@ -12,9 +12,9 @@
     <sheet name="Exogenous Shocks" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Papers'!$A$1:$L$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dataset Universe'!$A$1:$I$114</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Exogenous Shocks'!$A$1:$E$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Papers'!$A$1:$L$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dataset Universe'!$A$1:$I$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Exogenous Shocks'!$A$1:$E$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4204,57 +4204,281 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2025 - Cabral and Dillender - Doctor Discretion in Medical Evaluations</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="n"/>
+          <t>American Economic Review - 2025 - Lerche - Direct and Indirect Effects of Investment Tax Incentives</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>American Economic Review</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Cabral, Dillender</t>
+          <t>Lerche</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Doctor Discretion in Medical Evaluations</t>
+          <t>Direct and Indirect Effects of Investment Tax Incentives</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>This paper analyzes how the discretion of doctors conducting independent medical exams affects injured workers' outcomes. Exploiting the quasi-random assignment of claimants to more- or less-generous independent examiners, the authors trace downstream outcomes over three years—duration out of work, cash disability benefits, and subsequent medical care. Reduced-form estimates show that claimants assigned a more generous examiner experience longer durations out of work and receive more benefits and care. The results reveal that examiner discretion has large, persistent effects on disability outcomes. The paper documents the consequences of doctor discretion in a high-stakes evaluation setting.</t>
+          <t>The paper estimates both the direct effects and the local spillover effects of investment tax credits on firms, using a German policy that changed the tax-credit rate differently by firm size. Lerche finds that lowering a firm's investment cost by 7.6 percent raises its capital stock by 17.7 percent and employment by 12.0 percent. Positive local spillovers create roughly one additional manufacturing job for each directly created job; they are strongest between firms linked through input-output relationships and operate within about five kilometers. Firms reliant on local consumer demand also expand employment, while within-industry spillovers are slightly negative. The paper shows that general-equilibrium spillovers substantially amplify the direct effects of investment tax incentives.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>The paper studies independent medical exams, where a doctor's assessment shapes an injured worker's eligibility for disability benefits, and asks how much the specific examiner matters. It exploits the fact that claimants are effectively randomly assigned to examiners who differ in generosity, creating an examiner-leniency design. Because assignment is quasi-random, differences in outcomes across examiners of different generosity can be attributed to the examiner rather than the claimant. The authors follow claimants for three years, measuring duration out of work, cash benefits, and medical care. They find that being assigned a more generous examiner leads to longer time out of work and more benefits and care, though these also depend on later actions by claimants, insurers, and treating doctors. The paper concludes that doctor discretion in evaluations has substantial and lasting effects on disability outcomes.</t>
+          <t>The paper begins from the long-standing use of investment tax credits to lower the cost of capital and recent firm-level evidence that they raise investment, while stressing that general-equilibrium spillovers determine how firm-level effects translate into aggregate outcomes—agglomeration and local-demand forces may amplify them, while fixed labor supply and product-market competition may offset them through reallocation. To estimate both direct and indirect effects, Lerche exploits an investment tax credit introduced after German reunification whose rate fell more for small firms, creating a differential change in the user cost of capital by firm size. Using administrative matched employer-employee data and firm addresses, he first estimates direct (partial-equilibrium) effects with a difference-in-differences design comparing firms just below and above the 250-employee cutoff (excluding those right at the cutoff). He finds large direct increases in capital and employment. He then combines this with a second difference-in-differences design based on the local (county) exposure to the policy—excluding a firm's own employment—to identify local spillovers. He finds positive local spillovers of about one extra manufacturing job per directly created job, strongest among input-output-linked industries and within five kilometers, plus positive local-demand effects and small negative within-industry spillovers. The paper concludes that investment tax incentives have sizable direct effects that are meaningfully amplified by local general-equilibrium spillovers.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>An examiner-assignment (leniency) design exploiting the quasi-random assignment of injured workers to independent medical examiners who differ in generosity, using administrative data. Reduced-form estimates relate assigned-examiner generosity to downstream outcomes—duration out of work, cash disability benefits, and subsequent medical care—over three years. The unit of analysis is the claimant; identification comes from quasi-random examiner assignment.</t>
+          <t>A quasi-experimental study exploiting a post-reunification German investment tax credit whose rate changed differentially by firm size (around a 250-employee cutoff), using administrative matched employer-employee data with firm addresses. Direct effects are estimated with a difference-in-differences design comparing firms below and above the size cutoff; local spillovers are identified by combining this with a second difference-in-differences design based on county-level policy exposure (excluding a firm's own employment). Identification comes from the size-differential rate change and local exposure.</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Health Economics, Disability Insurance, Public Economics</t>
+          <t>Public Economics, Labor Economics, Regional &amp; Urban Economics</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Administrative workers' compensation / disability claims</t>
+          <t>Institute for Employment Research (IAB, Germany) — administrative matched employer-employee data</t>
         </is>
       </c>
       <c r="K71" s="2" t="n"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/American Economic Review - 2025 - Lerche - Direct and Indirect Effects of Investment Tax Incentives.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2025 - Cabral and Dillender - Doctor Discretion in Medical Evaluations</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Cabral, Dillender</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Doctor Discretion in Medical Evaluations</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>This paper analyzes how the discretion of doctors conducting independent medical exams affects injured workers' outcomes. Exploiting the quasi-random assignment of claimants to more- or less-generous independent examiners, the authors trace downstream outcomes over three years—duration out of work, cash disability benefits, and subsequent medical care. Reduced-form estimates show that claimants assigned a more generous examiner experience longer durations out of work and receive more benefits and care. The results reveal that examiner discretion has large, persistent effects on disability outcomes. The paper documents the consequences of doctor discretion in a high-stakes evaluation setting.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>The paper studies independent medical exams, where a doctor's assessment shapes an injured worker's eligibility for disability benefits, and asks how much the specific examiner matters. It exploits the fact that claimants are effectively randomly assigned to examiners who differ in generosity, creating an examiner-leniency design. Because assignment is quasi-random, differences in outcomes across examiners of different generosity can be attributed to the examiner rather than the claimant. The authors follow claimants for three years, measuring duration out of work, cash benefits, and medical care. They find that being assigned a more generous examiner leads to longer time out of work and more benefits and care, though these also depend on later actions by claimants, insurers, and treating doctors. The paper concludes that doctor discretion in evaluations has substantial and lasting effects on disability outcomes.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>An examiner-assignment (leniency) design exploiting the quasi-random assignment of injured workers to independent medical examiners who differ in generosity, using administrative data. Reduced-form estimates relate assigned-examiner generosity to downstream outcomes—duration out of work, cash disability benefits, and subsequent medical care—over three years. The unit of analysis is the claimant; identification comes from quasi-random examiner assignment.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Health Economics, Disability Insurance, Public Economics</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Administrative workers' compensation / disability claims</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
           <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Working Paper - 2025 - Cabral and Dillender - Doctor Discretion in Medical Evaluations.pdf</t>
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Econometrica - 2023 - Eeckhout and Veldkamp - Data and Markups A Macro-Finance Perspective</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Econometrica</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Eeckhout, Veldkamp</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Data and Markups: A Macro-Finance Perspective</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>The paper asks how to measure the extent to which data-intensive firms use market power, and argues that markups—the usual proxy—can be misleading. Building a model in which firms price risk in their capital-allocation and production decisions, the authors show data has competing effects on markups, so markups are an unreliable measure of data-derived market power. Instead, they show that comparing markups measured at different levels of aggregation (product, firm, industry) reveals the role of data and distinguishes data from other intangibles. This reconciles seemingly contradictory empirical markup findings across aggregation levels. The paper offers a new way to measure data and its effects on competition.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>The paper enters the debate over rising market power and whether the dominance of large, data-intensive firms reflects economies of scale in information that reduce competition. It asks how to measure such data-derived market power and questions the standard reliance on markups. The authors build a model drawing on macro theory (data as information that reduces uncertainty), corporate finance (firms price risk), and industrial organization (firms exploit market power), in which economies of scale in data lead a data-rich firm to lower its marginal cost and capture more market share. Working through the model, they show data exerts competing effects on markups, and that the net effect depends on the level of aggregation at which markups are measured, so a single markup number is an unreliable gauge of data-driven power. Crucially, they show the difference between markups measured at the firm versus product level acts as a sufficient statistic for the amount of relevant data. They demonstrate that this framework reconciles existing empirical findings that product-, firm-, and industry-level markups behave differently over the cycle and trend. The paper concludes that examining how markups differ across aggregation levels is the right way to detect and measure the effects of data on markets.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>A theoretical macro-finance model in which firms price risk in capital-allocation and production decisions and economies of scale in data lower marginal cost and raise market share. The analysis derives how data affects markups differently across levels of aggregation (product, firm, industry) and shows the firm-versus-product markup gap is a sufficient statistic for data, reconciling existing empirical markup evidence. It is analytical, using existing empirical facts for validation rather than estimating a new dataset.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Macroeconomics, Industrial Organization, Expectations &amp; Information</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Theoretical paper; no dataset. It reconciles existing empirical markup evidence (product/firm/industry level) rather than analyzing an original dataset. The supplied PDF is the February 2023 manuscript version of the article published in Econometrica (2023).</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Econometrica - 2023 - Eeckhout and Veldkamp - Data and Markups A Macro-Finance Perspective.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>American Law and Economics Review - 2023 - Ohlrogge - Down the Tubes Financial Distress, Bankruptcy, and Industrial Water Pollution</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>American Law and Economics Review</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Ohlrogge</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Down the Tubes: Financial Distress, Bankruptcy, and Industrial Water Pollution</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>The paper examines how firms' efforts to avoid harming third parties change as they approach, enter, and exit bankruptcy, focusing on industrial water pollution. Studying about 350 US firms regulated under the Clean Water Act that declared bankruptcy, Ohlrogge finds that as firms approach bankruptcy their rate of releasing pollutants beyond permitted limits rises by 50 percent. Once they file, compliance improves dramatically, returning to a baseline from well before filing. He argues the pattern is best explained by a mix of moral-hazard problems and financing frictions affecting thinly capitalized firms. The findings support policy interventions such as changes to bankruptcy claim priority and suggest an underappreciated public benefit of encouraging firms to file early.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>The paper starts from the recognized idea that financial distress distorts firm behavior—underinvestment from debt overhang and shareholder-creditor conflicts—and asks how distress and bankruptcy affect a firm's efforts to avoid harming third parties, here through water pollution. It assembles a panel of roughly 350 US firms regulated under the Clean Water Act (via NPDES permits) that all eventually declare bankruptcy, and studies their permitted-limit exceedances over time. Using a difference-in-differences-style comparison to similar facilities owned by non-bankrupt firms, Ohlrogge finds that as firms approach bankruptcy their rate of exceeding pollution limits rises by about 50 percent, and that after filing, compliance improves sharply back to a pre-distress baseline. He explores mechanisms and argues the pattern reflects a nexus of moral hazard (thinly capitalized firms have weak incentives to invest in compliance when liabilities can be discharged) and financing frictions that ease once bankruptcy resolves distress; he notes the bankruptcy code's higher administrative priority for post-filing environmental penalties as relevant. He draws policy implications, including changing claim priority to mitigate moral hazard and encouraging early filing. The paper concludes that bankruptcy can reduce public harms from distressed firms, implying benefits to policies that promote timely resolution of distress.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>An empirical panel study of about 350 US Clean Water Act (NPDES)-regulated firms that declare bankruptcy, using discharge-monitoring data on permitted-limit exceedances over time. A difference-in-differences-style design compares bankrupt firms' compliance around approach, filing, and exit to similar facilities owned by non-bankrupt firms. Identification comes from the timing of financial distress and bankruptcy filing relative to comparison facilities.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Law &amp; Economics, Corporate Finance, Environmental Economics</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>US Environmental Protection Agency — NPDES discharge monitoring reports (Clean Water Act); US bankruptcy filings — corporate bankruptcy records</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="n"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/American Law and Economics Review - 2023 - Ohlrogge - Down the Tubes Financial Distress, Bankruptcy, and Industrial Water Pollution.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Annual Review of Economics - 2022 - Baker and Kueng - Household Financial Transaction Data</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Annual Review of Economics</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Baker, Kueng</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Household Financial Transaction Data</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>This review surveys the fast-growing use of detailed household financial transaction micro-data in economics and finance. Such data—drawn from banks, FinTech aggregator apps, payment intermediaries, and card companies—provide comprehensive, high-frequency panels of financial flows and balances for many thousands to millions of individuals. The authors review how these data have advanced research on consumption, household balance sheets, and responses to income shocks and policy, and they weigh their benefits and limitations against traditional survey, scanner, and tax-based measures. They also discuss the data's future potential for firm-focused research, real-time policy analysis, and macroeconomic statistics. The paper serves as a guide to the sources, uses, and tradeoffs of household transaction data.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>The review begins by noting that measuring household consumption and finances well is central to many questions, yet traditional sources—government surveys, scanner data, and tax-based imputation—suffer from high cost, small samples, short panels, slow updating, partial coverage, or measurement error. It then introduces a newer class of data: comprehensive panels of financial transactions from credit, debit, and checking accounts, sourced from banks, financial aggregators (FinTech apps), and card companies, often at high frequency and spanning many account types. The authors organize how researchers have used these data to study consumption behavior, household balance sheets, and responses to income fluctuations and policy changes, improving understanding of heterogeneity in income, balance sheets, beliefs, and preferences. They systematically compare the benefits (coverage, frequency, sample size, timeliness) and limitations (representativeness, incomplete account linkage, categorization, access) of transaction data relative to traditional measures. Finally, they look ahead to applications in firm-focused research, real-time policy analysis, and macro statistics. The review concludes by positioning household financial transaction data as a flexible, powerful, but imperfect complement to existing measurement tools.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>A survey/review article that synthesizes the literature using household financial transaction micro-data (from banks, FinTech aggregators, payment intermediaries, and card companies), rather than conducting original empirical estimation. It categorizes applications across household finance and macroeconomics and assesses the benefits and limitations of transaction data relative to survey, scanner, and tax-based measures. There is no research-design shock or dataset of the authors' own.</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Household Finance, Data &amp; Measurement, Macroeconomics</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Review/survey article; it surveys the class of household financial transaction data (from banks, FinTech apps, and card companies) rather than analyzing a specific dataset of its own.</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Knowledge-Chest/Knowledge-Chest/Annual Review of Economics - 2022 - Baker and Kueng - Household Financial Transaction Data.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L71"/>
+  <autoFilter ref="A1:L75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4265,7 +4489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6083,18 +6307,18 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Institute for Private Capital</t>
+          <t>Institute for Employment Research (IAB, Germany)</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Failed-fund data</t>
+          <t>administrative matched employer-employee data</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Funds that failed to raise capital, used to build non-selected opportunity sets.</t>
+          <t>German administrative surveys and matched employer-employee data with firm addresses, used to measure firm capital and employment responses and local spillovers around the tax-credit change.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6105,7 +6329,7 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>failed funds</t>
+          <t>Germany; matched employer-employee; investment; tax credit</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
@@ -6113,36 +6337,36 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets</t>
+          <t>American Economic Review - 2025 - Lerche - Direct and Indirect Effects of Investment Tax Incentives</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Internet Archive</t>
+          <t>Institute for Private Capital</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Historical website (Wayback) data</t>
+          <t>Failed-fund data</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Archived snapshots of firms' company websites used to construct the disclosure measure.</t>
+          <t>Funds that failed to raise capital, used to build non-selected opportunity sets.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>websites; disclosure; web archive</t>
+          <t>failed funds</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
@@ -6150,25 +6374,25 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Journal of Accounting Research - 2026 - Boulland et al. - Company Websites A New Measure of Disclosure</t>
+          <t>Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>Internet Archive</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Taxpayer Assistance Center locations</t>
+          <t>Historical website (Wayback) data</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Locations and coverage of IRS Taxpayer Assistance Centers used to measure local access to tax help.</t>
+          <t>Archived snapshots of firms' company websites used to construct the disclosure measure.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6179,7 +6403,7 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>IRS; tax assistance; access</t>
+          <t>websites; disclosure; web archive</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
@@ -6187,7 +6411,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Journal of Accounting and Economics - 2026 - Armstrong and Glaeser - Does taxpayer assistance encourage entrepreneurship</t>
+          <t>Journal of Accounting Research - 2026 - Boulland et al. - Company Websites A New Measure of Disclosure</t>
         </is>
       </c>
     </row>
@@ -6199,13 +6423,13 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Statistics of Income (Schedule C)</t>
+          <t>Taxpayer Assistance Center locations</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Local self-employment/Schedule C business income and entry data used to measure entrepreneurship.</t>
+          <t>Locations and coverage of IRS Taxpayer Assistance Centers used to measure local access to tax help.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6216,7 +6440,7 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Schedule C; entrepreneurship; income</t>
+          <t>IRS; tax assistance; access</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
@@ -6231,29 +6455,29 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ISS Incentive Lab</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Executive incentive-plan data</t>
+          <t>Statistics of Income (Schedule C)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Detailed executive compensation and performance-metric data used to measure the number and dissimilarity of metrics in incentive contracts.</t>
+          <t>Local self-employment/Schedule C business income and entry data used to measure entrepreneurship.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>executive pay; performance metrics</t>
+          <t>Schedule C; entrepreneurship; income</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
@@ -6261,62 +6485,62 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Journal of Accounting and Economics - 2026 - Guay et al. - Internal information quality and performance metric selection</t>
+          <t>Journal of Accounting and Economics - 2026 - Armstrong and Glaeser - Does taxpayer assistance encourage entrepreneurship</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>KPSS patent value database</t>
+          <t>ISS Incentive Lab</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Kogan, Papanikolaou, Seru &amp; Stoffman (2017)</t>
+          <t>Executive incentive-plan data</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Dollar valuations of individual patents, used to weight firms' Alice-exposed patents. Market-based patent values used in validating innovation outcomes.</t>
+          <t>Detailed executive compensation and performance-metric data used to measure the number and dissimilarity of metrics in incentive contracts.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>patent value; innovation</t>
+          <t>executive pay; performance metrics</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language models; Journal of Financial Economics - 2026 - Woeppel and Yavuz - Measuring firms' capability to absorb external knowledge</t>
+          <t>Journal of Accounting and Economics - 2026 - Guay et al. - Internal information quality and performance metric selection</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>KPSS patent value database</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Chronicling America</t>
+          <t>Kogan, Papanikolaou, Seru &amp; Stoffman (2017)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Large-scale archive of digitized historical U.S. newspapers, the main source for detecting and dating bank runs.</t>
+          <t>Dollar valuations of individual patents, used to weight firms' Alice-exposed patents. Market-based patent values used in validating innovation outcomes.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -6327,44 +6551,44 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>historical newspapers; text source</t>
+          <t>patent value; innovation</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+          <t>Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language models; Journal of Financial Economics - 2026 - Woeppel and Yavuz - Measuring firms' capability to absorb external knowledge</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LPC (Refinitiv)</t>
+          <t>Library of Congress</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>LSTA/LPC Mark-to-Market Pricing Data</t>
+          <t>Chronicling America</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Secondary-market loan trading/pricing data used to measure loan liquidity and pricing.</t>
+          <t>Large-scale archive of digitized historical U.S. newspapers, the main source for detecting and dating bank runs.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>secondary loan prices; liquidity</t>
+          <t>historical newspapers; text source</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
@@ -6372,25 +6596,25 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>LPC (Refinitiv)</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Default and Recovery Database</t>
+          <t>LSTA/LPC Mark-to-Market Pricing Data</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Nominal recovery rates aggregated by industry, used in the risk-adjustment of spreads.</t>
+          <t>Secondary-market loan trading/pricing data used to measure loan liquidity and pricing.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -6401,7 +6625,7 @@
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>defaults; recoveries</t>
+          <t>secondary loan prices; liquidity</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
@@ -6416,29 +6640,29 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Moody's (1909)</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>First-ever railroad bond ratings</t>
+          <t>Default and Recovery Database</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Hand-collected letter ratings from John Moody's 1909 publication covering most listed railroad bonds.</t>
+          <t>Nominal recovery rates aggregated by industry, used in the risk-adjustment of spreads.</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>ratings; railroad bonds; 1909</t>
+          <t>defaults; recoveries</t>
         </is>
       </c>
       <c r="H61" s="2" t="n">
@@ -6446,25 +6670,25 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Bernstein - The Value of Ratings Evidence from Their Introduction in Securities Markets</t>
+          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MSRB</t>
+          <t>Moody's (1909)</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Municipal Securities Rulemaking Board trade data</t>
+          <t>First-ever railroad bond ratings</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Secondary-market municipal bond trades used to construct city-level bond spreads.</t>
+          <t>Hand-collected letter ratings from John Moody's 1909 publication covering most listed railroad bonds.</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -6475,7 +6699,7 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>municipal bonds; spreads; secondary market</t>
+          <t>ratings; railroad bonds; 1909</t>
         </is>
       </c>
       <c r="H62" s="2" t="n">
@@ -6483,25 +6707,25 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+          <t>Working Paper - 2026 - Bernstein - The Value of Ratings Evidence from Their Introduction in Securities Markets</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>NBER-CES</t>
+          <t>MSRB</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing Industry Database</t>
+          <t>Municipal Securities Rulemaking Board trade data</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Industry-level prices and quantities (derived from the U.S. Census) used to test cross-industry supply effects.</t>
+          <t>Secondary-market municipal bond trades used to construct city-level bond spreads.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -6512,7 +6736,7 @@
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>manufacturing; prices; quantities</t>
+          <t>municipal bonds; spreads; secondary market</t>
         </is>
       </c>
       <c r="H63" s="2" t="n">
@@ -6520,25 +6744,25 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
+          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>NBER–USPTO</t>
+          <t>NBER-CES</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Historical Patent Data Files (Marco et al. 2015)</t>
+          <t>Manufacturing Industry Database</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Comprehensive data on U.S. patent applications used to construct a forward-looking instrument for technology news shocks.</t>
+          <t>Industry-level prices and quantities (derived from the U.S. Census) used to test cross-industry supply effects.</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -6549,7 +6773,7 @@
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>patents; applications; news shocks; instrument</t>
+          <t>manufacturing; prices; quantities</t>
         </is>
       </c>
       <c r="H64" s="2" t="n">
@@ -6557,36 +6781,36 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Review of Economic Studies - 2026 - Miranda-Agrippino et al. - Patents, News, and Business Cycles</t>
+          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>NielsenIQ (Nielsen Consumer LLC)</t>
+          <t>NBER–USPTO</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Retail scanner data</t>
+          <t>Historical Patent Data Files (Marco et al. 2015)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Product-level retail prices and quantities for packaged-goods categories, used to measure pass-through in the food-products setting.</t>
+          <t>Comprehensive data on U.S. patent applications used to construct a forward-looking instrument for technology news shocks.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>retail scanner; prices; food</t>
+          <t>patents; applications; news shocks; instrument</t>
         </is>
       </c>
       <c r="H65" s="2" t="n">
@@ -6594,21 +6818,25 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Quarterly Journal of Economics - 2026 - Sangani - Complete Pass-Through in Levels</t>
+          <t>Review of Economic Studies - 2026 - Miranda-Agrippino et al. - Patents, News, and Business Cycles</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Nilson Report</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr"/>
+          <t>NielsenIQ (Nielsen Consumer LLC)</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Retail scanner data</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="inlineStr"/>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Industry statistics on interchange and network fees used to benchmark payment costs.</t>
+          <t>Product-level retail prices and quantities for packaged-goods categories, used to measure pass-through in the food-products setting.</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -6619,7 +6847,7 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>interchange; network fees; benchmarks</t>
+          <t>retail scanner; prices; food</t>
         </is>
       </c>
       <c r="H66" s="2" t="n">
@@ -6627,32 +6855,32 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Egan et al. - Who Pays for Payments</t>
+          <t>Quarterly Journal of Economics - 2026 - Sangani - Complete Pass-Through in Levels</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Norwegian Central Securities Depository (VPS)</t>
+          <t>Nilson Report</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr"/>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>All individual stock transactions on the Oslo Stock Exchange, 1997-2014.</t>
+          <t>Industry statistics on interchange and network fees used to benchmark payment costs.</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>individual trades; Norway</t>
+          <t>interchange; network fees; benchmarks</t>
         </is>
       </c>
       <c r="H67" s="2" t="n">
@@ -6660,21 +6888,21 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Journal of Financial Economics - 2026 - Hvide and Nielsen - Flying below the radar Insider trading by executives below the top</t>
+          <t>Working Paper - 2026 - Egan et al. - Who Pays for Payments</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Norwegian registers (LLC ownership; population)</t>
+          <t>Norwegian Central Securities Depository (VPS)</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr"/>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>LLC ownership and family links used to study indirect trades.</t>
+          <t>All individual stock transactions on the Oslo Stock Exchange, 1997-2014.</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -6685,7 +6913,7 @@
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>LLC; family links</t>
+          <t>individual trades; Norway</t>
         </is>
       </c>
       <c r="H68" s="2" t="n">
@@ -6700,29 +6928,25 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>OCC</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>National bank call reports (Annual Report to Congress)</t>
-        </is>
-      </c>
+          <t>Norwegian registers (LLC ownership; population)</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr"/>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Balance-sheet data for national banks used to measure bank fundamentals and outcomes.</t>
+          <t>LLC ownership and family links used to study indirect trades.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>call reports; bank balance sheets; fundamentals</t>
+          <t>LLC; family links</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
@@ -6730,32 +6954,36 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
+          <t>Journal of Financial Economics - 2026 - Hvide and Nielsen - Flying below the radar Insider trading by executives below the top</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Oslo Stock Exchange</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr"/>
+          <t>OCC</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>National bank call reports (Annual Report to Congress)</t>
+        </is>
+      </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Daily prices and market capitalization used to compute returns.</t>
+          <t>Balance-sheet data for national banks used to measure bank fundamentals and outcomes.</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>prices; market cap</t>
+          <t>call reports; bank balance sheets; fundamentals</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
@@ -6763,36 +6991,32 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Journal of Financial Economics - 2026 - Hvide and Nielsen - Flying below the radar Insider trading by executives below the top</t>
+          <t>Working Paper - 2026 - Correia et al. - Bank Runs with and without Bank Failure</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>PACER</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Public Access to Court Electronic Records</t>
-        </is>
-      </c>
+          <t>Oslo Stock Exchange</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr"/>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>U.S. bankruptcy court records used to identify DIP financing and Chapter 11 cases.</t>
+          <t>Daily prices and market capitalization used to compute returns.</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>bankruptcy; DIP; court records</t>
+          <t>prices; market cap</t>
         </is>
       </c>
       <c r="H71" s="2" t="n">
@@ -6800,32 +7024,36 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
+          <t>Journal of Financial Economics - 2026 - Hvide and Nielsen - Flying below the radar Insider trading by executives below the top</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>PitchBook</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr"/>
+          <t>PACER</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Public Access to Court Electronic Records</t>
+        </is>
+      </c>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Venture-capital-backed startups, their founders, financing rounds, and cap-table/board structures, used to build the sample and governance variables.</t>
+          <t>U.S. bankruptcy court records used to identify DIP financing and Chapter 11 cases.</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>venture capital; startups; cap tables</t>
+          <t>bankruptcy; DIP; court records</t>
         </is>
       </c>
       <c r="H72" s="2" t="n">
@@ -6833,21 +7061,21 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dyck et al. - Venture Fraud</t>
+          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Preqin</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>LP capital commitments and fund-level performance (IRR, TVPI), AuM, and flags for private-market funds 1995-2019. Industry-level private-credit assets used to gauge coverage and situate the sample within the broader market.</t>
+          <t>Venture-capital-backed startups, their founders, financing rounds, and cap-table/board structures, used to build the sample and governance variables.</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -6858,29 +7086,29 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>private credit; industry assets; private equity; commitments; IRR</t>
+          <t>venture capital; startups; cap tables</t>
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Matvos et al. - Private Credit, Balance Sheets and Financial Stability; Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets</t>
+          <t>Working Paper - 2026 - Dyck et al. - Venture Fraud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Proprietary private-credit data provider</t>
+          <t>Preqin</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>New proprietary fund- and asset-level data covering roughly 1,300 private-credit funds and their loans (capitalization, funding, maturities, performance), covering most of the industry.</t>
+          <t>LP capital commitments and fund-level performance (IRR, TVPI), AuM, and flags for private-market funds 1995-2019. Industry-level private-credit assets used to gauge coverage and situate the sample within the broader market.</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -6891,29 +7119,29 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>private credit; funds; balance sheets</t>
+          <t>private credit; industry assets; private equity; commitments; IRR</t>
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Matvos et al. - Private Credit, Balance Sheets and Financial Stability</t>
+          <t>Working Paper - 2026 - Matvos et al. - Private Credit, Balance Sheets and Financial Stability; Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Proprietary retail deposit data provider</t>
+          <t>Proprietary private-credit data provider</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr"/>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Transaction- and account-level data on retail deposit balances and activity, used to study the distribution and dynamics of household deposits.</t>
+          <t>New proprietary fund- and asset-level data covering roughly 1,300 private-credit funds and their loans (capitalization, funding, maturities, performance), covering most of the industry.</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -6924,7 +7152,7 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>transaction-level; retail deposits; accounts</t>
+          <t>private credit; funds; balance sheets</t>
         </is>
       </c>
       <c r="H75" s="2" t="n">
@@ -6932,21 +7160,21 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Argyle et al. - The Dynamics of Retail Deposit Balances</t>
+          <t>Working Paper - 2026 - Matvos et al. - Private Credit, Balance Sheets and Financial Stability</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Proprietary transaction-level data provider</t>
+          <t>Proprietary retail deposit data provider</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Household transaction-level data used to measure depositor inattention and the responsiveness of deposit balances to rate changes.</t>
+          <t>Transaction- and account-level data on retail deposit balances and activity, used to study the distribution and dynamics of household deposits.</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6957,7 +7185,7 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>transaction-level; deposits; inattention</t>
+          <t>transaction-level; retail deposits; accounts</t>
         </is>
       </c>
       <c r="H76" s="2" t="n">
@@ -6965,21 +7193,21 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Lu and Wu - Banking on Inattention</t>
+          <t>Working Paper - 2026 - Argyle et al. - The Dynamics of Retail Deposit Balances</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>RavenPack</t>
+          <t>Proprietary transaction-level data provider</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Macroeconomic news and announcement data used to identify concurrent macro information.</t>
+          <t>Household transaction-level data used to measure depositor inattention and the responsiveness of deposit balances to rate changes.</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -6990,7 +7218,7 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>macro news; announcements</t>
+          <t>transaction-level; deposits; inattention</t>
         </is>
       </c>
       <c r="H77" s="2" t="n">
@@ -6998,25 +7226,21 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Journal of Accounting Research - 2026 - Ferracuti and Lind - Macroeconomic Information Acquisition Around Earnings Clusters</t>
+          <t>Working Paper - 2026 - Lu and Wu - Banking on Inattention</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Refinitiv LPC</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>DealScan</t>
-        </is>
-      </c>
+          <t>RavenPack</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr"/>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Loan-level covenant terms (e.g., debt-to-EBITDA covenants) used to identify firms subject to earnings-based constraints. Facility-level syndicated loan terms used to build the sample of debtor-in-possession and highly speculative loans. Syndicated loan terms used to measure loan pricing and covenants for connected and non-connected firms.</t>
+          <t>Macroeconomic news and announcement data used to identify concurrent macro information.</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -7027,29 +7251,33 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>syndicated loans; DIP; facilities; loan covenants; debt-to-EBITDA; terms</t>
+          <t>macro news; announcements</t>
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers; Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics; Journal of Financial Economics - 2026 - Kaviani et al. - Reaching for influence Do banks use loans to establish political connections</t>
+          <t>Journal of Accounting Research - 2026 - Ferracuti and Lind - Macroeconomic Information Acquisition Around Earnings Clusters</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>RelSci</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr"/>
+          <t>Refinitiv LPC</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>DealScan</t>
+        </is>
+      </c>
       <c r="C79" s="2" t="inlineStr"/>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Personal/professional links between LP and GP employees.</t>
+          <t>Loan-level covenant terms (e.g., debt-to-EBITDA covenants) used to identify firms subject to earnings-based constraints. Facility-level syndicated loan terms used to build the sample of debtor-in-possession and highly speculative loans. Syndicated loan terms used to measure loan pricing and covenants for connected and non-connected firms.</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -7060,29 +7288,29 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>personal networks</t>
+          <t>syndicated loans; DIP; facilities; loan covenants; debt-to-EBITDA; terms</t>
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets</t>
+          <t>Working Paper - 2026 - Dou et al. - The Cost of Intermediary Market Power for Distressed Borrowers; Working Paper - 2026 - Ebsim et al. - Sophisticated Borrowing Constraints and Macroeconomic Dynamics; Journal of Financial Economics - 2026 - Kaviani et al. - Reaching for influence Do banks use loans to establish political connections</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Retail gasoline price microdata</t>
+          <t>RelSci</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr"/>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Station-level retail gasoline prices and wholesale input costs used to measure pass-through at gas stations.</t>
+          <t>Personal/professional links between LP and GP employees.</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7093,7 +7321,7 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>gasoline; station prices; pass-through</t>
+          <t>personal networks</t>
         </is>
       </c>
       <c r="H80" s="2" t="n">
@@ -7101,36 +7329,32 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Quarterly Journal of Economics - 2026 - Sangani - Complete Pass-Through in Levels</t>
+          <t>Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Robert Shiller</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Investor Confidence Survey</t>
-        </is>
-      </c>
+          <t>Retail gasoline price microdata</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr"/>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Investor-confidence survey data used as a comparison measure of investor beliefs.</t>
+          <t>Station-level retail gasoline prices and wholesale input costs used to measure pass-through at gas stations.</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>investor confidence; beliefs</t>
+          <t>gasoline; station prices; pass-through</t>
         </is>
       </c>
       <c r="H81" s="2" t="n">
@@ -7138,32 +7362,36 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+          <t>Quarterly Journal of Economics - 2026 - Sangani - Complete Pass-Through in Levels</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P Capital IQ</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr"/>
+          <t>Robert Shiller</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Investor Confidence Survey</t>
+        </is>
+      </c>
       <c r="C82" s="2" t="inlineStr"/>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Supplementary financial data used to improve customer-capital expense measures.</t>
+          <t>Investor-confidence survey data used as a comparison measure of investor beliefs.</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>financials; customer capital</t>
+          <t>investor confidence; beliefs</t>
         </is>
       </c>
       <c r="H82" s="2" t="n">
@@ -7171,40 +7399,32 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Eisfeldt et al. - Intangible Intensity</t>
+          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Form D filings</t>
-        </is>
-      </c>
+          <t>S&amp;P Capital IQ</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr"/>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Regulation D filings used to identify failed first-time fundraising.</t>
+          <t>Supplementary financial data used to improve customer-capital expense measures.</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>Bulk</t>
-        </is>
-      </c>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Form D; first-time funds</t>
+          <t>financials; customer capital</t>
         </is>
       </c>
       <c r="H83" s="2" t="n">
@@ -7212,7 +7432,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets</t>
+          <t>Working Paper - 2026 - Eisfeldt et al. - Intangible Intensity</t>
         </is>
       </c>
     </row>
@@ -7224,13 +7444,13 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Office jurisdictions / enforcement geography</t>
+          <t>Form D filings</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr"/>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Assignment of firms to SEC district/regional offices and the 2007 reorganization, used to define treated jurisdictions.</t>
+          <t>Regulation D filings used to identify failed first-time fundraising.</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -7238,10 +7458,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Bulk</t>
+        </is>
+      </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>SEC; jurisdictions; enforcement</t>
+          <t>Form D; first-time funds</t>
         </is>
       </c>
       <c r="H84" s="2" t="n">
@@ -7249,36 +7473,36 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Journal of Accounting and Economics - 2026 - Weber et al. - SEC scrutiny and corporate risk-taking</t>
+          <t>Journal of Financial Economics - 2026 - Goyal et al. - Picking partners Manager selection in private markets</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>SEC (WRDS SEC Analytics Suite)</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>10-K filings</t>
+          <t>Office jurisdictions / enforcement geography</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr"/>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Full-text corporate 10-K filings, accessed via the WRDS SEC Analytics Suite, used to build the text-based intangible-intensity measure.</t>
+          <t>Assignment of firms to SEC district/regional offices and the 2007 reorganization, used to define treated jurisdictions.</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>10-K; disclosure text; NLP</t>
+          <t>SEC; jurisdictions; enforcement</t>
         </is>
       </c>
       <c r="H85" s="2" t="n">
@@ -7286,32 +7510,36 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Eisfeldt et al. - Intangible Intensity</t>
+          <t>Journal of Accounting and Economics - 2026 - Weber et al. - SEC scrutiny and corporate risk-taking</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>SEC EDGAR log files</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr"/>
+          <t>SEC (WRDS SEC Analytics Suite)</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>10-K filings</t>
+        </is>
+      </c>
       <c r="C86" s="2" t="inlineStr"/>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Records of investors' access to firms' filings, used to proxy information acquisition around earnings clusters.</t>
+          <t>Full-text corporate 10-K filings, accessed via the WRDS SEC Analytics Suite, used to build the text-based intangible-intensity measure.</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>EDGAR logs; information acquisition</t>
+          <t>10-K; disclosure text; NLP</t>
         </is>
       </c>
       <c r="H86" s="2" t="n">
@@ -7319,21 +7547,21 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Journal of Accounting Research - 2026 - Ferracuti and Lind - Macroeconomic Information Acquisition Around Earnings Clusters</t>
+          <t>Working Paper - 2026 - Eisfeldt et al. - Intangible Intensity</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>SEC Form ADV (hedge-fund adviser filings)</t>
+          <t>SEC EDGAR log files</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr"/>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Investment-adviser regulatory disclosures of operational and investment risks, compared with other public information to identify inconsistencies.</t>
+          <t>Records of investors' access to firms' filings, used to proxy information acquisition around earnings clusters.</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -7344,7 +7572,7 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Form ADV; hedge funds; disclosure</t>
+          <t>EDGAR logs; information acquisition</t>
         </is>
       </c>
       <c r="H87" s="2" t="n">
@@ -7352,21 +7580,21 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Journal of Accounting Research - 2026 - Liu et al. - Strategic (Inconsistent) Disclosures and Sophisticated Investors Evidence from Hedge Funds</t>
+          <t>Journal of Accounting Research - 2026 - Ferracuti and Lind - Macroeconomic Information Acquisition Around Earnings Clusters</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Stanford NPE Litigation Database / PACER</t>
+          <t>SEC Form ADV (hedge-fund adviser filings)</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr"/>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>U.S. patent-infringement lawsuits (NPE vs operating company) used to measure litigation exposure.</t>
+          <t>Investment-adviser regulatory disclosures of operational and investment risks, compared with other public information to identify inconsistencies.</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -7377,7 +7605,7 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>patent litigation; NPE</t>
+          <t>Form ADV; hedge funds; disclosure</t>
         </is>
       </c>
       <c r="H88" s="2" t="n">
@@ -7385,21 +7613,21 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language models</t>
+          <t>Journal of Accounting Research - 2026 - Liu et al. - Strategic (Inconsistent) Disclosures and Sophisticated Investors Evidence from Hedge Funds</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>State corporate income tax data</t>
+          <t>Stanford NPE Litigation Database / PACER</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr"/>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>State-by-year corporate income tax rates and tax-base rules (e.g., depreciation and apportionment), hand-collected/extended, used as variation in the tax incentive to borrow.</t>
+          <t>U.S. patent-infringement lawsuits (NPE vs operating company) used to measure litigation exposure.</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -7410,7 +7638,7 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>state taxes; corporate income; leverage</t>
+          <t>patent litigation; NPE</t>
         </is>
       </c>
       <c r="H89" s="2" t="n">
@@ -7418,36 +7646,32 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Review of Economic Studies - 2026 - Ivanov et al. - Taxes Depress Corporate Borrowing Evidence from Private Firms</t>
+          <t>Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language models</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Statistics Norway</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Employer-employee register (ISCO-88)</t>
-        </is>
-      </c>
+          <t>State corporate income tax data</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Population employer-employee data identifying each individual's position and demographics.</t>
+          <t>State-by-year corporate income tax rates and tax-base rules (e.g., depreciation and apportionment), hand-collected/extended, used as variation in the tax incentive to borrow.</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>employer-employee; occupation</t>
+          <t>state taxes; corporate income; leverage</t>
         </is>
       </c>
       <c r="H90" s="2" t="n">
@@ -7455,32 +7679,36 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Journal of Financial Economics - 2026 - Hvide and Nielsen - Flying below the radar Insider trading by executives below the top</t>
+          <t>Review of Economic Studies - 2026 - Ivanov et al. - Taxes Depress Corporate Borrowing Evidence from Private Firms</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Supply-chain relationship data</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr"/>
+          <t>Statistics Norway</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Employer-employee register (ISCO-88)</t>
+        </is>
+      </c>
       <c r="C91" s="2" t="inlineStr"/>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Customer-supplier links used to identify U.S. manufacturers exposed to Taiwanese supply-chain disruption, combined with firm financials to compute productivity.</t>
+          <t>Population employer-employee data identifying each individual's position and demographics.</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>supply chain; customer-supplier; productivity</t>
+          <t>employer-employee; occupation</t>
         </is>
       </c>
       <c r="H91" s="2" t="n">
@@ -7488,32 +7716,32 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Journal of Accounting and Economics - 2026 - Berger and Tomy - Supply chain shocks and firm productivity The role of reporting quality</t>
+          <t>Journal of Financial Economics - 2026 - Hvide and Nielsen - Flying below the radar Insider trading by executives below the top</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Takeover announcement texts (intangibles word list)</t>
+          <t>Supply-chain relationship data</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr"/>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Text of takeover announcements scored with a purpose-built intangibles word list, used to measure 'intangibles talk'.</t>
+          <t>Customer-supplier links used to identify U.S. manufacturers exposed to Taiwanese supply-chain disruption, combined with firm financials to compute productivity.</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A; text; intangibles</t>
+          <t>supply chain; customer-supplier; productivity</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
@@ -7521,32 +7749,32 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Review of Financial Studies - 2026 - Filipović and Wagner - The Intangibles Song in Takeover Announcements Good Tempo, Hollow Tune</t>
+          <t>Journal of Accounting and Economics - 2026 - Berger and Tomy - Supply chain shocks and firm productivity The role of reporting quality</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Transaction-level international trade (customs) data</t>
+          <t>Takeover announcement texts (intangibles word list)</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr"/>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Firm-to-firm customs transactions with values, timing, payment terms, and partner identities, used to measure relationships and trade credit.</t>
+          <t>Text of takeover announcements scored with a purpose-built intangibles word list, used to measure 'intangibles talk'.</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>customs; trade; firm-to-firm</t>
+          <t>M&amp;A; text; intangibles</t>
         </is>
       </c>
       <c r="H93" s="2" t="n">
@@ -7554,21 +7782,21 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Journal of Financial Economics - 2026 - Benguria et al. - Trade credit and relationships</t>
+          <t>Review of Financial Studies - 2026 - Filipović and Wagner - The Intangibles Song in Takeover Announcements Good Tempo, Hollow Tune</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>U.S. Call Reports (via FOIA)</t>
+          <t>Transaction-level international trade (customs) data</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr"/>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Bank-level regulatory balance-sheet data obtained back to 1959 through a Freedom of Information Act request, used to measure deposits and lending contractions.</t>
+          <t>Firm-to-firm customs transactions with values, timing, payment terms, and partner identities, used to measure relationships and trade credit.</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -7579,7 +7807,7 @@
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>call reports; bank lending; 1959-</t>
+          <t>customs; trade; firm-to-firm</t>
         </is>
       </c>
       <c r="H94" s="2" t="n">
@@ -7587,36 +7815,32 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
+          <t>Journal of Financial Economics - 2026 - Benguria et al. - Trade credit and relationships</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>U.S. Census Bureau</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>LODES (LEHD Origin-Destination Employment Statistics)</t>
-        </is>
-      </c>
+          <t>U.S. Call Reports (via FOIA)</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr"/>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Sector-level job counts used to measure a city's industrial concentration.</t>
+          <t>Bank-level regulatory balance-sheet data obtained back to 1959 through a Freedom of Information Act request, used to measure deposits and lending contractions.</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>employment; industry concentration; LODES</t>
+          <t>call reports; bank lending; 1959-</t>
         </is>
       </c>
       <c r="H95" s="2" t="n">
@@ -7624,7 +7848,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
+          <t>Working Paper - 2026 - Drechsler et al. - Credit Crunches and the Great Stagflation</t>
         </is>
       </c>
     </row>
@@ -7636,24 +7860,24 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>LEHD merged with Longitudinal Business Database (LBD)</t>
+          <t>LODES (LEHD Origin-Destination Employment Statistics)</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr"/>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Confidential administrative data on establishment-level wage bill and employment used to measure local monopsony power and firm responses to monetary policy.</t>
+          <t>Sector-level job counts used to measure a city's industrial concentration.</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>administrative; wage bill; employment; monopsony</t>
+          <t>employment; industry concentration; LODES</t>
         </is>
       </c>
       <c r="H96" s="2" t="n">
@@ -7661,7 +7885,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Bardóczy et al. - Monopsony Power and the Transmission of Monetary Policy</t>
+          <t>Working Paper - 2026 - Ahern - Industrial Concentration, Property Values, and Municipal Bond Spreads</t>
         </is>
       </c>
     </row>
@@ -7673,13 +7897,13 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Business Database (LBD)</t>
+          <t>LEHD merged with Longitudinal Business Database (LBD)</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr"/>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Confidential data tracking entry and exit for the universe of U.S. employers, used to estimate the debt–exit relationship.</t>
+          <t>Confidential administrative data on establishment-level wage bill and employment used to measure local monopsony power and firm responses to monetary policy.</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -7690,7 +7914,7 @@
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>firm entry/exit; universe of employers</t>
+          <t>administrative; wage bill; employment; monopsony</t>
         </is>
       </c>
       <c r="H97" s="2" t="n">
@@ -7698,7 +7922,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Bornstein and Castillo-Martinez - Firm Exit and Financial Frictions</t>
+          <t>Working Paper - 2026 - Bardóczy et al. - Monopsony Power and the Transmission of Monetary Policy</t>
         </is>
       </c>
     </row>
@@ -7710,13 +7934,13 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Annual Survey of Manufactures / Census of Manufactures</t>
+          <t>Longitudinal Business Database (LBD)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr"/>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Establishment-level production, cost, and price data used to measure pass-through in manufacturing.</t>
+          <t>Confidential data tracking entry and exit for the universe of U.S. employers, used to estimate the debt–exit relationship.</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -7727,7 +7951,7 @@
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>manufacturing; costs; production</t>
+          <t>firm entry/exit; universe of employers</t>
         </is>
       </c>
       <c r="H98" s="2" t="n">
@@ -7735,7 +7959,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Quarterly Journal of Economics - 2026 - Sangani - Complete Pass-Through in Levels</t>
+          <t>Working Paper - 2026 - Bornstein and Castillo-Martinez - Firm Exit and Financial Frictions</t>
         </is>
       </c>
     </row>
@@ -7747,13 +7971,13 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal Business Database / firm microdata</t>
+          <t>Annual Survey of Manufactures / Census of Manufactures</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr"/>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Confidential firm entry and employment data used to measure entrepreneurship outcomes.</t>
+          <t>Establishment-level production, cost, and price data used to measure pass-through in manufacturing.</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -7764,7 +7988,7 @@
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>firm entry; employment; Census</t>
+          <t>manufacturing; costs; production</t>
         </is>
       </c>
       <c r="H99" s="2" t="n">
@@ -7772,36 +7996,36 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Journal of Financial Economics - 2026 - Lindsey and Stein - Angels, entrepreneurship, and employment dynamics Evidence from investor accreditation rules</t>
+          <t>Quarterly Journal of Economics - 2026 - Sangani - Complete Pass-Through in Levels</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>U.S. Department of Transportation</t>
+          <t>U.S. Census Bureau</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>DB1B (Airline Origin and Destination Survey)</t>
+          <t>Longitudinal Business Database / firm microdata</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr"/>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Route-level airline ticket prices and quantities used to measure competitive responses to the tax reform.</t>
+          <t>Confidential firm entry and employment data used to measure entrepreneurship outcomes.</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>airlines; routes; prices; market share</t>
+          <t>firm entry; employment; Census</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
@@ -7809,21 +8033,25 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Journal of Accounting and Economics - 2026 - Hanlon et al. - Taxes and Competition Evidence from the airline industry</t>
+          <t>Journal of Financial Economics - 2026 - Lindsey and Stein - Angels, entrepreneurship, and employment dynamics Evidence from investor accreditation rules</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>U.S. federal district court filings (PACER)</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr"/>
+          <t>U.S. Department of Transportation</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>DB1B (Airline Origin and Destination Survey)</t>
+        </is>
+      </c>
       <c r="C101" s="2" t="inlineStr"/>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Comprehensive civil case filings against public-company defendants (2006-2021), spanning many allegation types, used to measure litigation incidence and outcomes.</t>
+          <t>Route-level airline ticket prices and quantities used to measure competitive responses to the tax reform.</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -7834,7 +8062,7 @@
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>federal courts; lawsuits; PACER</t>
+          <t>airlines; routes; prices; market share</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
@@ -7842,21 +8070,21 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Journal of Accounting Research - 2026 - Billings et al. - Incidence, Risk, and Disclosure of Corporate Litigation Insights from Federal Court Filings</t>
+          <t>Journal of Accounting and Economics - 2026 - Hanlon et al. - Taxes and Competition Evidence from the airline industry</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>UBS/Gallup and Livingston Survey</t>
+          <t>U.S. federal district court filings (PACER)</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr"/>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Survey measures of individual-investor and professional-forecaster return/earnings expectations used for comparison.</t>
+          <t>Comprehensive civil case filings against public-company defendants (2006-2021), spanning many allegation types, used to measure litigation incidence and outcomes.</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -7867,7 +8095,7 @@
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>investor surveys; forecaster expectations</t>
+          <t>federal courts; lawsuits; PACER</t>
         </is>
       </c>
       <c r="H102" s="2" t="n">
@@ -7875,36 +8103,32 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+          <t>Journal of Accounting Research - 2026 - Billings et al. - Incidence, Risk, and Disclosure of Corporate Litigation Insights from Federal Court Filings</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Unified Patents</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Post-grant review data</t>
-        </is>
-      </c>
+          <t>UBS/Gallup and Livingston Survey</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="2" t="inlineStr"/>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>USPTO post-grant reviews used to validate the ModernBERT Alice score.</t>
+          <t>Survey measures of individual-investor and professional-forecaster return/earnings expectations used for comparison.</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>post-grant review; validation</t>
+          <t>investor surveys; forecaster expectations</t>
         </is>
       </c>
       <c r="H103" s="2" t="n">
@@ -7912,40 +8136,36 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language models</t>
+          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>USPTO</t>
+          <t>Unified Patents</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Patent application office actions</t>
+          <t>Post-grant review data</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr"/>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>U.S. patent applications and examiner rejections used to identify Alice-based rejections and build training labels.</t>
+          <t>USPTO post-grant reviews used to validate the ModernBERT Alice score.</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>Bulk</t>
-        </is>
-      </c>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>patents; rejections</t>
+          <t>post-grant review; validation</t>
         </is>
       </c>
       <c r="H104" s="2" t="n">
@@ -7960,18 +8180,18 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>USPTO</t>
+          <t>US bankruptcy filings</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Patent assignment (reassignment) records</t>
+          <t>corporate bankruptcy records</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr"/>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Records of patent ownership transfers used to identify the timing and characteristics of firms' patent sales.</t>
+          <t>Records of corporate bankruptcy filings used to date firms' approach to, entry into, and exit from bankruptcy.</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -7982,7 +8202,7 @@
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>patents; assignments; sales</t>
+          <t>bankruptcy; financial distress; firms</t>
         </is>
       </c>
       <c r="H105" s="2" t="n">
@@ -7990,21 +8210,25 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Journal of Accounting and Economics - 2026 - Kim and Valentine - Earnings targets, strategic patent sales, and patent trolls</t>
+          <t>American Law and Economics Review - 2023 - Ohlrogge - Down the Tubes Financial Distress, Bankruptcy, and Industrial Water Pollution</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>USPTO patent and inventor data</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr"/>
+          <t>US Environmental Protection Agency</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>NPDES discharge monitoring reports (Clean Water Act)</t>
+        </is>
+      </c>
       <c r="C106" s="2" t="inlineStr"/>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Patents, inventors, and assignment records used to track inventors' retention and reassignment of rights around the ruling.</t>
+          <t>Facility-level water-pollution discharge monitoring reports and permitted-limit exceedances under the Clean Water Act's NPDES program, for roughly 350 bankrupt firms and comparison facilities.</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -8012,14 +8236,10 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>Bulk</t>
-        </is>
-      </c>
+      <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>patents; inventors; assignments</t>
+          <t>water pollution; NPDES; compliance; Clean Water Act</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
@@ -8027,21 +8247,25 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Journal of Accounting Research - 2026 - Armstrong et al. - The Assignment of Intellectual Property Rights and Innovation</t>
+          <t>American Law and Economics Review - 2023 - Ohlrogge - Down the Tubes Financial Distress, Bankruptcy, and Industrial Water Pollution</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>USPTO patent data</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr"/>
+          <t>USPTO</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Patent application office actions</t>
+        </is>
+      </c>
       <c r="C107" s="2" t="inlineStr"/>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Patent grants, citations, and text used to construct firms' absorption-intensity measure.</t>
+          <t>U.S. patent applications and examiner rejections used to identify Alice-based rejections and build training labels.</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -8049,10 +8273,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Bulk</t>
+        </is>
+      </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>patents; citations; absorption</t>
+          <t>patents; rejections</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
@@ -8060,32 +8288,36 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Journal of Financial Economics - 2026 - Woeppel and Yavuz - Measuring firms' capability to absorb external knowledge</t>
+          <t>Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language models</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Value Line Investment Survey</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr"/>
+          <t>USPTO</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Patent assignment (reassignment) records</t>
+        </is>
+      </c>
       <c r="C108" s="2" t="inlineStr"/>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Analyst forecasts hand-collected from microfilm records (1956-2024) used to construct a long-run series of sophisticated investors' subjective expected returns.</t>
+          <t>Records of patent ownership transfers used to identify the timing and characteristics of firms' patent sales.</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>subjective expectations; analyst forecasts; microfilm</t>
+          <t>patents; assignments; sales</t>
         </is>
       </c>
       <c r="H108" s="2" t="n">
@@ -8093,21 +8325,21 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
+          <t>Journal of Accounting and Economics - 2026 - Kim and Valentine - Earnings targets, strategic patent sales, and patent trolls</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Vehicle tariff exposure data</t>
+          <t>USPTO patent and inventor data</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="2" t="inlineStr"/>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Data on which vehicles/components were affected by tariffs, used to construct exposure to the trade-policy shock.</t>
+          <t>Patents, inventors, and assignment records used to track inventors' retention and reassignment of rights around the ruling.</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -8115,10 +8347,14 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Bulk</t>
+        </is>
+      </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>tariffs; autos; exposure</t>
+          <t>patents; inventors; assignments</t>
         </is>
       </c>
       <c r="H109" s="2" t="n">
@@ -8126,32 +8362,32 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>American Economic Review - 2026 - Hankins et al. - Consumer Credit and the Incidence of Tariffs Evidence from the Auto Industry</t>
+          <t>Journal of Accounting Research - 2026 - Armstrong et al. - The Assignment of Intellectual Property Rights and Innovation</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Venture Expert (Refinitiv)</t>
+          <t>USPTO patent data</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="2" t="inlineStr"/>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>VC financing rounds and startup descriptions used to measure VC-backed entry.</t>
+          <t>Patent grants, citations, and text used to construct firms' absorption-intensity measure.</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>venture capital; entry</t>
+          <t>patents; citations; absorption</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
@@ -8159,32 +8395,32 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language models</t>
+          <t>Journal of Financial Economics - 2026 - Woeppel and Yavuz - Measuring firms' capability to absorb external knowledge</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Website cookie / web-tracking data</t>
+          <t>Value Line Investment Survey</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr"/>
       <c r="C111" s="2" t="inlineStr"/>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Data on cookies and trackers deployed on U.S. firms' websites, used to proxy the intensity of consumer-data collection.</t>
+          <t>Analyst forecasts hand-collected from microfilm records (1956-2024) used to construct a long-run series of sophisticated investors' subjective expected returns.</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>cookies; web tracking; consumer data</t>
+          <t>subjective expectations; analyst forecasts; microfilm</t>
         </is>
       </c>
       <c r="H111" s="2" t="n">
@@ -8192,69 +8428,65 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Journal of Accounting and Economics - 2026 - Liu - Website cookies and voluntary disclosure</t>
+          <t>Working Paper - 2026 - Thesmar and Verner - Beliefs and Stock Market Fluctuations New Evidence from the Past Seven Decades</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>WIND</t>
+          <t>Vehicle tariff exposure data</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr"/>
       <c r="C112" s="2" t="inlineStr"/>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Adjusted opening prices and free-floating shares for Chinese listed stocks. Chinese market and firm data used alongside CSMAR.</t>
+          <t>Data on which vehicles/components were affected by tariffs, used to construct exposure to the trade-policy shock.</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Proprietary</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>China; prices; shares; firm data</t>
+          <t>tariffs; autos; exposure</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Working Paper - 2026 - He et al. - Homemade Foreign Trading; Journal of Financial Economics - 2026 - Goldstein et al. - Market feedback Evidence from the horse's mouth</t>
+          <t>American Economic Review - 2026 - Hankins et al. - Consumer Credit and the Incidence of Tariffs Evidence from the Auto Industry</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>World Bank</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Firm-level Adoption of Technology (FAT) survey</t>
-        </is>
-      </c>
+          <t>Venture Expert (Refinitiv)</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr"/>
       <c r="C113" s="2" t="inlineStr"/>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Novel establishment survey measuring the most advanced and most widely used technologies across business functions for 21,000+ establishments in 15 countries.</t>
+          <t>VC financing rounds and startup descriptions used to measure VC-backed entry.</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>technology adoption; establishments; cross-country survey</t>
+          <t>venture capital; entry</t>
         </is>
       </c>
       <c r="H113" s="2" t="n">
@@ -8262,49 +8494,152 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Quarterly Journal of Economics - 2026 - Cirera et al. - Technology Sophistication Across Establishments</t>
+          <t>Journal of Financial Economics - 2026 - Acikalin et al. - Intellectual property protection lost and competition An examination using large language models</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Yunan Ji</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Medicare DME auction bids</t>
-        </is>
-      </c>
+          <t>Website cookie / web-tracking data</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr"/>
       <c r="C114" s="2" t="inlineStr"/>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Bids submitted in Medicare's DME competitive-bidding auctions, shared by the author, used in the bidding analysis.</t>
+          <t>Data on cookies and trackers deployed on U.S. firms' websites, used to proxy the intensity of consumer-data collection.</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Proprietary</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
+          <t>cookies; web tracking; consumer data</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Accounting and Economics - 2026 - Liu - Website cookies and voluntary disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>WIND</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr"/>
+      <c r="C115" s="2" t="inlineStr"/>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Adjusted opening prices and free-floating shares for Chinese listed stocks. Chinese market and firm data used alongside CSMAR.</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>China; prices; shares; firm data</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Working Paper - 2026 - He et al. - Homemade Foreign Trading; Journal of Financial Economics - 2026 - Goldstein et al. - Market feedback Evidence from the horse's mouth</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>World Bank</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Firm-level Adoption of Technology (FAT) survey</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr"/>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Novel establishment survey measuring the most advanced and most widely used technologies across business functions for 21,000+ establishments in 15 countries.</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>technology adoption; establishments; cross-country survey</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly Journal of Economics - 2026 - Cirera et al. - Technology Sophistication Across Establishments</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Yunan Ji</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Medicare DME auction bids</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr"/>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Bids submitted in Medicare's DME competitive-bidding auctions, shared by the author, used in the bidding analysis.</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
           <t>auction bids; competitive bidding</t>
         </is>
       </c>
-      <c r="H114" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
+      <c r="H117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
         <is>
           <t>Working Paper - 2026 - Diwan et al. - Competition and Fraud in Health Care</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I114"/>
+  <autoFilter ref="A1:I117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8315,7 +8650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9111,32 +9446,86 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>Direct and Indirect Effects of Investment Tax Incentives</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Lerche</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Post-reunification German investment tax credit (size-differential rate change)</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>policy natural experiment (difference-in-differences)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>An investment tax credit whose rate changed more for small firms (around a 250-employee cutoff), providing differential variation in the user cost of capital used to identify direct and local spillover effects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>Doctor Discretion in Medical Evaluations</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Cabral, Dillender</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Quasi-random assignment of independent medical examiners</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Examiner-leniency (random assignment)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>The quasi-random assignment of injured workers to more- or less-generous independent medical examiners, used as an examiner-leniency design to identify the effect of medical evaluations on disability outcomes.</t>
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Down the Tubes: Financial Distress, Bankruptcy, and Industrial Water Pollution</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Ohlrogge</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Corporate bankruptcy filing</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>event study / difference-in-differences</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>The approach to, filing of, and exit from bankruptcy by CWA-regulated firms, whose timing is used to identify changes in pollution compliance relative to non-bankrupt comparison facilities.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E30"/>
+  <autoFilter ref="A1:E32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>